--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="173">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -546,6 +546,9 @@
   </si>
   <si>
     <t>The first plan: conversations.conversation_archived and conversations.conversation_unarchived, with a conversations.conversation snapshot (the reference flow of ADR 0020).</t>
+  </si>
+  <si>
+    <t>#632</t>
   </si>
 </sst>
 </file>
@@ -2085,6 +2088,9 @@
       <c r="C2" s="3" t="s">
         <v>171</v>
       </c>
+      <c r="D2" s="3" t="s">
+        <v>172</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D2"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -18,19 +18,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Actors!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Records!$A$1:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Records!$A$1:$I$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="786">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Plan version</t>
   </si>
   <si>
-    <t>1 (2026-10-23)</t>
+    <t>2 (2026-10-24)</t>
   </si>
   <si>
     <t>What this is</t>
@@ -233,6 +233,84 @@
     <t>add-tracked-events</t>
   </si>
   <si>
+    <t>conversations.conversation_labelled</t>
+  </si>
+  <si>
+    <t>labelled</t>
+  </si>
+  <si>
+    <t>user, client, assistant, automation</t>
+  </si>
+  <si>
+    <t>A label was put on a conversation.</t>
+  </si>
+  <si>
+    <t>Adding the label links it to the conversation (conversations.add_label). A label already on it tracks nothing.</t>
+  </si>
+  <si>
+    <t>track-conversations-events</t>
+  </si>
+  <si>
+    <t>conversations.conversation_moved</t>
+  </si>
+  <si>
+    <t>moved</t>
+  </si>
+  <si>
+    <t>A member moved a conversation to another stream.</t>
+  </si>
+  <si>
+    <t>Moving it changes its stream (conversations.move_to_stream); the move is recorded as a correction. A move to the stream it is in tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.conversation_read</t>
+  </si>
+  <si>
+    <t>read</t>
+  </si>
+  <si>
+    <t>A conversation was marked read.</t>
+  </si>
+  <si>
+    <t>Marking it read changes at least one of its messages (conversations.mark_read), in the transaction of that change. A conversation already read tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.conversation_spammed</t>
+  </si>
+  <si>
+    <t>spammed</t>
+  </si>
+  <si>
+    <t>A conversation was reported as spam: out of the inbox, into spam.</t>
+  </si>
+  <si>
+    <t>Reporting it changes at least one of its messages (conversations.report_spam). One already in spam tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.conversation_starred</t>
+  </si>
+  <si>
+    <t>starred</t>
+  </si>
+  <si>
+    <t>A conversation was starred.</t>
+  </si>
+  <si>
+    <t>Starring it stars its newest message (conversations.star). One already starred tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.conversation_trashed</t>
+  </si>
+  <si>
+    <t>trashed</t>
+  </si>
+  <si>
+    <t>A conversation went to the trash.</t>
+  </si>
+  <si>
+    <t>Trashing it changes at least one of its messages (conversations.trash). One already in the trash tracks nothing.</t>
+  </si>
+  <si>
     <t>conversations.conversation_unarchived</t>
   </si>
   <si>
@@ -245,6 +323,450 @@
     <t>Moving it back changes at least one of the conversation's messages (conversations.unarchive, the undo of conversations.archive), in the transaction of that change.</t>
   </si>
   <si>
+    <t>conversations.conversation_unlabelled</t>
+  </si>
+  <si>
+    <t>unlabelled</t>
+  </si>
+  <si>
+    <t>A label was taken off a conversation.</t>
+  </si>
+  <si>
+    <t>Removing the label unlinks it (conversations.remove_label).</t>
+  </si>
+  <si>
+    <t>conversations.conversation_unread_marked</t>
+  </si>
+  <si>
+    <t>unread_marked</t>
+  </si>
+  <si>
+    <t>A conversation was marked unread.</t>
+  </si>
+  <si>
+    <t>Marking it unread changes its newest message (conversations.mark_unread). One already unread tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.conversation_unspammed</t>
+  </si>
+  <si>
+    <t>unspammed</t>
+  </si>
+  <si>
+    <t>A conversation was taken out of spam (Not spam): received mail back in the inbox.</t>
+  </si>
+  <si>
+    <t>Taking it out of spam changes at least one of its messages (conversations.not_spam).</t>
+  </si>
+  <si>
+    <t>conversations.conversation_unstarred</t>
+  </si>
+  <si>
+    <t>unstarred</t>
+  </si>
+  <si>
+    <t>A conversation was unstarred.</t>
+  </si>
+  <si>
+    <t>Unstarring it changes at least one of its messages (conversations.unstar). One with no star tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.conversation_untrashed</t>
+  </si>
+  <si>
+    <t>untrashed</t>
+  </si>
+  <si>
+    <t>A conversation came out of the trash, back where it was.</t>
+  </si>
+  <si>
+    <t>Taking it out of the trash changes at least one of its messages (conversations.untrash).</t>
+  </si>
+  <si>
+    <t>conversations.draft_created</t>
+  </si>
+  <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>created</t>
+  </si>
+  <si>
+    <t>user, client, assistant</t>
+  </si>
+  <si>
+    <t>A draft was started: new, a reply, a reply all, a forward or a nudge.</t>
+  </si>
+  <si>
+    <t>The draft is stored (conversations.create_draft).</t>
+  </si>
+  <si>
+    <t>conversations.draft_discarded</t>
+  </si>
+  <si>
+    <t>discarded</t>
+  </si>
+  <si>
+    <t>A draft was discarded.</t>
+  </si>
+  <si>
+    <t>The draft is deleted (conversations.delete_draft).</t>
+  </si>
+  <si>
+    <t>conversations.draft_released</t>
+  </si>
+  <si>
+    <t>released</t>
+  </si>
+  <si>
+    <t>system</t>
+  </si>
+  <si>
+    <t>A scheduled send was handed to the connector.</t>
+  </si>
+  <si>
+    <t>Its undo window passed and the release marks it sending (conversations.release_send).</t>
+  </si>
+  <si>
+    <t>conversations.draft_scheduled</t>
+  </si>
+  <si>
+    <t>scheduled</t>
+  </si>
+  <si>
+    <t>user, client</t>
+  </si>
+  <si>
+    <t>A member sent a draft: it waits out its undo window.</t>
+  </si>
+  <si>
+    <t>The send is scheduled (conversations.send_draft).</t>
+  </si>
+  <si>
+    <t>conversations.draft_send_failed</t>
+  </si>
+  <si>
+    <t>send_failed</t>
+  </si>
+  <si>
+    <t>A send failed: the draft is editable and sendable again.</t>
+  </si>
+  <si>
+    <t>The connector reports it failed (conversations.record_send), or no report came back in time (conversations.check_send, unknown_outcome).</t>
+  </si>
+  <si>
+    <t>conversations.draft_sent</t>
+  </si>
+  <si>
+    <t>sent</t>
+  </si>
+  <si>
+    <t>The provider sent a draft.</t>
+  </si>
+  <si>
+    <t>The connector reports it sent (conversations.record_send, on connectors.send_completed), before the draft is deleted.</t>
+  </si>
+  <si>
+    <t>conversations.draft_unscheduled</t>
+  </si>
+  <si>
+    <t>unscheduled</t>
+  </si>
+  <si>
+    <t>user, client, system</t>
+  </si>
+  <si>
+    <t>A scheduled send was taken back: a draft again.</t>
+  </si>
+  <si>
+    <t>A member cancels it during its undo window (conversations.cancel_send), or the release finds its author may no longer send from the inbox (conversations.release_send). A draft not scheduled tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.draft_updated</t>
+  </si>
+  <si>
+    <t>updated</t>
+  </si>
+  <si>
+    <t>A draft was saved with a change.</t>
+  </si>
+  <si>
+    <t>A save changes its recipients, subject, text, quoted history, attachments, or makes a failed draft a draft again (conversations.update_draft). A save that changes nothing tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.inbox_closed</t>
+  </si>
+  <si>
+    <t>inbox</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>A removed connection's inbox was deleted with its mail, or kept read-only.</t>
+  </si>
+  <si>
+    <t>The inbox is deleted or frozen (conversations.forget_connection, on connectors.connection_removed). An inbox already gone or frozen tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.inbox_created</t>
+  </si>
+  <si>
+    <t>An inbox was created for a connection that gained the messages capability.</t>
+  </si>
+  <si>
+    <t>The inbox is created (conversations.create_inbox, on connectors.capability_granted). A replay or an inbox already there tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.message_batch_applied</t>
+  </si>
+  <si>
+    <t>message_batch</t>
+  </si>
+  <si>
+    <t>applied</t>
+  </si>
+  <si>
+    <t>A batch of the provider's message changes was applied to an inbox.</t>
+  </si>
+  <si>
+    <t>Applying it adds, changes or removes at least one message (conversations.apply_changes). A batch that changes nothing tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.message_decided</t>
+  </si>
+  <si>
+    <t>message</t>
+  </si>
+  <si>
+    <t>decided</t>
+  </si>
+  <si>
+    <t>The model pass answered the triage questions about an inbound message.</t>
+  </si>
+  <si>
+    <t>Its answers are stored (conversations.decide_message as mail arrives, conversations.decide_backlog for stored mail). A pass that stores nothing (no model, over the daily limit, already answered) tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.message_read_completed</t>
+  </si>
+  <si>
+    <t>message_read</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>A read of a message was stored: the sender's own structured data, or Scout's read.</t>
+  </si>
+  <si>
+    <t>The read is stored (conversations.read_structured, conversations.read_message). Never what it read: counts only.</t>
+  </si>
+  <si>
+    <t>conversations.message_read_requested</t>
+  </si>
+  <si>
+    <t>requested</t>
+  </si>
+  <si>
+    <t>A member opened a message and Scout's read of it was queued.</t>
+  </si>
+  <si>
+    <t>The read is queued (conversations.request_message_read). Anything else it answers (already read, queued, not flagged, unavailable) tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.need_confirmed</t>
+  </si>
+  <si>
+    <t>need</t>
+  </si>
+  <si>
+    <t>confirmed</t>
+  </si>
+  <si>
+    <t>A member answered yes to the question a conversation's need asked.</t>
+  </si>
+  <si>
+    <t>The yes is stored (conversations.confirm_need).</t>
+  </si>
+  <si>
+    <t>conversations.need_reopened</t>
+  </si>
+  <si>
+    <t>reopened</t>
+  </si>
+  <si>
+    <t>A member took back their verdict on a conversation's need (Undo).</t>
+  </si>
+  <si>
+    <t>The verdict is taken back (conversations.reopen_need).</t>
+  </si>
+  <si>
+    <t>conversations.need_resolved</t>
+  </si>
+  <si>
+    <t>resolved</t>
+  </si>
+  <si>
+    <t>A member gave a verdict on what a conversation needs: done, not needed, already paid or still to pay.</t>
+  </si>
+  <si>
+    <t>The verdict is stored (conversations.resolve_need), in the transaction that works the need out again. Still to pay on a need that was no question changes nothing and tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.person_note_deleted</t>
+  </si>
+  <si>
+    <t>person_note</t>
+  </si>
+  <si>
+    <t>deleted</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>A member deleted a note about a person.</t>
+  </si>
+  <si>
+    <t>The note is deleted (conversations.delete_person_note).</t>
+  </si>
+  <si>
+    <t>conversations.person_note_saved</t>
+  </si>
+  <si>
+    <t>saved</t>
+  </si>
+  <si>
+    <t>A member saved what they told Scout about a person.</t>
+  </si>
+  <si>
+    <t>A note is created or its text changed (conversations.set_person_note). The same text again tracks nothing. Never the note, nor whom it is about.</t>
+  </si>
+  <si>
+    <t>conversations.rule_confirmed</t>
+  </si>
+  <si>
+    <t>rule</t>
+  </si>
+  <si>
+    <t>A member said yes to a rule: it acts with their rights.</t>
+  </si>
+  <si>
+    <t>A proposal is kept, or a kept rule is bound again (conversations.confirm_rule).</t>
+  </si>
+  <si>
+    <t>conversations.rule_created</t>
+  </si>
+  <si>
+    <t>A taught rule was stored: acting, or proposed for a member's yes.</t>
+  </si>
+  <si>
+    <t>The rule is stored (conversations.create_rule).</t>
+  </si>
+  <si>
+    <t>conversations.rule_declined</t>
+  </si>
+  <si>
+    <t>declined</t>
+  </si>
+  <si>
+    <t>A member turned a proposed rule down.</t>
+  </si>
+  <si>
+    <t>The proposal is removed (conversations.decline_rule).</t>
+  </si>
+  <si>
+    <t>conversations.rule_notice_answer_cleared</t>
+  </si>
+  <si>
+    <t>rule_notice</t>
+  </si>
+  <si>
+    <t>answer_cleared</t>
+  </si>
+  <si>
+    <t>A member took back their answer to a suggestion (Undo): it is offered again.</t>
+  </si>
+  <si>
+    <t>An answer is deleted (conversations.clear_rule_notice_answer). No answer to take back tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.rule_notice_answered</t>
+  </si>
+  <si>
+    <t>answered</t>
+  </si>
+  <si>
+    <t>A member answered a Scout-noticed suggestion: not now, or never.</t>
+  </si>
+  <si>
+    <t>The answer is stored (conversations.answer_rule_notice).</t>
+  </si>
+  <si>
+    <t>conversations.rule_removed</t>
+  </si>
+  <si>
+    <t>removed</t>
+  </si>
+  <si>
+    <t>A rule was removed.</t>
+  </si>
+  <si>
+    <t>A member removes it (conversations.remove_rule), or a rule created, confirmed, updated or restored replaces it (cause replaced), in that transaction.</t>
+  </si>
+  <si>
+    <t>conversations.rule_restored</t>
+  </si>
+  <si>
+    <t>restored</t>
+  </si>
+  <si>
+    <t>A removed rule was brought back (Undo).</t>
+  </si>
+  <si>
+    <t>The rule is restored (conversations.restore_rule).</t>
+  </si>
+  <si>
+    <t>conversations.rule_run_finished</t>
+  </si>
+  <si>
+    <t>rule_run</t>
+  </si>
+  <si>
+    <t>finished</t>
+  </si>
+  <si>
+    <t>A run applying a rule to an inbox's mail, or putting it back, ended.</t>
+  </si>
+  <si>
+    <t>The run ends, done or cancelled (conversations.apply_rule), in the transaction of its last batch. One event per run, with its counts: a run touches a whole inbox.</t>
+  </si>
+  <si>
+    <t>conversations.rule_suggestion_dismissed</t>
+  </si>
+  <si>
+    <t>rule_suggestion</t>
+  </si>
+  <si>
+    <t>dismissed</t>
+  </si>
+  <si>
+    <t>A member turned down the rules suggested after acting on a conversation.</t>
+  </si>
+  <si>
+    <t>The dismissal is stored (conversations.dismiss_rule_suggestion). Only a member's own dismissal is stored.</t>
+  </si>
+  <si>
+    <t>conversations.rule_updated</t>
+  </si>
+  <si>
+    <t>A rule was changed: reshaped, paused, resumed or adopted.</t>
+  </si>
+  <si>
+    <t>The rule is saved (conversations.update_rule).</t>
+  </si>
+  <si>
     <t>Property</t>
   </si>
   <si>
@@ -284,9 +806,321 @@
     <t>The conversation after archiving.</t>
   </si>
   <si>
+    <t>The conversation afterwards.</t>
+  </si>
+  <si>
+    <t>label_created</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>Whether the inbox's label was created by this request.</t>
+  </si>
+  <si>
+    <t>label_id</t>
+  </si>
+  <si>
+    <t>The label (its name is never tracked).</t>
+  </si>
+  <si>
+    <t>before</t>
+  </si>
+  <si>
+    <t>The conversation before the move: the stream it left and who had placed it there.</t>
+  </si>
+  <si>
     <t>The conversation after it went back to the inbox.</t>
   </si>
   <si>
+    <t>The label.</t>
+  </si>
+  <si>
+    <t>conversations.draft</t>
+  </si>
+  <si>
+    <t>The draft afterwards.</t>
+  </si>
+  <si>
+    <t>The draft as it was when it was discarded.</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>enum</t>
+  </si>
+  <si>
+    <t>conversations.send_error</t>
+  </si>
+  <si>
+    <t>The kind of failure.</t>
+  </si>
+  <si>
+    <t>The draft as it left (state sent).</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>conversations.unschedule_reason</t>
+  </si>
+  <si>
+    <t>Why it was taken back.</t>
+  </si>
+  <si>
+    <t>draft_count</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>Drafts it held.</t>
+  </si>
+  <si>
+    <t>inbox_id</t>
+  </si>
+  <si>
+    <t>The inbox.</t>
+  </si>
+  <si>
+    <t>mail</t>
+  </si>
+  <si>
+    <t>conversations.closed_mail</t>
+  </si>
+  <si>
+    <t>What happened to its mail.</t>
+  </si>
+  <si>
+    <t>message_count</t>
+  </si>
+  <si>
+    <t>Messages it held.</t>
+  </si>
+  <si>
+    <t>connection_id</t>
+  </si>
+  <si>
+    <t>The connection that feeds it.</t>
+  </si>
+  <si>
+    <t>member_added</t>
+  </si>
+  <si>
+    <t>Whether the granting member was added as its manager.</t>
+  </si>
+  <si>
+    <t>backfill</t>
+  </si>
+  <si>
+    <t>Whether it is part of the first import.</t>
+  </si>
+  <si>
+    <t>conversations_changed</t>
+  </si>
+  <si>
+    <t>Conversations the batch created or changed.</t>
+  </si>
+  <si>
+    <t>messages_added</t>
+  </si>
+  <si>
+    <t>Messages stored.</t>
+  </si>
+  <si>
+    <t>messages_removed</t>
+  </si>
+  <si>
+    <t>Messages the provider deleted.</t>
+  </si>
+  <si>
+    <t>messages_updated</t>
+  </si>
+  <si>
+    <t>Known messages whose flags, labels or stream changed.</t>
+  </si>
+  <si>
+    <t>rules_acted</t>
+  </si>
+  <si>
+    <t>Arriving messages a taught rule acted on.</t>
+  </si>
+  <si>
+    <t>answer_count</t>
+  </si>
+  <si>
+    <t>How many answers it stored.</t>
+  </si>
+  <si>
+    <t>Its conversation afterwards.</t>
+  </si>
+  <si>
+    <t>message_id</t>
+  </si>
+  <si>
+    <t>The message.</t>
+  </si>
+  <si>
+    <t>moves_only</t>
+  </si>
+  <si>
+    <t>Whether only whose move it is was asked.</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>conversations.decide_pass</t>
+  </si>
+  <si>
+    <t>Which pass.</t>
+  </si>
+  <si>
+    <t>placed</t>
+  </si>
+  <si>
+    <t>Whether its answer placed the conversation in a stream.</t>
+  </si>
+  <si>
+    <t>ask_count</t>
+  </si>
+  <si>
+    <t>Obligations it found.</t>
+  </si>
+  <si>
+    <t>conversation_id</t>
+  </si>
+  <si>
+    <t>Its conversation.</t>
+  </si>
+  <si>
+    <t>item_count</t>
+  </si>
+  <si>
+    <t>Things that happen at a time it found.</t>
+  </si>
+  <si>
+    <t>layer</t>
+  </si>
+  <si>
+    <t>conversations.read_layer</t>
+  </si>
+  <si>
+    <t>Which read.</t>
+  </si>
+  <si>
+    <t>outcome</t>
+  </si>
+  <si>
+    <t>conversations.read_outcome</t>
+  </si>
+  <si>
+    <t>Whether the read was usable.</t>
+  </si>
+  <si>
+    <t>summary_ready</t>
+  </si>
+  <si>
+    <t>Whether it wrote a summary of the need.</t>
+  </si>
+  <si>
+    <t>trigger</t>
+  </si>
+  <si>
+    <t>conversations.read_trigger</t>
+  </si>
+  <si>
+    <t>What asked for Scout's read; absent for structured data.</t>
+  </si>
+  <si>
+    <t>conversations.need</t>
+  </si>
+  <si>
+    <t>Its need afterwards; absent when it has none.</t>
+  </si>
+  <si>
+    <t>note_id</t>
+  </si>
+  <si>
+    <t>The note.</t>
+  </si>
+  <si>
+    <t>Whether it is a new note.</t>
+  </si>
+  <si>
+    <t>conversations.rule</t>
+  </si>
+  <si>
+    <t>The rule afterwards.</t>
+  </si>
+  <si>
+    <t>acted_without_asking</t>
+  </si>
+  <si>
+    <t>Whether it acts at once because the member lets Campbooks act without asking.</t>
+  </si>
+  <si>
+    <t>Its inbox.</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>conversations.notice_kind</t>
+  </si>
+  <si>
+    <t>What it suggested.</t>
+  </si>
+  <si>
+    <t>notice_id</t>
+  </si>
+  <si>
+    <t>The suggestion.</t>
+  </si>
+  <si>
+    <t>answer</t>
+  </si>
+  <si>
+    <t>conversations.notice_answer</t>
+  </si>
+  <si>
+    <t>The answer.</t>
+  </si>
+  <si>
+    <t>cause</t>
+  </si>
+  <si>
+    <t>conversations.rule_removal_cause</t>
+  </si>
+  <si>
+    <t>Why it was removed.</t>
+  </si>
+  <si>
+    <t>put_back</t>
+  </si>
+  <si>
+    <t>Whether what it changed is being put back.</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>conversations.rule_run</t>
+  </si>
+  <si>
+    <t>The run as it ended.</t>
+  </si>
+  <si>
+    <t>The conversation the suggestion came from.</t>
+  </si>
+  <si>
+    <t>times</t>
+  </si>
+  <si>
+    <t>How many times the member has turned it down.</t>
+  </si>
+  <si>
     <t>Record</t>
   </si>
   <si>
@@ -299,9 +1133,6 @@
     <t>The conversation's id.</t>
   </si>
   <si>
-    <t>inbox_id</t>
-  </si>
-  <si>
     <t>The inbox it belongs to.</t>
   </si>
   <si>
@@ -314,30 +1145,15 @@
     <t>When its newest message was sent: its last activity.</t>
   </si>
   <si>
-    <t>message_count</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>How many messages it holds.</t>
   </si>
   <si>
-    <t>starred</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>Whether any of its messages is starred.</t>
   </si>
   <si>
     <t>status</t>
   </si>
   <si>
-    <t>enum</t>
-  </si>
-  <si>
     <t>conversations.conversation_status</t>
   </si>
   <si>
@@ -368,15 +1184,315 @@
     <t>How many of its inbound messages are unread.</t>
   </si>
   <si>
+    <t>attachment_count</t>
+  </si>
+  <si>
+    <t>How many forwarded attachments.</t>
+  </si>
+  <si>
+    <t>bcc_count</t>
+  </si>
+  <si>
+    <t>How many blind-copied recipients.</t>
+  </si>
+  <si>
+    <t>cc_count</t>
+  </si>
+  <si>
+    <t>How many copied recipients.</t>
+  </si>
+  <si>
+    <t>The conversation it answers, if any.</t>
+  </si>
+  <si>
+    <t>failure</t>
+  </si>
+  <si>
+    <t>Why its last send failed, while it is failed.</t>
+  </si>
+  <si>
+    <t>The draft.</t>
+  </si>
+  <si>
+    <t>The inbox it is sent from.</t>
+  </si>
+  <si>
+    <t>conversations.draft_kind</t>
+  </si>
+  <si>
+    <t>What it answers.</t>
+  </si>
+  <si>
+    <t>The message it replies to or forwards, if any.</t>
+  </si>
+  <si>
+    <t>send_at</t>
+  </si>
+  <si>
+    <t>When a scheduled send leaves.</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>conversations.draft_state</t>
+  </si>
+  <si>
+    <t>Where it is in its life.</t>
+  </si>
+  <si>
+    <t>to_count</t>
+  </si>
+  <si>
+    <t>How many recipients (never who).</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Its save count.</t>
+  </si>
+  <si>
+    <t>basis</t>
+  </si>
+  <si>
+    <t>conversations.need_basis</t>
+  </si>
+  <si>
+    <t>Whose answer raised it.</t>
+  </si>
+  <si>
+    <t>cleared_because</t>
+  </si>
+  <si>
+    <t>conversations.clear_cause</t>
+  </si>
+  <si>
+    <t>Why it was cleared, once cleared.</t>
+  </si>
+  <si>
+    <t>The conversation it belongs to.</t>
+  </si>
+  <si>
+    <t>has_due_date</t>
+  </si>
+  <si>
+    <t>Whether it has a date to act by (the date itself is not tracked).</t>
+  </si>
+  <si>
+    <t>The inbound message it comes from.</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>conversations.need_question</t>
+  </si>
+  <si>
+    <t>The question that raised it.</t>
+  </si>
+  <si>
+    <t>conversations.need_reason</t>
+  </si>
+  <si>
+    <t>Why the conversation needs its members.</t>
+  </si>
+  <si>
+    <t>conversations.need_state</t>
+  </si>
+  <si>
+    <t>Open, or cleared.</t>
+  </si>
+  <si>
+    <t>trust</t>
+  </si>
+  <si>
+    <t>conversations.need_trust</t>
+  </si>
+  <si>
+    <t>How much Campbooks stands behind it.</t>
+  </si>
+  <si>
+    <t>urgent</t>
+  </si>
+  <si>
+    <t>Whether it is urgent.</t>
+  </si>
+  <si>
+    <t>verdict</t>
+  </si>
+  <si>
+    <t>conversations.need_verdict</t>
+  </si>
+  <si>
+    <t>A member's verdict on it, if any.</t>
+  </si>
+  <si>
+    <t>actions</t>
+  </si>
+  <si>
+    <t>conversations.rule_action</t>
+  </si>
+  <si>
+    <t>The kinds of its actions (never their values).</t>
+  </si>
+  <si>
+    <t>applied_count</t>
+  </si>
+  <si>
+    <t>How often it acted on arriving mail.</t>
+  </si>
+  <si>
+    <t>condition_count</t>
+  </si>
+  <si>
+    <t>How many conditions it has (never what they match).</t>
+  </si>
+  <si>
+    <t>The rule.</t>
+  </si>
+  <si>
+    <t>The inbox it acts in.</t>
+  </si>
+  <si>
+    <t>origin</t>
+  </si>
+  <si>
+    <t>conversations.rule_origin</t>
+  </si>
+  <si>
+    <t>How it was taught.</t>
+  </si>
+  <si>
+    <t>paused_reason</t>
+  </si>
+  <si>
+    <t>conversations.paused_reason</t>
+  </si>
+  <si>
+    <t>Why it is paused, when it is.</t>
+  </si>
+  <si>
+    <t>conversations.rule_state</t>
+  </si>
+  <si>
+    <t>Its state as readers see it (paused while its author may not act).</t>
+  </si>
+  <si>
+    <t>changed</t>
+  </si>
+  <si>
+    <t>Conversations it changed.</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>Conversations it went through.</t>
+  </si>
+  <si>
+    <t>The run.</t>
+  </si>
+  <si>
+    <t>conversations.run_kind</t>
+  </si>
+  <si>
+    <t>Applying, or putting back.</t>
+  </si>
+  <si>
+    <t>rule_id</t>
+  </si>
+  <si>
+    <t>Its rule.</t>
+  </si>
+  <si>
+    <t>skipped_member</t>
+  </si>
+  <si>
+    <t>Conversations a member had changed, left alone.</t>
+  </si>
+  <si>
+    <t>skipped_suspicious</t>
+  </si>
+  <si>
+    <t>Suspicious mail it left alone.</t>
+  </si>
+  <si>
+    <t>conversations.run_state</t>
+  </si>
+  <si>
+    <t>How it ended.</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>Conversations it matched.</t>
+  </si>
+  <si>
     <t>Value</t>
   </si>
   <si>
+    <t>It was archived.</t>
+  </si>
+  <si>
+    <t>A member said it is done.</t>
+  </si>
+  <si>
+    <t>heard_back</t>
+  </si>
+  <si>
+    <t>The person waited on wrote back.</t>
+  </si>
+  <si>
+    <t>lapsed</t>
+  </si>
+  <si>
+    <t>What it asked lapsed.</t>
+  </si>
+  <si>
+    <t>not_needed</t>
+  </si>
+  <si>
+    <t>A member said it is not needed.</t>
+  </si>
+  <si>
+    <t>opened</t>
+  </si>
+  <si>
+    <t>It was opened (worth a look).</t>
+  </si>
+  <si>
+    <t>replied</t>
+  </si>
+  <si>
+    <t>The inbox replied.</t>
+  </si>
+  <si>
+    <t>A taught rule cleared it.</t>
+  </si>
+  <si>
+    <t>superseded</t>
+  </si>
+  <si>
+    <t>A newer message replaced it.</t>
+  </si>
+  <si>
+    <t>It was binned.</t>
+  </si>
+  <si>
+    <t>Deleted with the inbox.</t>
+  </si>
+  <si>
+    <t>kept</t>
+  </si>
+  <si>
+    <t>Kept read-only.</t>
+  </si>
+  <si>
     <t>No message is in the inbox, and it is not binned.</t>
   </si>
   <si>
-    <t>inbox</t>
-  </si>
-  <si>
     <t>At least one message is in the inbox.</t>
   </si>
   <si>
@@ -392,6 +1508,477 @@
     <t>Every message is in the trash or spam, at least one in the trash.</t>
   </si>
   <si>
+    <t>arrival</t>
+  </si>
+  <si>
+    <t>As the message arrived.</t>
+  </si>
+  <si>
+    <t>backlog</t>
+  </si>
+  <si>
+    <t>For mail stored before.</t>
+  </si>
+  <si>
+    <t>forward</t>
+  </si>
+  <si>
+    <t>A forward.</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>A new message.</t>
+  </si>
+  <si>
+    <t>nudge</t>
+  </si>
+  <si>
+    <t>A nudge to someone the member waits on.</t>
+  </si>
+  <si>
+    <t>reply</t>
+  </si>
+  <si>
+    <t>A reply to the sender.</t>
+  </si>
+  <si>
+    <t>reply_all</t>
+  </si>
+  <si>
+    <t>A reply to everyone.</t>
+  </si>
+  <si>
+    <t>Being written.</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>The provider did not send it.</t>
+  </si>
+  <si>
+    <t>Sent, waiting out its undo window.</t>
+  </si>
+  <si>
+    <t>sending</t>
+  </si>
+  <si>
+    <t>Handed to the connector.</t>
+  </si>
+  <si>
+    <t>The provider sent it (the draft is gone).</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>A member.</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>The model's answer.</t>
+  </si>
+  <si>
+    <t>rules</t>
+  </si>
+  <si>
+    <t>The facts.</t>
+  </si>
+  <si>
+    <t>taught</t>
+  </si>
+  <si>
+    <t>A rule a member taught.</t>
+  </si>
+  <si>
+    <t>asks_action</t>
+  </si>
+  <si>
+    <t>Does it ask for an action?</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>Is money owed?</t>
+  </si>
+  <si>
+    <t>needs_reply</t>
+  </si>
+  <si>
+    <t>Does it need a reply?</t>
+  </si>
+  <si>
+    <t>next_move</t>
+  </si>
+  <si>
+    <t>Whose move is it?</t>
+  </si>
+  <si>
+    <t>still_needs_reply</t>
+  </si>
+  <si>
+    <t>Still needs a reply?</t>
+  </si>
+  <si>
+    <t>still_to_do</t>
+  </si>
+  <si>
+    <t>Still to do?</t>
+  </si>
+  <si>
+    <t>suspicious</t>
+  </si>
+  <si>
+    <t>Is it suspicious?</t>
+  </si>
+  <si>
+    <t>worth_a_look</t>
+  </si>
+  <si>
+    <t>A taught highlight.</t>
+  </si>
+  <si>
+    <t>do</t>
+  </si>
+  <si>
+    <t>Someone asked for something to be done.</t>
+  </si>
+  <si>
+    <t>The wait passed its nudge time.</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>Money is owed.</t>
+  </si>
+  <si>
+    <t>Someone is waiting for an answer.</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>Look before acting: a warning, or a question to the member.</t>
+  </si>
+  <si>
+    <t>waiting</t>
+  </si>
+  <si>
+    <t>Someone else has the next move.</t>
+  </si>
+  <si>
+    <t>A taught rule keeps it in front of the member until opened.</t>
+  </si>
+  <si>
+    <t>cleared</t>
+  </si>
+  <si>
+    <t>It no longer does.</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>It needs the members.</t>
+  </si>
+  <si>
+    <t>check</t>
+  </si>
+  <si>
+    <t>A suggestion put to the member as a question.</t>
+  </si>
+  <si>
+    <t>sure</t>
+  </si>
+  <si>
+    <t>An answer the policy lets act, or a member confirmed.</t>
+  </si>
+  <si>
+    <t>already_paid</t>
+  </si>
+  <si>
+    <t>Already paid.</t>
+  </si>
+  <si>
+    <t>A question answered yes.</t>
+  </si>
+  <si>
+    <t>Done.</t>
+  </si>
+  <si>
+    <t>Not needed.</t>
+  </si>
+  <si>
+    <t>still_to_pay</t>
+  </si>
+  <si>
+    <t>Still to pay.</t>
+  </si>
+  <si>
+    <t>never</t>
+  </si>
+  <si>
+    <t>Never for this sender and kind.</t>
+  </si>
+  <si>
+    <t>not_now</t>
+  </si>
+  <si>
+    <t>Not now: offered again later.</t>
+  </si>
+  <si>
+    <t>archive_on_arrival</t>
+  </si>
+  <si>
+    <t>Archive this sender's mail as it arrives.</t>
+  </si>
+  <si>
+    <t>keep_off_home</t>
+  </si>
+  <si>
+    <t>Keep this sender's mail off Home.</t>
+  </si>
+  <si>
+    <t>author_cannot_write</t>
+  </si>
+  <si>
+    <t>Its author may not change the inbox.</t>
+  </si>
+  <si>
+    <t>author_unavailable</t>
+  </si>
+  <si>
+    <t>Its author is away.</t>
+  </si>
+  <si>
+    <t>domain_too_broad</t>
+  </si>
+  <si>
+    <t>Its domain is too broad to trust.</t>
+  </si>
+  <si>
+    <t>inbox_read_only</t>
+  </si>
+  <si>
+    <t>Its inbox is kept read-only.</t>
+  </si>
+  <si>
+    <t>paused_by_member</t>
+  </si>
+  <si>
+    <t>A member paused it.</t>
+  </si>
+  <si>
+    <t>Scout's read.</t>
+  </si>
+  <si>
+    <t>structured</t>
+  </si>
+  <si>
+    <t>The sender's machine-readable data.</t>
+  </si>
+  <si>
+    <t>Nothing usable came back.</t>
+  </si>
+  <si>
+    <t>Stored a usable read.</t>
+  </si>
+  <si>
+    <t>A need opened on it.</t>
+  </si>
+  <si>
+    <t>A member opened it.</t>
+  </si>
+  <si>
+    <t>add_label</t>
+  </si>
+  <si>
+    <t>Put a label on it.</t>
+  </si>
+  <si>
+    <t>archive</t>
+  </si>
+  <si>
+    <t>Take it out of the inbox.</t>
+  </si>
+  <si>
+    <t>Whether it asks for an action.</t>
+  </si>
+  <si>
+    <t>mark_paid</t>
+  </si>
+  <si>
+    <t>Its bills are paid.</t>
+  </si>
+  <si>
+    <t>mark_read</t>
+  </si>
+  <si>
+    <t>Mark it read.</t>
+  </si>
+  <si>
+    <t>move_to_stream</t>
+  </si>
+  <si>
+    <t>Put it in a stream.</t>
+  </si>
+  <si>
+    <t>Whether it needs a reply.</t>
+  </si>
+  <si>
+    <t>show_images</t>
+  </si>
+  <si>
+    <t>Show its remote images.</t>
+  </si>
+  <si>
+    <t>Report it as spam.</t>
+  </si>
+  <si>
+    <t>surface</t>
+  </si>
+  <si>
+    <t>Always or never show it.</t>
+  </si>
+  <si>
+    <t>Put it in the trash.</t>
+  </si>
+  <si>
+    <t>Keep it in front of the member until opened.</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>From something the member did.</t>
+  </si>
+  <si>
+    <t>correction</t>
+  </si>
+  <si>
+    <t>From a member's correction.</t>
+  </si>
+  <si>
+    <t>instruction</t>
+  </si>
+  <si>
+    <t>From what the member told Scout.</t>
+  </si>
+  <si>
+    <t>onboarding</t>
+  </si>
+  <si>
+    <t>From onboarding.</t>
+  </si>
+  <si>
+    <t>suggestion</t>
+  </si>
+  <si>
+    <t>From a suggestion.</t>
+  </si>
+  <si>
+    <t>A member removed it.</t>
+  </si>
+  <si>
+    <t>replaced</t>
+  </si>
+  <si>
+    <t>Another rule replaced it.</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Acting.</t>
+  </si>
+  <si>
+    <t>paused</t>
+  </si>
+  <si>
+    <t>Not acting for now.</t>
+  </si>
+  <si>
+    <t>proposed</t>
+  </si>
+  <si>
+    <t>Waiting for a member's yes.</t>
+  </si>
+  <si>
+    <t>Removed.</t>
+  </si>
+  <si>
+    <t>apply</t>
+  </si>
+  <si>
+    <t>Applying it to the mail already there.</t>
+  </si>
+  <si>
+    <t>revert</t>
+  </si>
+  <si>
+    <t>Putting back what it changed.</t>
+  </si>
+  <si>
+    <t>cancelled</t>
+  </si>
+  <si>
+    <t>Stopped before the end.</t>
+  </si>
+  <si>
+    <t>running</t>
+  </si>
+  <si>
+    <t>Running.</t>
+  </si>
+  <si>
+    <t>needs_reauth</t>
+  </si>
+  <si>
+    <t>The connection needs signing in again.</t>
+  </si>
+  <si>
+    <t>not_connected</t>
+  </si>
+  <si>
+    <t>The inbox's connection is gone.</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>A reason this plan does not know yet.</t>
+  </si>
+  <si>
+    <t>rejected</t>
+  </si>
+  <si>
+    <t>The provider refused it.</t>
+  </si>
+  <si>
+    <t>too_large</t>
+  </si>
+  <si>
+    <t>Too large for the provider.</t>
+  </si>
+  <si>
+    <t>unavailable</t>
+  </si>
+  <si>
+    <t>The provider could not be reached; nothing was sent.</t>
+  </si>
+  <si>
+    <t>unknown_outcome</t>
+  </si>
+  <si>
+    <t>It may have been sent: no answer came back.</t>
+  </si>
+  <si>
     <t>newsletters</t>
   </si>
   <si>
@@ -422,28 +2009,22 @@
     <t>Nobody: no accepted answer, so Primary.</t>
   </si>
   <si>
-    <t>member</t>
-  </si>
-  <si>
     <t>A member moved it.</t>
   </si>
   <si>
-    <t>model</t>
-  </si>
-  <si>
     <t>An accepted model answer.</t>
   </si>
   <si>
-    <t>rules</t>
-  </si>
-  <si>
     <t>An accepted rules answer.</t>
   </si>
   <si>
-    <t>taught</t>
-  </si>
-  <si>
-    <t>A rule a member taught.</t>
+    <t>The member took it back (Undo).</t>
+  </si>
+  <si>
+    <t>sender_may_not_send</t>
+  </si>
+  <si>
+    <t>Its author may no longer send from the inbox.</t>
   </si>
   <si>
     <t>Actor type</t>
@@ -452,9 +2033,6 @@
     <t>The id is</t>
   </si>
   <si>
-    <t>user</t>
-  </si>
-  <si>
     <t>the person's Campbooks account id</t>
   </si>
   <si>
@@ -485,9 +2063,6 @@
     <t>A rule or workflow, running an operation for a person.</t>
   </si>
   <si>
-    <t>system</t>
-  </si>
-  <si>
     <t>the job, handler or schedule kind, or the command's name</t>
   </si>
   <si>
@@ -524,15 +2099,273 @@
     <t>Exemption</t>
   </si>
   <si>
+    <t>handler</t>
+  </si>
+  <si>
+    <t>conversations.create_inbox</t>
+  </si>
+  <si>
+    <t>conversations.decide_message</t>
+  </si>
+  <si>
+    <t>conversations.forget_connection</t>
+  </si>
+  <si>
+    <t>conversations.forget_member</t>
+  </si>
+  <si>
+    <t>consequence of workspaces.member_left, tracked there: the departed member's own rows go</t>
+  </si>
+  <si>
+    <t>conversations.ingest_messages</t>
+  </si>
+  <si>
+    <t>only enqueues conversations.apply_changes, which tracks</t>
+  </si>
+  <si>
+    <t>conversations.pause_suspended_author</t>
+  </si>
+  <si>
+    <t>projection of workspaces.member_suspended: nothing on the rules changes</t>
+  </si>
+  <si>
+    <t>conversations.record_send</t>
+  </si>
+  <si>
+    <t>conversations.draft_sent, conversations.draft_send_failed</t>
+  </si>
+  <si>
+    <t>conversations.resume_unsuspended_author</t>
+  </si>
+  <si>
+    <t>projection of workspaces.member_unsuspended: nothing on the rules changes</t>
+  </si>
+  <si>
+    <t>conversations.schedule_workspace_purge</t>
+  </si>
+  <si>
+    <t>projection of workspaces.workspace_deleting: it only schedules the purge</t>
+  </si>
+  <si>
+    <t>job</t>
+  </si>
+  <si>
+    <t>conversations.apply_changes</t>
+  </si>
+  <si>
+    <t>conversations.apply_rule</t>
+  </si>
+  <si>
+    <t>conversations.backfill_needs</t>
+  </si>
+  <si>
+    <t>derived state: a need worked out again from stored messages and answers (conversations.need_changed); no action of anyone</t>
+  </si>
+  <si>
+    <t>conversations.check_send</t>
+  </si>
+  <si>
+    <t>conversations.decide_backlog</t>
+  </si>
+  <si>
+    <t>conversations.fill_templates</t>
+  </si>
+  <si>
+    <t>maintenance, no action of anyone: subject templates filled in for older mail</t>
+  </si>
+  <si>
+    <t>conversations.notice_rules</t>
+  </si>
+  <si>
+    <t>derived state: suggestions recounted from recent mail; answering one is tracked</t>
+  </si>
+  <si>
+    <t>conversations.purge_workspace</t>
+  </si>
+  <si>
+    <t>maintenance: a deleted workspace's rows deleted; the deletion is tracked by workspaces</t>
+  </si>
+  <si>
+    <t>conversations.read_message</t>
+  </si>
+  <si>
+    <t>conversations.read_structured</t>
+  </si>
+  <si>
+    <t>conversations.refresh_need</t>
+  </si>
+  <si>
+    <t>conversations.release_send</t>
+  </si>
+  <si>
+    <t>conversations.draft_released, conversations.draft_unscheduled</t>
+  </si>
+  <si>
+    <t>conversations.resign_rules</t>
+  </si>
+  <si>
+    <t>maintenance, no action of anyone: rules that predate bindings signed once</t>
+  </si>
+  <si>
+    <t>conversations.retag_bindings</t>
+  </si>
+  <si>
+    <t>maintenance, no action of anyone: MACs re-tagged after a key rotation</t>
+  </si>
+  <si>
+    <t>conversations.wake_needs</t>
+  </si>
+  <si>
     <t>operation</t>
   </si>
   <si>
+    <t>conversations.add_label</t>
+  </si>
+  <si>
+    <t>conversations.answer_rule_notice</t>
+  </si>
+  <si>
     <t>conversations.archive</t>
   </si>
   <si>
+    <t>conversations.cancel_send</t>
+  </si>
+  <si>
+    <t>conversations.clear_rule_notice_answer</t>
+  </si>
+  <si>
+    <t>conversations.confirm_need</t>
+  </si>
+  <si>
+    <t>conversations.confirm_rule</t>
+  </si>
+  <si>
+    <t>conversations.rule_confirmed, conversations.rule_removed</t>
+  </si>
+  <si>
+    <t>conversations.create_draft</t>
+  </si>
+  <si>
+    <t>conversations.create_rule</t>
+  </si>
+  <si>
+    <t>conversations.rule_created, conversations.rule_removed</t>
+  </si>
+  <si>
+    <t>conversations.decline_rule</t>
+  </si>
+  <si>
+    <t>conversations.delete_draft</t>
+  </si>
+  <si>
+    <t>conversations.delete_person_note</t>
+  </si>
+  <si>
+    <t>conversations.dismiss_rule_suggestion</t>
+  </si>
+  <si>
+    <t>conversations.mark_read</t>
+  </si>
+  <si>
+    <t>conversations.mark_unread</t>
+  </si>
+  <si>
+    <t>conversations.move_to_stream</t>
+  </si>
+  <si>
+    <t>conversations.not_spam</t>
+  </si>
+  <si>
+    <t>conversations.preview_rule</t>
+  </si>
+  <si>
+    <t>read: a preview changes nothing</t>
+  </si>
+  <si>
+    <t>conversations.remove_label</t>
+  </si>
+  <si>
+    <t>conversations.remove_rule</t>
+  </si>
+  <si>
+    <t>conversations.reopen_need</t>
+  </si>
+  <si>
+    <t>conversations.report_spam</t>
+  </si>
+  <si>
+    <t>conversations.request_message_read</t>
+  </si>
+  <si>
+    <t>conversations.resolve_need</t>
+  </si>
+  <si>
+    <t>conversations.restore_rule</t>
+  </si>
+  <si>
+    <t>conversations.rule_restored, conversations.rule_removed</t>
+  </si>
+  <si>
+    <t>conversations.send_draft</t>
+  </si>
+  <si>
+    <t>conversations.set_person_note</t>
+  </si>
+  <si>
+    <t>conversations.star</t>
+  </si>
+  <si>
+    <t>conversations.stream_reply</t>
+  </si>
+  <si>
+    <t>stores nothing: Scout proposes text, and a draft made from it is tracked by conversations.create_draft</t>
+  </si>
+  <si>
+    <t>conversations.suggest_replies</t>
+  </si>
+  <si>
+    <t>conversations.trash</t>
+  </si>
+  <si>
     <t>conversations.unarchive</t>
   </si>
   <si>
+    <t>conversations.unstar</t>
+  </si>
+  <si>
+    <t>conversations.untrash</t>
+  </si>
+  <si>
+    <t>conversations.update_draft</t>
+  </si>
+  <si>
+    <t>conversations.update_rule</t>
+  </si>
+  <si>
+    <t>conversations.rule_updated, conversations.rule_removed</t>
+  </si>
+  <si>
+    <t>conversations.write_nudge</t>
+  </si>
+  <si>
+    <t>conversations.write_reply</t>
+  </si>
+  <si>
+    <t>schedule</t>
+  </si>
+  <si>
+    <t>conversations.dispatch_need_clocks</t>
+  </si>
+  <si>
+    <t>maintenance, no action of anyone: only enqueues the jobs that do the work</t>
+  </si>
+  <si>
+    <t>conversations.dispatch_needs_backfills</t>
+  </si>
+  <si>
+    <t>conversations.dispatch_rule_resigns</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -549,6 +2382,12 @@
   </si>
   <si>
     <t>#632</t>
+  </si>
+  <si>
+    <t>2026-10-24</t>
+  </si>
+  <si>
+    <t>The conversations module instrumented (campbooks-cloud#325): 40 events for flags, streams, labels, needs, drafts and sends, taught rules and their runs, suggestions, person notes, provider batches, the model pass, Scout's reads and inboxes; records draft, need, rule and rule_run; Coverage for every operation, job, schedule and handler of the module.</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +2971,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -1246,23 +3085,1543 @@
         <v>62</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="3">
+        <v>2</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="3">
+        <v>2</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="3">
+        <v>2</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K6" s="3">
+        <v>2</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K7" s="3">
+        <v>2</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K8" s="3">
+        <v>2</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" s="3">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>66</v>
+      <c r="I10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K11" s="3">
+        <v>2</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" s="3">
+        <v>2</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" s="3">
+        <v>2</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K15" s="3">
+        <v>2</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="3">
+        <v>2</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K17" s="3">
+        <v>2</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K18" s="3">
+        <v>2</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K19" s="3">
+        <v>2</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K20" s="3">
+        <v>2</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="K21" s="3">
+        <v>2</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K22" s="3">
+        <v>2</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K23" s="3">
+        <v>2</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="K24" s="3">
+        <v>2</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K25" s="3">
+        <v>2</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K26" s="3">
+        <v>2</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="K27" s="3">
+        <v>2</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="K28" s="3">
+        <v>2</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K29" s="3">
+        <v>2</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K30" s="3">
+        <v>2</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K31" s="3">
+        <v>2</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K32" s="3">
+        <v>2</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" s="3">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="K33" s="3">
+        <v>2</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B34" s="3">
+        <v>1</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K34" s="3">
+        <v>2</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" s="3">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="K35" s="3">
+        <v>2</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B36" s="3">
+        <v>1</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="K36" s="3">
+        <v>2</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B37" s="3">
+        <v>1</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="K37" s="3">
+        <v>2</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B38" s="3">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K38" s="3">
+        <v>2</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" s="3">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="K39" s="3">
+        <v>2</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B40" s="3">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="K40" s="3">
+        <v>2</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="K41" s="3">
+        <v>2</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B42" s="3">
+        <v>1</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="K42" s="3">
+        <v>2</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K43" s="3">
+        <v>2</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L43"/>
   <dataValidations count="12">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Event" prompt="&lt;module&gt;.&lt;object&gt;_&lt;past verb&gt;" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Version" prompt="From 1. A published version never changes meaning." sqref="B2:B2001"/>
@@ -1287,7 +4646,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -1311,31 +4670,31 @@
         <v>46</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>71</v>
+        <v>245</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>72</v>
+        <v>246</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>73</v>
+        <v>247</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>74</v>
+        <v>248</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>75</v>
+        <v>249</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>76</v>
+        <v>250</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>53</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>78</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1349,22 +4708,22 @@
         <v>59</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>83</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1378,26 +4737,2345 @@
         <v>59</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>84</v>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B33" s="3">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="3">
+        <v>1</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" s="3">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" s="3">
+        <v>1</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="3">
+        <v>1</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="3">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" s="3">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" s="3">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B42" s="3">
+        <v>1</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" s="3">
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45" s="3">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="3">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" s="3">
+        <v>1</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B48" s="3">
+        <v>1</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B49" s="3">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B50" s="3">
+        <v>1</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B51" s="3">
+        <v>1</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B52" s="3">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B53" s="3">
+        <v>1</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B54" s="3">
+        <v>1</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B55" s="3">
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" s="3">
+        <v>1</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B57" s="3">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B58" s="3">
+        <v>1</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B59" s="3">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" s="3">
+        <v>1</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B61" s="3">
+        <v>1</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B62" s="3">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B63" s="3">
+        <v>1</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B64" s="3">
+        <v>1</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" s="3">
+        <v>1</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B66" s="3">
+        <v>1</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B67" s="3">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B68" s="3">
+        <v>1</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B69" s="3">
+        <v>1</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B70" s="3">
+        <v>1</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B71" s="3">
+        <v>1</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B72" s="3">
+        <v>1</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B73" s="3">
+        <v>1</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B74" s="3">
+        <v>1</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B75" s="3">
+        <v>1</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B76" s="3">
+        <v>1</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B77" s="3">
+        <v>1</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B78" s="3">
+        <v>1</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B79" s="3">
+        <v>1</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B80" s="3">
+        <v>1</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B81" s="3">
+        <v>1</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B82" s="3">
+        <v>1</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B83" s="3">
+        <v>1</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B84" s="3">
+        <v>1</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B85" s="3">
+        <v>1</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B86" s="3">
+        <v>1</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B87" s="3">
+        <v>1</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K87"/>
   <dataValidations count="11">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Event" prompt="The event's name." sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Version" prompt="The event's version." sqref="B2:B2001"/>
@@ -1425,7 +7103,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -1441,28 +7119,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
-        <v>85</v>
+        <v>363</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>86</v>
+        <v>364</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>72</v>
+        <v>246</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>73</v>
+        <v>247</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>87</v>
+        <v>365</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>75</v>
+        <v>249</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>76</v>
+        <v>250</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>53</v>
@@ -1470,7 +7148,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>13</v>
@@ -1479,213 +7157,1204 @@
         <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>88</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>89</v>
+        <v>282</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>90</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>91</v>
+        <v>368</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>92</v>
+        <v>369</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>93</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>94</v>
+        <v>287</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>95</v>
+        <v>280</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>96</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>98</v>
+        <v>260</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>99</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>373</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>101</v>
+        <v>272</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>102</v>
+        <v>374</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>103</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>104</v>
+        <v>376</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>101</v>
+        <v>272</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>105</v>
+        <v>377</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>106</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>107</v>
+        <v>379</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>101</v>
+        <v>272</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>108</v>
+        <v>380</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>109</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>110</v>
+        <v>382</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>95</v>
+        <v>280</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>111</v>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>465</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I10"/>
+  <autoFilter ref="A1:I51"/>
   <dataValidations count="9">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Record" prompt="&lt;module&gt;.&lt;record&gt;" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Field" prompt="snake_case" sqref="B2:B2001"/>
@@ -1711,7 +8380,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -1721,10 +8390,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>87</v>
+        <v>365</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>112</v>
+        <v>466</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>53</v>
@@ -1732,149 +8401,1293 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>102</v>
+        <v>411</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>113</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>411</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>114</v>
+        <v>451</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>115</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>102</v>
+        <v>411</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>116</v>
+        <v>469</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>117</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>102</v>
+        <v>411</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>118</v>
+        <v>471</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>119</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>105</v>
+        <v>411</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>120</v>
+        <v>473</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>121</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>105</v>
+        <v>411</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>122</v>
+        <v>475</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>123</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>105</v>
+        <v>411</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>124</v>
+        <v>477</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>125</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>105</v>
+        <v>411</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>127</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>108</v>
+        <v>411</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>128</v>
+        <v>480</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>129</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>108</v>
+        <v>411</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>131</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="3" t="s">
-        <v>108</v>
+        <v>285</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>133</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
-        <v>108</v>
+        <v>285</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>134</v>
+        <v>484</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>135</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>374</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>137</v>
+        <v>486</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>664</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C14"/>
+  <autoFilter ref="A1:C118"/>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Enum" prompt="&lt;module&gt;.&lt;enum&gt;" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Value" prompt="snake_case" sqref="B2:B2001"/>
@@ -1896,10 +9709,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>138</v>
+        <v>665</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>139</v>
+        <v>666</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>53</v>
@@ -1907,79 +9720,79 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>141</v>
+        <v>667</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>142</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>143</v>
+        <v>669</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>670</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>145</v>
+        <v>671</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>146</v>
+        <v>672</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>147</v>
+        <v>673</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>148</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>149</v>
+        <v>675</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>147</v>
+        <v>673</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>150</v>
+        <v>676</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>152</v>
+        <v>677</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>153</v>
+        <v>678</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>154</v>
+        <v>679</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>680</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>156</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>157</v>
+        <v>682</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>158</v>
+        <v>683</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>159</v>
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -1995,7 +9808,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2006,42 +9819,735 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>160</v>
+        <v>685</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>161</v>
+        <v>686</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>162</v>
+        <v>687</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>163</v>
+        <v>688</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>164</v>
+        <v>689</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>165</v>
+        <v>690</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>57</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>689</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>166</v>
+        <v>691</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>67</v>
       </c>
     </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>775</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D3"/>
+  <autoFilter ref="A1:D66"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not in the list" error="Pick one of: operation, job, schedule, handler." promptTitle="Kind" prompt="operation, job, schedule or handler" sqref="A2:A2001">
       <formula1>"operation,job,schedule,handler"</formula1>
@@ -2056,7 +10562,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -2066,34 +10572,45 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>167</v>
+        <v>778</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>168</v>
+        <v>779</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>169</v>
+        <v>780</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>170</v>
+        <v>781</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>171</v>
+        <v>782</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>172</v>
+        <v>783</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>785</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D2"/>
+  <autoFilter ref="A1:D3"/>
   <dataValidations count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Date" prompt="YYYY-MM-DD" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Plan version" prompt="From 1, one per change." sqref="B2:B2001"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="787">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -2388,6 +2388,9 @@
   </si>
   <si>
     <t>The conversations module instrumented (campbooks-cloud#325): 40 events for flags, streams, labels, needs, drafts and sends, taught rules and their runs, suggestions, person notes, provider batches, the model pass, Scout's reads and inboxes; records draft, need, rule and rule_run; Coverage for every operation, job, schedule and handler of the module.</t>
+  </si>
+  <si>
+    <t>#650</t>
   </si>
 </sst>
 </file>
@@ -10608,6 +10611,9 @@
       <c r="C3" s="3" t="s">
         <v>785</v>
       </c>
+      <c r="D3" s="3" t="s">
+        <v>786</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D3"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -764,7 +764,7 @@
     <t>A rule was changed: reshaped, paused, resumed or adopted.</t>
   </si>
   <si>
-    <t>The rule is saved (conversations.update_rule).</t>
+    <t>A save changes its conditions, actions, state or author (conversations.update_rule). A save that changes none of them tracks nothing.</t>
   </si>
   <si>
     <t>Property</t>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -18,19 +18,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Actors!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Records!$A$1:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Records!$A$1:$I$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="787">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Plan version</t>
   </si>
   <si>
-    <t>1 (2026-10-23)</t>
+    <t>2 (2026-10-24)</t>
   </si>
   <si>
     <t>What this is</t>
@@ -233,6 +233,84 @@
     <t>add-tracked-events</t>
   </si>
   <si>
+    <t>conversations.conversation_labelled</t>
+  </si>
+  <si>
+    <t>labelled</t>
+  </si>
+  <si>
+    <t>user, client, assistant, automation</t>
+  </si>
+  <si>
+    <t>A label was put on a conversation.</t>
+  </si>
+  <si>
+    <t>Adding the label links it to the conversation (conversations.add_label). A label already on it tracks nothing.</t>
+  </si>
+  <si>
+    <t>track-conversations-events</t>
+  </si>
+  <si>
+    <t>conversations.conversation_moved</t>
+  </si>
+  <si>
+    <t>moved</t>
+  </si>
+  <si>
+    <t>A member moved a conversation to another stream.</t>
+  </si>
+  <si>
+    <t>Moving it changes its stream (conversations.move_to_stream); the move is recorded as a correction. A move to the stream it is in tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.conversation_read</t>
+  </si>
+  <si>
+    <t>read</t>
+  </si>
+  <si>
+    <t>A conversation was marked read.</t>
+  </si>
+  <si>
+    <t>Marking it read changes at least one of its messages (conversations.mark_read), in the transaction of that change. A conversation already read tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.conversation_spammed</t>
+  </si>
+  <si>
+    <t>spammed</t>
+  </si>
+  <si>
+    <t>A conversation was reported as spam: out of the inbox, into spam.</t>
+  </si>
+  <si>
+    <t>Reporting it changes at least one of its messages (conversations.report_spam). One already in spam tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.conversation_starred</t>
+  </si>
+  <si>
+    <t>starred</t>
+  </si>
+  <si>
+    <t>A conversation was starred.</t>
+  </si>
+  <si>
+    <t>Starring it stars its newest message (conversations.star). One already starred tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.conversation_trashed</t>
+  </si>
+  <si>
+    <t>trashed</t>
+  </si>
+  <si>
+    <t>A conversation went to the trash.</t>
+  </si>
+  <si>
+    <t>Trashing it changes at least one of its messages (conversations.trash). One already in the trash tracks nothing.</t>
+  </si>
+  <si>
     <t>conversations.conversation_unarchived</t>
   </si>
   <si>
@@ -245,6 +323,450 @@
     <t>Moving it back changes at least one of the conversation's messages (conversations.unarchive, the undo of conversations.archive), in the transaction of that change.</t>
   </si>
   <si>
+    <t>conversations.conversation_unlabelled</t>
+  </si>
+  <si>
+    <t>unlabelled</t>
+  </si>
+  <si>
+    <t>A label was taken off a conversation.</t>
+  </si>
+  <si>
+    <t>Removing the label unlinks it (conversations.remove_label).</t>
+  </si>
+  <si>
+    <t>conversations.conversation_unread_marked</t>
+  </si>
+  <si>
+    <t>unread_marked</t>
+  </si>
+  <si>
+    <t>A conversation was marked unread.</t>
+  </si>
+  <si>
+    <t>Marking it unread changes its newest message (conversations.mark_unread). One already unread tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.conversation_unspammed</t>
+  </si>
+  <si>
+    <t>unspammed</t>
+  </si>
+  <si>
+    <t>A conversation was taken out of spam (Not spam): received mail back in the inbox.</t>
+  </si>
+  <si>
+    <t>Taking it out of spam changes at least one of its messages (conversations.not_spam).</t>
+  </si>
+  <si>
+    <t>conversations.conversation_unstarred</t>
+  </si>
+  <si>
+    <t>unstarred</t>
+  </si>
+  <si>
+    <t>A conversation was unstarred.</t>
+  </si>
+  <si>
+    <t>Unstarring it changes at least one of its messages (conversations.unstar). One with no star tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.conversation_untrashed</t>
+  </si>
+  <si>
+    <t>untrashed</t>
+  </si>
+  <si>
+    <t>A conversation came out of the trash, back where it was.</t>
+  </si>
+  <si>
+    <t>Taking it out of the trash changes at least one of its messages (conversations.untrash).</t>
+  </si>
+  <si>
+    <t>conversations.draft_created</t>
+  </si>
+  <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>created</t>
+  </si>
+  <si>
+    <t>user, client, assistant</t>
+  </si>
+  <si>
+    <t>A draft was started: new, a reply, a reply all, a forward or a nudge.</t>
+  </si>
+  <si>
+    <t>The draft is stored (conversations.create_draft).</t>
+  </si>
+  <si>
+    <t>conversations.draft_discarded</t>
+  </si>
+  <si>
+    <t>discarded</t>
+  </si>
+  <si>
+    <t>A draft was discarded.</t>
+  </si>
+  <si>
+    <t>The draft is deleted (conversations.delete_draft).</t>
+  </si>
+  <si>
+    <t>conversations.draft_released</t>
+  </si>
+  <si>
+    <t>released</t>
+  </si>
+  <si>
+    <t>system</t>
+  </si>
+  <si>
+    <t>A scheduled send was handed to the connector.</t>
+  </si>
+  <si>
+    <t>Its undo window passed and the release marks it sending (conversations.release_send).</t>
+  </si>
+  <si>
+    <t>conversations.draft_scheduled</t>
+  </si>
+  <si>
+    <t>scheduled</t>
+  </si>
+  <si>
+    <t>user, client</t>
+  </si>
+  <si>
+    <t>A member sent a draft: it waits out its undo window.</t>
+  </si>
+  <si>
+    <t>The send is scheduled (conversations.send_draft).</t>
+  </si>
+  <si>
+    <t>conversations.draft_send_failed</t>
+  </si>
+  <si>
+    <t>send_failed</t>
+  </si>
+  <si>
+    <t>A send failed: the draft is editable and sendable again.</t>
+  </si>
+  <si>
+    <t>The connector reports it failed (conversations.record_send), or no report came back in time (conversations.check_send, unknown_outcome).</t>
+  </si>
+  <si>
+    <t>conversations.draft_sent</t>
+  </si>
+  <si>
+    <t>sent</t>
+  </si>
+  <si>
+    <t>The provider sent a draft.</t>
+  </si>
+  <si>
+    <t>The connector reports it sent (conversations.record_send, on connectors.send_completed), before the draft is deleted.</t>
+  </si>
+  <si>
+    <t>conversations.draft_unscheduled</t>
+  </si>
+  <si>
+    <t>unscheduled</t>
+  </si>
+  <si>
+    <t>user, client, system</t>
+  </si>
+  <si>
+    <t>A scheduled send was taken back: a draft again.</t>
+  </si>
+  <si>
+    <t>A member cancels it during its undo window (conversations.cancel_send), or the release finds its author may no longer send from the inbox (conversations.release_send). A draft not scheduled tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.draft_updated</t>
+  </si>
+  <si>
+    <t>updated</t>
+  </si>
+  <si>
+    <t>A draft was saved with a change.</t>
+  </si>
+  <si>
+    <t>A save changes its recipients, subject, text, quoted history, attachments, or makes a failed draft a draft again (conversations.update_draft). A save that changes nothing tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.inbox_closed</t>
+  </si>
+  <si>
+    <t>inbox</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>A removed connection's inbox was deleted with its mail, or kept read-only.</t>
+  </si>
+  <si>
+    <t>The inbox is deleted or frozen (conversations.forget_connection, on connectors.connection_removed). An inbox already gone or frozen tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.inbox_created</t>
+  </si>
+  <si>
+    <t>An inbox was created for a connection that gained the messages capability.</t>
+  </si>
+  <si>
+    <t>The inbox is created (conversations.create_inbox, on connectors.capability_granted). A replay or an inbox already there tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.message_batch_applied</t>
+  </si>
+  <si>
+    <t>message_batch</t>
+  </si>
+  <si>
+    <t>applied</t>
+  </si>
+  <si>
+    <t>A batch of the provider's message changes was applied to an inbox.</t>
+  </si>
+  <si>
+    <t>Applying it adds, changes or removes at least one message (conversations.apply_changes). A batch that changes nothing tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.message_decided</t>
+  </si>
+  <si>
+    <t>message</t>
+  </si>
+  <si>
+    <t>decided</t>
+  </si>
+  <si>
+    <t>The model pass answered the triage questions about an inbound message.</t>
+  </si>
+  <si>
+    <t>Its answers are stored (conversations.decide_message as mail arrives, conversations.decide_backlog for stored mail). A pass that stores nothing (no model, over the daily limit, already answered) tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.message_read_completed</t>
+  </si>
+  <si>
+    <t>message_read</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>A read of a message was stored: the sender's own structured data, or Scout's read.</t>
+  </si>
+  <si>
+    <t>The read is stored (conversations.read_structured, conversations.read_message). Never what it read: counts only.</t>
+  </si>
+  <si>
+    <t>conversations.message_read_requested</t>
+  </si>
+  <si>
+    <t>requested</t>
+  </si>
+  <si>
+    <t>A member opened a message and Scout's read of it was queued.</t>
+  </si>
+  <si>
+    <t>The read is queued (conversations.request_message_read). Anything else it answers (already read, queued, not flagged, unavailable) tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.need_confirmed</t>
+  </si>
+  <si>
+    <t>need</t>
+  </si>
+  <si>
+    <t>confirmed</t>
+  </si>
+  <si>
+    <t>A member answered yes to the question a conversation's need asked.</t>
+  </si>
+  <si>
+    <t>The yes is stored (conversations.confirm_need).</t>
+  </si>
+  <si>
+    <t>conversations.need_reopened</t>
+  </si>
+  <si>
+    <t>reopened</t>
+  </si>
+  <si>
+    <t>A member took back their verdict on a conversation's need (Undo).</t>
+  </si>
+  <si>
+    <t>The verdict is taken back (conversations.reopen_need).</t>
+  </si>
+  <si>
+    <t>conversations.need_resolved</t>
+  </si>
+  <si>
+    <t>resolved</t>
+  </si>
+  <si>
+    <t>A member gave a verdict on what a conversation needs: done, not needed, already paid or still to pay.</t>
+  </si>
+  <si>
+    <t>The verdict is stored (conversations.resolve_need), in the transaction that works the need out again. Still to pay on a need that was no question changes nothing and tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.person_note_deleted</t>
+  </si>
+  <si>
+    <t>person_note</t>
+  </si>
+  <si>
+    <t>deleted</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>A member deleted a note about a person.</t>
+  </si>
+  <si>
+    <t>The note is deleted (conversations.delete_person_note).</t>
+  </si>
+  <si>
+    <t>conversations.person_note_saved</t>
+  </si>
+  <si>
+    <t>saved</t>
+  </si>
+  <si>
+    <t>A member saved what they told Scout about a person.</t>
+  </si>
+  <si>
+    <t>A note is created or its text changed (conversations.set_person_note). The same text again tracks nothing. Never the note, nor whom it is about.</t>
+  </si>
+  <si>
+    <t>conversations.rule_confirmed</t>
+  </si>
+  <si>
+    <t>rule</t>
+  </si>
+  <si>
+    <t>A member said yes to a rule: it acts with their rights.</t>
+  </si>
+  <si>
+    <t>A proposal is kept, or a kept rule is bound again (conversations.confirm_rule).</t>
+  </si>
+  <si>
+    <t>conversations.rule_created</t>
+  </si>
+  <si>
+    <t>A taught rule was stored: acting, or proposed for a member's yes.</t>
+  </si>
+  <si>
+    <t>The rule is stored (conversations.create_rule).</t>
+  </si>
+  <si>
+    <t>conversations.rule_declined</t>
+  </si>
+  <si>
+    <t>declined</t>
+  </si>
+  <si>
+    <t>A member turned a proposed rule down.</t>
+  </si>
+  <si>
+    <t>The proposal is removed (conversations.decline_rule).</t>
+  </si>
+  <si>
+    <t>conversations.rule_notice_answer_cleared</t>
+  </si>
+  <si>
+    <t>rule_notice</t>
+  </si>
+  <si>
+    <t>answer_cleared</t>
+  </si>
+  <si>
+    <t>A member took back their answer to a suggestion (Undo): it is offered again.</t>
+  </si>
+  <si>
+    <t>An answer is deleted (conversations.clear_rule_notice_answer). No answer to take back tracks nothing.</t>
+  </si>
+  <si>
+    <t>conversations.rule_notice_answered</t>
+  </si>
+  <si>
+    <t>answered</t>
+  </si>
+  <si>
+    <t>A member answered a Scout-noticed suggestion: not now, or never.</t>
+  </si>
+  <si>
+    <t>The answer is stored (conversations.answer_rule_notice).</t>
+  </si>
+  <si>
+    <t>conversations.rule_removed</t>
+  </si>
+  <si>
+    <t>removed</t>
+  </si>
+  <si>
+    <t>A rule was removed.</t>
+  </si>
+  <si>
+    <t>A member removes it (conversations.remove_rule), or a rule created, confirmed, updated or restored replaces it (cause replaced), in that transaction.</t>
+  </si>
+  <si>
+    <t>conversations.rule_restored</t>
+  </si>
+  <si>
+    <t>restored</t>
+  </si>
+  <si>
+    <t>A removed rule was brought back (Undo).</t>
+  </si>
+  <si>
+    <t>The rule is restored (conversations.restore_rule).</t>
+  </si>
+  <si>
+    <t>conversations.rule_run_finished</t>
+  </si>
+  <si>
+    <t>rule_run</t>
+  </si>
+  <si>
+    <t>finished</t>
+  </si>
+  <si>
+    <t>A run applying a rule to an inbox's mail, or putting it back, ended.</t>
+  </si>
+  <si>
+    <t>The run ends, done or cancelled (conversations.apply_rule), in the transaction of its last batch. One event per run, with its counts: a run touches a whole inbox.</t>
+  </si>
+  <si>
+    <t>conversations.rule_suggestion_dismissed</t>
+  </si>
+  <si>
+    <t>rule_suggestion</t>
+  </si>
+  <si>
+    <t>dismissed</t>
+  </si>
+  <si>
+    <t>A member turned down the rules suggested after acting on a conversation.</t>
+  </si>
+  <si>
+    <t>The dismissal is stored (conversations.dismiss_rule_suggestion). Only a member's own dismissal is stored.</t>
+  </si>
+  <si>
+    <t>conversations.rule_updated</t>
+  </si>
+  <si>
+    <t>A rule was changed: reshaped, paused, resumed or adopted.</t>
+  </si>
+  <si>
+    <t>A save changes its conditions, actions, state or author (conversations.update_rule). A save that changes none of them tracks nothing.</t>
+  </si>
+  <si>
     <t>Property</t>
   </si>
   <si>
@@ -284,9 +806,321 @@
     <t>The conversation after archiving.</t>
   </si>
   <si>
+    <t>The conversation afterwards.</t>
+  </si>
+  <si>
+    <t>label_created</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>Whether the inbox's label was created by this request.</t>
+  </si>
+  <si>
+    <t>label_id</t>
+  </si>
+  <si>
+    <t>The label (its name is never tracked).</t>
+  </si>
+  <si>
+    <t>before</t>
+  </si>
+  <si>
+    <t>The conversation before the move: the stream it left and who had placed it there.</t>
+  </si>
+  <si>
     <t>The conversation after it went back to the inbox.</t>
   </si>
   <si>
+    <t>The label.</t>
+  </si>
+  <si>
+    <t>conversations.draft</t>
+  </si>
+  <si>
+    <t>The draft afterwards.</t>
+  </si>
+  <si>
+    <t>The draft as it was when it was discarded.</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>enum</t>
+  </si>
+  <si>
+    <t>conversations.send_error</t>
+  </si>
+  <si>
+    <t>The kind of failure.</t>
+  </si>
+  <si>
+    <t>The draft as it left (state sent).</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>conversations.unschedule_reason</t>
+  </si>
+  <si>
+    <t>Why it was taken back.</t>
+  </si>
+  <si>
+    <t>draft_count</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>Drafts it held.</t>
+  </si>
+  <si>
+    <t>inbox_id</t>
+  </si>
+  <si>
+    <t>The inbox.</t>
+  </si>
+  <si>
+    <t>mail</t>
+  </si>
+  <si>
+    <t>conversations.closed_mail</t>
+  </si>
+  <si>
+    <t>What happened to its mail.</t>
+  </si>
+  <si>
+    <t>message_count</t>
+  </si>
+  <si>
+    <t>Messages it held.</t>
+  </si>
+  <si>
+    <t>connection_id</t>
+  </si>
+  <si>
+    <t>The connection that feeds it.</t>
+  </si>
+  <si>
+    <t>member_added</t>
+  </si>
+  <si>
+    <t>Whether the granting member was added as its manager.</t>
+  </si>
+  <si>
+    <t>backfill</t>
+  </si>
+  <si>
+    <t>Whether it is part of the first import.</t>
+  </si>
+  <si>
+    <t>conversations_changed</t>
+  </si>
+  <si>
+    <t>Conversations the batch created or changed.</t>
+  </si>
+  <si>
+    <t>messages_added</t>
+  </si>
+  <si>
+    <t>Messages stored.</t>
+  </si>
+  <si>
+    <t>messages_removed</t>
+  </si>
+  <si>
+    <t>Messages the provider deleted.</t>
+  </si>
+  <si>
+    <t>messages_updated</t>
+  </si>
+  <si>
+    <t>Known messages whose flags, labels or stream changed.</t>
+  </si>
+  <si>
+    <t>rules_acted</t>
+  </si>
+  <si>
+    <t>Arriving messages a taught rule acted on.</t>
+  </si>
+  <si>
+    <t>answer_count</t>
+  </si>
+  <si>
+    <t>How many answers it stored.</t>
+  </si>
+  <si>
+    <t>Its conversation afterwards.</t>
+  </si>
+  <si>
+    <t>message_id</t>
+  </si>
+  <si>
+    <t>The message.</t>
+  </si>
+  <si>
+    <t>moves_only</t>
+  </si>
+  <si>
+    <t>Whether only whose move it is was asked.</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>conversations.decide_pass</t>
+  </si>
+  <si>
+    <t>Which pass.</t>
+  </si>
+  <si>
+    <t>placed</t>
+  </si>
+  <si>
+    <t>Whether its answer placed the conversation in a stream.</t>
+  </si>
+  <si>
+    <t>ask_count</t>
+  </si>
+  <si>
+    <t>Obligations it found.</t>
+  </si>
+  <si>
+    <t>conversation_id</t>
+  </si>
+  <si>
+    <t>Its conversation.</t>
+  </si>
+  <si>
+    <t>item_count</t>
+  </si>
+  <si>
+    <t>Things that happen at a time it found.</t>
+  </si>
+  <si>
+    <t>layer</t>
+  </si>
+  <si>
+    <t>conversations.read_layer</t>
+  </si>
+  <si>
+    <t>Which read.</t>
+  </si>
+  <si>
+    <t>outcome</t>
+  </si>
+  <si>
+    <t>conversations.read_outcome</t>
+  </si>
+  <si>
+    <t>Whether the read was usable.</t>
+  </si>
+  <si>
+    <t>summary_ready</t>
+  </si>
+  <si>
+    <t>Whether it wrote a summary of the need.</t>
+  </si>
+  <si>
+    <t>trigger</t>
+  </si>
+  <si>
+    <t>conversations.read_trigger</t>
+  </si>
+  <si>
+    <t>What asked for Scout's read; absent for structured data.</t>
+  </si>
+  <si>
+    <t>conversations.need</t>
+  </si>
+  <si>
+    <t>Its need afterwards; absent when it has none.</t>
+  </si>
+  <si>
+    <t>note_id</t>
+  </si>
+  <si>
+    <t>The note.</t>
+  </si>
+  <si>
+    <t>Whether it is a new note.</t>
+  </si>
+  <si>
+    <t>conversations.rule</t>
+  </si>
+  <si>
+    <t>The rule afterwards.</t>
+  </si>
+  <si>
+    <t>acted_without_asking</t>
+  </si>
+  <si>
+    <t>Whether it acts at once because the member lets Campbooks act without asking.</t>
+  </si>
+  <si>
+    <t>Its inbox.</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>conversations.notice_kind</t>
+  </si>
+  <si>
+    <t>What it suggested.</t>
+  </si>
+  <si>
+    <t>notice_id</t>
+  </si>
+  <si>
+    <t>The suggestion.</t>
+  </si>
+  <si>
+    <t>answer</t>
+  </si>
+  <si>
+    <t>conversations.notice_answer</t>
+  </si>
+  <si>
+    <t>The answer.</t>
+  </si>
+  <si>
+    <t>cause</t>
+  </si>
+  <si>
+    <t>conversations.rule_removal_cause</t>
+  </si>
+  <si>
+    <t>Why it was removed.</t>
+  </si>
+  <si>
+    <t>put_back</t>
+  </si>
+  <si>
+    <t>Whether what it changed is being put back.</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>conversations.rule_run</t>
+  </si>
+  <si>
+    <t>The run as it ended.</t>
+  </si>
+  <si>
+    <t>The conversation the suggestion came from.</t>
+  </si>
+  <si>
+    <t>times</t>
+  </si>
+  <si>
+    <t>How many times the member has turned it down.</t>
+  </si>
+  <si>
     <t>Record</t>
   </si>
   <si>
@@ -299,9 +1133,6 @@
     <t>The conversation's id.</t>
   </si>
   <si>
-    <t>inbox_id</t>
-  </si>
-  <si>
     <t>The inbox it belongs to.</t>
   </si>
   <si>
@@ -314,30 +1145,15 @@
     <t>When its newest message was sent: its last activity.</t>
   </si>
   <si>
-    <t>message_count</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>How many messages it holds.</t>
   </si>
   <si>
-    <t>starred</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>Whether any of its messages is starred.</t>
   </si>
   <si>
     <t>status</t>
   </si>
   <si>
-    <t>enum</t>
-  </si>
-  <si>
     <t>conversations.conversation_status</t>
   </si>
   <si>
@@ -368,15 +1184,315 @@
     <t>How many of its inbound messages are unread.</t>
   </si>
   <si>
+    <t>attachment_count</t>
+  </si>
+  <si>
+    <t>How many forwarded attachments.</t>
+  </si>
+  <si>
+    <t>bcc_count</t>
+  </si>
+  <si>
+    <t>How many blind-copied recipients.</t>
+  </si>
+  <si>
+    <t>cc_count</t>
+  </si>
+  <si>
+    <t>How many copied recipients.</t>
+  </si>
+  <si>
+    <t>The conversation it answers, if any.</t>
+  </si>
+  <si>
+    <t>failure</t>
+  </si>
+  <si>
+    <t>Why its last send failed, while it is failed.</t>
+  </si>
+  <si>
+    <t>The draft.</t>
+  </si>
+  <si>
+    <t>The inbox it is sent from.</t>
+  </si>
+  <si>
+    <t>conversations.draft_kind</t>
+  </si>
+  <si>
+    <t>What it answers.</t>
+  </si>
+  <si>
+    <t>The message it replies to or forwards, if any.</t>
+  </si>
+  <si>
+    <t>send_at</t>
+  </si>
+  <si>
+    <t>When a scheduled send leaves.</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>conversations.draft_state</t>
+  </si>
+  <si>
+    <t>Where it is in its life.</t>
+  </si>
+  <si>
+    <t>to_count</t>
+  </si>
+  <si>
+    <t>How many recipients (never who).</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Its save count.</t>
+  </si>
+  <si>
+    <t>basis</t>
+  </si>
+  <si>
+    <t>conversations.need_basis</t>
+  </si>
+  <si>
+    <t>Whose answer raised it.</t>
+  </si>
+  <si>
+    <t>cleared_because</t>
+  </si>
+  <si>
+    <t>conversations.clear_cause</t>
+  </si>
+  <si>
+    <t>Why it was cleared, once cleared.</t>
+  </si>
+  <si>
+    <t>The conversation it belongs to.</t>
+  </si>
+  <si>
+    <t>has_due_date</t>
+  </si>
+  <si>
+    <t>Whether it has a date to act by (the date itself is not tracked).</t>
+  </si>
+  <si>
+    <t>The inbound message it comes from.</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>conversations.need_question</t>
+  </si>
+  <si>
+    <t>The question that raised it.</t>
+  </si>
+  <si>
+    <t>conversations.need_reason</t>
+  </si>
+  <si>
+    <t>Why the conversation needs its members.</t>
+  </si>
+  <si>
+    <t>conversations.need_state</t>
+  </si>
+  <si>
+    <t>Open, or cleared.</t>
+  </si>
+  <si>
+    <t>trust</t>
+  </si>
+  <si>
+    <t>conversations.need_trust</t>
+  </si>
+  <si>
+    <t>How much Campbooks stands behind it.</t>
+  </si>
+  <si>
+    <t>urgent</t>
+  </si>
+  <si>
+    <t>Whether it is urgent.</t>
+  </si>
+  <si>
+    <t>verdict</t>
+  </si>
+  <si>
+    <t>conversations.need_verdict</t>
+  </si>
+  <si>
+    <t>A member's verdict on it, if any.</t>
+  </si>
+  <si>
+    <t>actions</t>
+  </si>
+  <si>
+    <t>conversations.rule_action</t>
+  </si>
+  <si>
+    <t>The kinds of its actions (never their values).</t>
+  </si>
+  <si>
+    <t>applied_count</t>
+  </si>
+  <si>
+    <t>How often it acted on arriving mail.</t>
+  </si>
+  <si>
+    <t>condition_count</t>
+  </si>
+  <si>
+    <t>How many conditions it has (never what they match).</t>
+  </si>
+  <si>
+    <t>The rule.</t>
+  </si>
+  <si>
+    <t>The inbox it acts in.</t>
+  </si>
+  <si>
+    <t>origin</t>
+  </si>
+  <si>
+    <t>conversations.rule_origin</t>
+  </si>
+  <si>
+    <t>How it was taught.</t>
+  </si>
+  <si>
+    <t>paused_reason</t>
+  </si>
+  <si>
+    <t>conversations.paused_reason</t>
+  </si>
+  <si>
+    <t>Why it is paused, when it is.</t>
+  </si>
+  <si>
+    <t>conversations.rule_state</t>
+  </si>
+  <si>
+    <t>Its state as readers see it (paused while its author may not act).</t>
+  </si>
+  <si>
+    <t>changed</t>
+  </si>
+  <si>
+    <t>Conversations it changed.</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>Conversations it went through.</t>
+  </si>
+  <si>
+    <t>The run.</t>
+  </si>
+  <si>
+    <t>conversations.run_kind</t>
+  </si>
+  <si>
+    <t>Applying, or putting back.</t>
+  </si>
+  <si>
+    <t>rule_id</t>
+  </si>
+  <si>
+    <t>Its rule.</t>
+  </si>
+  <si>
+    <t>skipped_member</t>
+  </si>
+  <si>
+    <t>Conversations a member had changed, left alone.</t>
+  </si>
+  <si>
+    <t>skipped_suspicious</t>
+  </si>
+  <si>
+    <t>Suspicious mail it left alone.</t>
+  </si>
+  <si>
+    <t>conversations.run_state</t>
+  </si>
+  <si>
+    <t>How it ended.</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>Conversations it matched.</t>
+  </si>
+  <si>
     <t>Value</t>
   </si>
   <si>
+    <t>It was archived.</t>
+  </si>
+  <si>
+    <t>A member said it is done.</t>
+  </si>
+  <si>
+    <t>heard_back</t>
+  </si>
+  <si>
+    <t>The person waited on wrote back.</t>
+  </si>
+  <si>
+    <t>lapsed</t>
+  </si>
+  <si>
+    <t>What it asked lapsed.</t>
+  </si>
+  <si>
+    <t>not_needed</t>
+  </si>
+  <si>
+    <t>A member said it is not needed.</t>
+  </si>
+  <si>
+    <t>opened</t>
+  </si>
+  <si>
+    <t>It was opened (worth a look).</t>
+  </si>
+  <si>
+    <t>replied</t>
+  </si>
+  <si>
+    <t>The inbox replied.</t>
+  </si>
+  <si>
+    <t>A taught rule cleared it.</t>
+  </si>
+  <si>
+    <t>superseded</t>
+  </si>
+  <si>
+    <t>A newer message replaced it.</t>
+  </si>
+  <si>
+    <t>It was binned.</t>
+  </si>
+  <si>
+    <t>Deleted with the inbox.</t>
+  </si>
+  <si>
+    <t>kept</t>
+  </si>
+  <si>
+    <t>Kept read-only.</t>
+  </si>
+  <si>
     <t>No message is in the inbox, and it is not binned.</t>
   </si>
   <si>
-    <t>inbox</t>
-  </si>
-  <si>
     <t>At least one message is in the inbox.</t>
   </si>
   <si>
@@ -392,6 +1508,477 @@
     <t>Every message is in the trash or spam, at least one in the trash.</t>
   </si>
   <si>
+    <t>arrival</t>
+  </si>
+  <si>
+    <t>As the message arrived.</t>
+  </si>
+  <si>
+    <t>backlog</t>
+  </si>
+  <si>
+    <t>For mail stored before.</t>
+  </si>
+  <si>
+    <t>forward</t>
+  </si>
+  <si>
+    <t>A forward.</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>A new message.</t>
+  </si>
+  <si>
+    <t>nudge</t>
+  </si>
+  <si>
+    <t>A nudge to someone the member waits on.</t>
+  </si>
+  <si>
+    <t>reply</t>
+  </si>
+  <si>
+    <t>A reply to the sender.</t>
+  </si>
+  <si>
+    <t>reply_all</t>
+  </si>
+  <si>
+    <t>A reply to everyone.</t>
+  </si>
+  <si>
+    <t>Being written.</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>The provider did not send it.</t>
+  </si>
+  <si>
+    <t>Sent, waiting out its undo window.</t>
+  </si>
+  <si>
+    <t>sending</t>
+  </si>
+  <si>
+    <t>Handed to the connector.</t>
+  </si>
+  <si>
+    <t>The provider sent it (the draft is gone).</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>A member.</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>The model's answer.</t>
+  </si>
+  <si>
+    <t>rules</t>
+  </si>
+  <si>
+    <t>The facts.</t>
+  </si>
+  <si>
+    <t>taught</t>
+  </si>
+  <si>
+    <t>A rule a member taught.</t>
+  </si>
+  <si>
+    <t>asks_action</t>
+  </si>
+  <si>
+    <t>Does it ask for an action?</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>Is money owed?</t>
+  </si>
+  <si>
+    <t>needs_reply</t>
+  </si>
+  <si>
+    <t>Does it need a reply?</t>
+  </si>
+  <si>
+    <t>next_move</t>
+  </si>
+  <si>
+    <t>Whose move is it?</t>
+  </si>
+  <si>
+    <t>still_needs_reply</t>
+  </si>
+  <si>
+    <t>Still needs a reply?</t>
+  </si>
+  <si>
+    <t>still_to_do</t>
+  </si>
+  <si>
+    <t>Still to do?</t>
+  </si>
+  <si>
+    <t>suspicious</t>
+  </si>
+  <si>
+    <t>Is it suspicious?</t>
+  </si>
+  <si>
+    <t>worth_a_look</t>
+  </si>
+  <si>
+    <t>A taught highlight.</t>
+  </si>
+  <si>
+    <t>do</t>
+  </si>
+  <si>
+    <t>Someone asked for something to be done.</t>
+  </si>
+  <si>
+    <t>The wait passed its nudge time.</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>Money is owed.</t>
+  </si>
+  <si>
+    <t>Someone is waiting for an answer.</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>Look before acting: a warning, or a question to the member.</t>
+  </si>
+  <si>
+    <t>waiting</t>
+  </si>
+  <si>
+    <t>Someone else has the next move.</t>
+  </si>
+  <si>
+    <t>A taught rule keeps it in front of the member until opened.</t>
+  </si>
+  <si>
+    <t>cleared</t>
+  </si>
+  <si>
+    <t>It no longer does.</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>It needs the members.</t>
+  </si>
+  <si>
+    <t>check</t>
+  </si>
+  <si>
+    <t>A suggestion put to the member as a question.</t>
+  </si>
+  <si>
+    <t>sure</t>
+  </si>
+  <si>
+    <t>An answer the policy lets act, or a member confirmed.</t>
+  </si>
+  <si>
+    <t>already_paid</t>
+  </si>
+  <si>
+    <t>Already paid.</t>
+  </si>
+  <si>
+    <t>A question answered yes.</t>
+  </si>
+  <si>
+    <t>Done.</t>
+  </si>
+  <si>
+    <t>Not needed.</t>
+  </si>
+  <si>
+    <t>still_to_pay</t>
+  </si>
+  <si>
+    <t>Still to pay.</t>
+  </si>
+  <si>
+    <t>never</t>
+  </si>
+  <si>
+    <t>Never for this sender and kind.</t>
+  </si>
+  <si>
+    <t>not_now</t>
+  </si>
+  <si>
+    <t>Not now: offered again later.</t>
+  </si>
+  <si>
+    <t>archive_on_arrival</t>
+  </si>
+  <si>
+    <t>Archive this sender's mail as it arrives.</t>
+  </si>
+  <si>
+    <t>keep_off_home</t>
+  </si>
+  <si>
+    <t>Keep this sender's mail off Home.</t>
+  </si>
+  <si>
+    <t>author_cannot_write</t>
+  </si>
+  <si>
+    <t>Its author may not change the inbox.</t>
+  </si>
+  <si>
+    <t>author_unavailable</t>
+  </si>
+  <si>
+    <t>Its author is away.</t>
+  </si>
+  <si>
+    <t>domain_too_broad</t>
+  </si>
+  <si>
+    <t>Its domain is too broad to trust.</t>
+  </si>
+  <si>
+    <t>inbox_read_only</t>
+  </si>
+  <si>
+    <t>Its inbox is kept read-only.</t>
+  </si>
+  <si>
+    <t>paused_by_member</t>
+  </si>
+  <si>
+    <t>A member paused it.</t>
+  </si>
+  <si>
+    <t>Scout's read.</t>
+  </si>
+  <si>
+    <t>structured</t>
+  </si>
+  <si>
+    <t>The sender's machine-readable data.</t>
+  </si>
+  <si>
+    <t>Nothing usable came back.</t>
+  </si>
+  <si>
+    <t>Stored a usable read.</t>
+  </si>
+  <si>
+    <t>A need opened on it.</t>
+  </si>
+  <si>
+    <t>A member opened it.</t>
+  </si>
+  <si>
+    <t>add_label</t>
+  </si>
+  <si>
+    <t>Put a label on it.</t>
+  </si>
+  <si>
+    <t>archive</t>
+  </si>
+  <si>
+    <t>Take it out of the inbox.</t>
+  </si>
+  <si>
+    <t>Whether it asks for an action.</t>
+  </si>
+  <si>
+    <t>mark_paid</t>
+  </si>
+  <si>
+    <t>Its bills are paid.</t>
+  </si>
+  <si>
+    <t>mark_read</t>
+  </si>
+  <si>
+    <t>Mark it read.</t>
+  </si>
+  <si>
+    <t>move_to_stream</t>
+  </si>
+  <si>
+    <t>Put it in a stream.</t>
+  </si>
+  <si>
+    <t>Whether it needs a reply.</t>
+  </si>
+  <si>
+    <t>show_images</t>
+  </si>
+  <si>
+    <t>Show its remote images.</t>
+  </si>
+  <si>
+    <t>Report it as spam.</t>
+  </si>
+  <si>
+    <t>surface</t>
+  </si>
+  <si>
+    <t>Always or never show it.</t>
+  </si>
+  <si>
+    <t>Put it in the trash.</t>
+  </si>
+  <si>
+    <t>Keep it in front of the member until opened.</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>From something the member did.</t>
+  </si>
+  <si>
+    <t>correction</t>
+  </si>
+  <si>
+    <t>From a member's correction.</t>
+  </si>
+  <si>
+    <t>instruction</t>
+  </si>
+  <si>
+    <t>From what the member told Scout.</t>
+  </si>
+  <si>
+    <t>onboarding</t>
+  </si>
+  <si>
+    <t>From onboarding.</t>
+  </si>
+  <si>
+    <t>suggestion</t>
+  </si>
+  <si>
+    <t>From a suggestion.</t>
+  </si>
+  <si>
+    <t>A member removed it.</t>
+  </si>
+  <si>
+    <t>replaced</t>
+  </si>
+  <si>
+    <t>Another rule replaced it.</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Acting.</t>
+  </si>
+  <si>
+    <t>paused</t>
+  </si>
+  <si>
+    <t>Not acting for now.</t>
+  </si>
+  <si>
+    <t>proposed</t>
+  </si>
+  <si>
+    <t>Waiting for a member's yes.</t>
+  </si>
+  <si>
+    <t>Removed.</t>
+  </si>
+  <si>
+    <t>apply</t>
+  </si>
+  <si>
+    <t>Applying it to the mail already there.</t>
+  </si>
+  <si>
+    <t>revert</t>
+  </si>
+  <si>
+    <t>Putting back what it changed.</t>
+  </si>
+  <si>
+    <t>cancelled</t>
+  </si>
+  <si>
+    <t>Stopped before the end.</t>
+  </si>
+  <si>
+    <t>running</t>
+  </si>
+  <si>
+    <t>Running.</t>
+  </si>
+  <si>
+    <t>needs_reauth</t>
+  </si>
+  <si>
+    <t>The connection needs signing in again.</t>
+  </si>
+  <si>
+    <t>not_connected</t>
+  </si>
+  <si>
+    <t>The inbox's connection is gone.</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>A reason this plan does not know yet.</t>
+  </si>
+  <si>
+    <t>rejected</t>
+  </si>
+  <si>
+    <t>The provider refused it.</t>
+  </si>
+  <si>
+    <t>too_large</t>
+  </si>
+  <si>
+    <t>Too large for the provider.</t>
+  </si>
+  <si>
+    <t>unavailable</t>
+  </si>
+  <si>
+    <t>The provider could not be reached; nothing was sent.</t>
+  </si>
+  <si>
+    <t>unknown_outcome</t>
+  </si>
+  <si>
+    <t>It may have been sent: no answer came back.</t>
+  </si>
+  <si>
     <t>newsletters</t>
   </si>
   <si>
@@ -422,28 +2009,22 @@
     <t>Nobody: no accepted answer, so Primary.</t>
   </si>
   <si>
-    <t>member</t>
-  </si>
-  <si>
     <t>A member moved it.</t>
   </si>
   <si>
-    <t>model</t>
-  </si>
-  <si>
     <t>An accepted model answer.</t>
   </si>
   <si>
-    <t>rules</t>
-  </si>
-  <si>
     <t>An accepted rules answer.</t>
   </si>
   <si>
-    <t>taught</t>
-  </si>
-  <si>
-    <t>A rule a member taught.</t>
+    <t>The member took it back (Undo).</t>
+  </si>
+  <si>
+    <t>sender_may_not_send</t>
+  </si>
+  <si>
+    <t>Its author may no longer send from the inbox.</t>
   </si>
   <si>
     <t>Actor type</t>
@@ -452,9 +2033,6 @@
     <t>The id is</t>
   </si>
   <si>
-    <t>user</t>
-  </si>
-  <si>
     <t>the person's Campbooks account id</t>
   </si>
   <si>
@@ -485,9 +2063,6 @@
     <t>A rule or workflow, running an operation for a person.</t>
   </si>
   <si>
-    <t>system</t>
-  </si>
-  <si>
     <t>the job, handler or schedule kind, or the command's name</t>
   </si>
   <si>
@@ -524,15 +2099,273 @@
     <t>Exemption</t>
   </si>
   <si>
+    <t>handler</t>
+  </si>
+  <si>
+    <t>conversations.create_inbox</t>
+  </si>
+  <si>
+    <t>conversations.decide_message</t>
+  </si>
+  <si>
+    <t>conversations.forget_connection</t>
+  </si>
+  <si>
+    <t>conversations.forget_member</t>
+  </si>
+  <si>
+    <t>consequence of workspaces.member_left, tracked there: the departed member's own rows go</t>
+  </si>
+  <si>
+    <t>conversations.ingest_messages</t>
+  </si>
+  <si>
+    <t>only enqueues conversations.apply_changes, which tracks</t>
+  </si>
+  <si>
+    <t>conversations.pause_suspended_author</t>
+  </si>
+  <si>
+    <t>projection of workspaces.member_suspended: nothing on the rules changes</t>
+  </si>
+  <si>
+    <t>conversations.record_send</t>
+  </si>
+  <si>
+    <t>conversations.draft_sent, conversations.draft_send_failed</t>
+  </si>
+  <si>
+    <t>conversations.resume_unsuspended_author</t>
+  </si>
+  <si>
+    <t>projection of workspaces.member_unsuspended: nothing on the rules changes</t>
+  </si>
+  <si>
+    <t>conversations.schedule_workspace_purge</t>
+  </si>
+  <si>
+    <t>projection of workspaces.workspace_deleting: it only schedules the purge</t>
+  </si>
+  <si>
+    <t>job</t>
+  </si>
+  <si>
+    <t>conversations.apply_changes</t>
+  </si>
+  <si>
+    <t>conversations.apply_rule</t>
+  </si>
+  <si>
+    <t>conversations.backfill_needs</t>
+  </si>
+  <si>
+    <t>derived state: a need worked out again from stored messages and answers (conversations.need_changed); no action of anyone</t>
+  </si>
+  <si>
+    <t>conversations.check_send</t>
+  </si>
+  <si>
+    <t>conversations.decide_backlog</t>
+  </si>
+  <si>
+    <t>conversations.fill_templates</t>
+  </si>
+  <si>
+    <t>maintenance, no action of anyone: subject templates filled in for older mail</t>
+  </si>
+  <si>
+    <t>conversations.notice_rules</t>
+  </si>
+  <si>
+    <t>derived state: suggestions recounted from recent mail; answering one is tracked</t>
+  </si>
+  <si>
+    <t>conversations.purge_workspace</t>
+  </si>
+  <si>
+    <t>maintenance: a deleted workspace's rows deleted; the deletion is tracked by workspaces</t>
+  </si>
+  <si>
+    <t>conversations.read_message</t>
+  </si>
+  <si>
+    <t>conversations.read_structured</t>
+  </si>
+  <si>
+    <t>conversations.refresh_need</t>
+  </si>
+  <si>
+    <t>conversations.release_send</t>
+  </si>
+  <si>
+    <t>conversations.draft_released, conversations.draft_unscheduled</t>
+  </si>
+  <si>
+    <t>conversations.resign_rules</t>
+  </si>
+  <si>
+    <t>maintenance, no action of anyone: rules that predate bindings signed once</t>
+  </si>
+  <si>
+    <t>conversations.retag_bindings</t>
+  </si>
+  <si>
+    <t>maintenance, no action of anyone: MACs re-tagged after a key rotation</t>
+  </si>
+  <si>
+    <t>conversations.wake_needs</t>
+  </si>
+  <si>
     <t>operation</t>
   </si>
   <si>
+    <t>conversations.add_label</t>
+  </si>
+  <si>
+    <t>conversations.answer_rule_notice</t>
+  </si>
+  <si>
     <t>conversations.archive</t>
   </si>
   <si>
+    <t>conversations.cancel_send</t>
+  </si>
+  <si>
+    <t>conversations.clear_rule_notice_answer</t>
+  </si>
+  <si>
+    <t>conversations.confirm_need</t>
+  </si>
+  <si>
+    <t>conversations.confirm_rule</t>
+  </si>
+  <si>
+    <t>conversations.rule_confirmed, conversations.rule_removed</t>
+  </si>
+  <si>
+    <t>conversations.create_draft</t>
+  </si>
+  <si>
+    <t>conversations.create_rule</t>
+  </si>
+  <si>
+    <t>conversations.rule_created, conversations.rule_removed</t>
+  </si>
+  <si>
+    <t>conversations.decline_rule</t>
+  </si>
+  <si>
+    <t>conversations.delete_draft</t>
+  </si>
+  <si>
+    <t>conversations.delete_person_note</t>
+  </si>
+  <si>
+    <t>conversations.dismiss_rule_suggestion</t>
+  </si>
+  <si>
+    <t>conversations.mark_read</t>
+  </si>
+  <si>
+    <t>conversations.mark_unread</t>
+  </si>
+  <si>
+    <t>conversations.move_to_stream</t>
+  </si>
+  <si>
+    <t>conversations.not_spam</t>
+  </si>
+  <si>
+    <t>conversations.preview_rule</t>
+  </si>
+  <si>
+    <t>read: a preview changes nothing</t>
+  </si>
+  <si>
+    <t>conversations.remove_label</t>
+  </si>
+  <si>
+    <t>conversations.remove_rule</t>
+  </si>
+  <si>
+    <t>conversations.reopen_need</t>
+  </si>
+  <si>
+    <t>conversations.report_spam</t>
+  </si>
+  <si>
+    <t>conversations.request_message_read</t>
+  </si>
+  <si>
+    <t>conversations.resolve_need</t>
+  </si>
+  <si>
+    <t>conversations.restore_rule</t>
+  </si>
+  <si>
+    <t>conversations.rule_restored, conversations.rule_removed</t>
+  </si>
+  <si>
+    <t>conversations.send_draft</t>
+  </si>
+  <si>
+    <t>conversations.set_person_note</t>
+  </si>
+  <si>
+    <t>conversations.star</t>
+  </si>
+  <si>
+    <t>conversations.stream_reply</t>
+  </si>
+  <si>
+    <t>stores nothing: Scout proposes text, and a draft made from it is tracked by conversations.create_draft</t>
+  </si>
+  <si>
+    <t>conversations.suggest_replies</t>
+  </si>
+  <si>
+    <t>conversations.trash</t>
+  </si>
+  <si>
     <t>conversations.unarchive</t>
   </si>
   <si>
+    <t>conversations.unstar</t>
+  </si>
+  <si>
+    <t>conversations.untrash</t>
+  </si>
+  <si>
+    <t>conversations.update_draft</t>
+  </si>
+  <si>
+    <t>conversations.update_rule</t>
+  </si>
+  <si>
+    <t>conversations.rule_updated, conversations.rule_removed</t>
+  </si>
+  <si>
+    <t>conversations.write_nudge</t>
+  </si>
+  <si>
+    <t>conversations.write_reply</t>
+  </si>
+  <si>
+    <t>schedule</t>
+  </si>
+  <si>
+    <t>conversations.dispatch_need_clocks</t>
+  </si>
+  <si>
+    <t>maintenance, no action of anyone: only enqueues the jobs that do the work</t>
+  </si>
+  <si>
+    <t>conversations.dispatch_needs_backfills</t>
+  </si>
+  <si>
+    <t>conversations.dispatch_rule_resigns</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -549,6 +2382,15 @@
   </si>
   <si>
     <t>#632</t>
+  </si>
+  <si>
+    <t>2026-10-24</t>
+  </si>
+  <si>
+    <t>The conversations module instrumented (campbooks-cloud#325): 40 events for flags, streams, labels, needs, drafts and sends, taught rules and their runs, suggestions, person notes, provider batches, the model pass, Scout's reads and inboxes; records draft, need, rule and rule_run; Coverage for every operation, job, schedule and handler of the module.</t>
+  </si>
+  <si>
+    <t>#650</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +2974,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -1246,23 +3088,1543 @@
         <v>62</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="3">
+        <v>2</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="3">
+        <v>2</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="3">
+        <v>2</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K6" s="3">
+        <v>2</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K7" s="3">
+        <v>2</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K8" s="3">
+        <v>2</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" s="3">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>66</v>
+      <c r="I10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K11" s="3">
+        <v>2</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" s="3">
+        <v>2</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" s="3">
+        <v>2</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K15" s="3">
+        <v>2</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="3">
+        <v>2</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K17" s="3">
+        <v>2</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K18" s="3">
+        <v>2</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K19" s="3">
+        <v>2</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K20" s="3">
+        <v>2</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="K21" s="3">
+        <v>2</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K22" s="3">
+        <v>2</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K23" s="3">
+        <v>2</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="K24" s="3">
+        <v>2</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K25" s="3">
+        <v>2</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K26" s="3">
+        <v>2</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="K27" s="3">
+        <v>2</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="K28" s="3">
+        <v>2</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K29" s="3">
+        <v>2</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K30" s="3">
+        <v>2</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K31" s="3">
+        <v>2</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K32" s="3">
+        <v>2</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" s="3">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="K33" s="3">
+        <v>2</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B34" s="3">
+        <v>1</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K34" s="3">
+        <v>2</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" s="3">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="K35" s="3">
+        <v>2</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B36" s="3">
+        <v>1</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="K36" s="3">
+        <v>2</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B37" s="3">
+        <v>1</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="K37" s="3">
+        <v>2</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B38" s="3">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K38" s="3">
+        <v>2</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" s="3">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="K39" s="3">
+        <v>2</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B40" s="3">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="K40" s="3">
+        <v>2</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="K41" s="3">
+        <v>2</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B42" s="3">
+        <v>1</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="K42" s="3">
+        <v>2</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K43" s="3">
+        <v>2</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L43"/>
   <dataValidations count="12">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Event" prompt="&lt;module&gt;.&lt;object&gt;_&lt;past verb&gt;" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Version" prompt="From 1. A published version never changes meaning." sqref="B2:B2001"/>
@@ -1287,7 +4649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -1311,31 +4673,31 @@
         <v>46</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>71</v>
+        <v>245</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>72</v>
+        <v>246</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>73</v>
+        <v>247</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>74</v>
+        <v>248</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>75</v>
+        <v>249</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>76</v>
+        <v>250</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>53</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>78</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1349,22 +4711,22 @@
         <v>59</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>83</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1378,26 +4740,2345 @@
         <v>59</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>84</v>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B33" s="3">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="3">
+        <v>1</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" s="3">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" s="3">
+        <v>1</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="3">
+        <v>1</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="3">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" s="3">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" s="3">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B42" s="3">
+        <v>1</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" s="3">
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45" s="3">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="3">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" s="3">
+        <v>1</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B48" s="3">
+        <v>1</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B49" s="3">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B50" s="3">
+        <v>1</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B51" s="3">
+        <v>1</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B52" s="3">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B53" s="3">
+        <v>1</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B54" s="3">
+        <v>1</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B55" s="3">
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" s="3">
+        <v>1</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B57" s="3">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B58" s="3">
+        <v>1</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B59" s="3">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" s="3">
+        <v>1</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B61" s="3">
+        <v>1</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B62" s="3">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B63" s="3">
+        <v>1</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B64" s="3">
+        <v>1</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" s="3">
+        <v>1</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B66" s="3">
+        <v>1</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B67" s="3">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B68" s="3">
+        <v>1</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B69" s="3">
+        <v>1</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B70" s="3">
+        <v>1</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B71" s="3">
+        <v>1</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B72" s="3">
+        <v>1</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B73" s="3">
+        <v>1</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B74" s="3">
+        <v>1</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B75" s="3">
+        <v>1</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B76" s="3">
+        <v>1</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B77" s="3">
+        <v>1</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B78" s="3">
+        <v>1</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B79" s="3">
+        <v>1</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B80" s="3">
+        <v>1</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B81" s="3">
+        <v>1</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B82" s="3">
+        <v>1</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B83" s="3">
+        <v>1</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B84" s="3">
+        <v>1</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B85" s="3">
+        <v>1</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B86" s="3">
+        <v>1</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B87" s="3">
+        <v>1</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K87"/>
   <dataValidations count="11">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Event" prompt="The event's name." sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Version" prompt="The event's version." sqref="B2:B2001"/>
@@ -1425,7 +7106,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -1441,28 +7122,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
-        <v>85</v>
+        <v>363</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>86</v>
+        <v>364</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>72</v>
+        <v>246</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>73</v>
+        <v>247</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>87</v>
+        <v>365</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>75</v>
+        <v>249</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>76</v>
+        <v>250</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>53</v>
@@ -1470,7 +7151,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>13</v>
@@ -1479,213 +7160,1204 @@
         <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>88</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>89</v>
+        <v>282</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>90</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>91</v>
+        <v>368</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>92</v>
+        <v>369</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>93</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>94</v>
+        <v>287</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>95</v>
+        <v>280</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>96</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>98</v>
+        <v>260</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>99</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>373</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>101</v>
+        <v>272</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>102</v>
+        <v>374</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>103</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>104</v>
+        <v>376</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>101</v>
+        <v>272</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>105</v>
+        <v>377</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>106</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>107</v>
+        <v>379</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>101</v>
+        <v>272</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>108</v>
+        <v>380</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>109</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>110</v>
+        <v>382</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>95</v>
+        <v>280</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>111</v>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>465</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I10"/>
+  <autoFilter ref="A1:I51"/>
   <dataValidations count="9">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Record" prompt="&lt;module&gt;.&lt;record&gt;" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Field" prompt="snake_case" sqref="B2:B2001"/>
@@ -1711,7 +8383,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -1721,10 +8393,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>87</v>
+        <v>365</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>112</v>
+        <v>466</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>53</v>
@@ -1732,149 +8404,1293 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>102</v>
+        <v>411</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>113</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>411</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>114</v>
+        <v>451</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>115</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>102</v>
+        <v>411</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>116</v>
+        <v>469</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>117</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>102</v>
+        <v>411</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>118</v>
+        <v>471</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>119</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>105</v>
+        <v>411</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>120</v>
+        <v>473</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>121</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>105</v>
+        <v>411</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>122</v>
+        <v>475</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>123</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>105</v>
+        <v>411</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>124</v>
+        <v>477</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>125</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>105</v>
+        <v>411</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>127</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>108</v>
+        <v>411</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>128</v>
+        <v>480</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>129</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>108</v>
+        <v>411</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>131</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="3" t="s">
-        <v>108</v>
+        <v>285</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>133</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
-        <v>108</v>
+        <v>285</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>134</v>
+        <v>484</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>135</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>374</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>137</v>
+        <v>486</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>664</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C14"/>
+  <autoFilter ref="A1:C118"/>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Enum" prompt="&lt;module&gt;.&lt;enum&gt;" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Value" prompt="snake_case" sqref="B2:B2001"/>
@@ -1896,10 +9712,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>138</v>
+        <v>665</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>139</v>
+        <v>666</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>53</v>
@@ -1907,79 +9723,79 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>141</v>
+        <v>667</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>142</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>143</v>
+        <v>669</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>670</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>145</v>
+        <v>671</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>146</v>
+        <v>672</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>147</v>
+        <v>673</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>148</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>149</v>
+        <v>675</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>147</v>
+        <v>673</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>150</v>
+        <v>676</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>152</v>
+        <v>677</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>153</v>
+        <v>678</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>154</v>
+        <v>679</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>680</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>156</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>157</v>
+        <v>682</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>158</v>
+        <v>683</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>159</v>
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -1995,7 +9811,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2006,42 +9822,735 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>160</v>
+        <v>685</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>161</v>
+        <v>686</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>162</v>
+        <v>687</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>163</v>
+        <v>688</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>164</v>
+        <v>689</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>165</v>
+        <v>690</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>57</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>689</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>166</v>
+        <v>691</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>67</v>
       </c>
     </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>775</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D3"/>
+  <autoFilter ref="A1:D66"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not in the list" error="Pick one of: operation, job, schedule, handler." promptTitle="Kind" prompt="operation, job, schedule or handler" sqref="A2:A2001">
       <formula1>"operation,job,schedule,handler"</formula1>
@@ -2056,7 +10565,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -2066,34 +10575,48 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>167</v>
+        <v>778</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>168</v>
+        <v>779</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>169</v>
+        <v>780</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>170</v>
+        <v>781</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>171</v>
+        <v>782</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>172</v>
+        <v>783</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>786</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D2"/>
+  <autoFilter ref="A1:D3"/>
   <dataValidations count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Date" prompt="YYYY-MM-DD" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Plan version" prompt="From 1, one per change." sqref="B2:B2001"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="1142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3350" uniqueCount="1143">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -3456,6 +3456,9 @@
   </si>
   <si>
     <t>The identity module instrumented (campbooks-cloud#326): 27 events for sign-ins succeeded and refused, accounts created, sessions ended, ways in and passkeys added and removed, suspensions, workspace and registered apps, consents, held mailbox grants, and token exchanges, reuse and revocation; records account, session, way_in, passkey, client and consent; Coverage for every operation, handler and schedule of the module.</t>
+  </si>
+  <si>
+    <t>#654</t>
   </si>
 </sst>
 </file>
@@ -16171,6 +16174,9 @@
       <c r="C4" s="3" t="s">
         <v>1141</v>
       </c>
+      <c r="D4" s="3" t="s">
+        <v>1142</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D4"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -2957,7 +2957,7 @@
     <t>A person, through one of Campbooks' apps or an app they allowed.</t>
   </si>
   <si>
-    <t>the OAuth client id</t>
+    <t>the OAuth client id when Campbooks minted it (campbooks-web, campbooks-native, cb_…, dcr_…); none for any other client (one known by its metadata document has a URL for an id)</t>
   </si>
   <si>
     <t>An app acting on its own behalf (client credentials).</t>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3524" uniqueCount="1207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3525" uniqueCount="1208">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -3651,6 +3651,9 @@
   </si>
   <si>
     <t>The web BFF instrumented (campbooks-cloud#327): 3 events for web sessions started, ended one at a time (logging out, signing in again, a copied cookie, outdated scopes, a refused refresh, unreadable tokens, an expired access token) and ended at once (back-channel logout, signing out everywhere, a suspension); the enums of how they end; Coverage for every operation, handler and schedule of the BFF. bff is a platform module, generated into the kernel and tracked from the server.</t>
+  </si>
+  <si>
+    <t>#655</t>
   </si>
 </sst>
 </file>
@@ -17016,6 +17019,9 @@
       <c r="C5" s="3" t="s">
         <v>1206</v>
       </c>
+      <c r="D5" s="3" t="s">
+        <v>1207</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D5"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4233" uniqueCount="1409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4234" uniqueCount="1410">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -4257,6 +4257,9 @@
   </si>
   <si>
     <t>The workspaces module instrumented (campbooks-cloud#328): 16 events for workspaces created, updated, deleted and purged, members joined, role changed, left, suspended and unsuspended, invitations created, signup requests filed, approved and rejected, and signup codes minted, revoked and redeemed; records workspace, member, invitation, signup_request and signup_code; Coverage for every operation, handler and job of the module; the conversations and identity exemptions name workspaces.workspace_deleted.</t>
+  </si>
+  <si>
+    <t>#657</t>
   </si>
 </sst>
 </file>
@@ -20151,6 +20154,9 @@
       <c r="C6" s="3" t="s">
         <v>1408</v>
       </c>
+      <c r="D6" s="3" t="s">
+        <v>1409</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D6"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -1238,7 +1238,7 @@
     <t>A member's account was suspended: whatever acts in their name in the workspace stops until it is lifted. Tracked in each workspace they belong to.</t>
   </si>
   <si>
-    <t>workspaces.announce_member_suspended announces identity.account_suspended in the workspace, in the transaction that publishes workspaces.member_suspended there; a replay of the change announced already, or an older change, tracks nothing.</t>
+    <t>workspaces.announce_member_suspended announces identity.account_suspended in the workspace, in the transaction that publishes workspaces.member_suspended there; a change that leaves them as they were (a replay, an older change, a second suspension with no lift between) tracks nothing.</t>
   </si>
   <si>
     <t>workspaces.member_unsuspended</t>
@@ -1247,7 +1247,7 @@
     <t>A member's suspension was lifted. Tracked in each workspace they belong to.</t>
   </si>
   <si>
-    <t>workspaces.announce_member_unsuspended announces identity.account_unsuspended in the workspace, likewise; a replay or an older change tracks nothing.</t>
+    <t>workspaces.announce_member_unsuspended announces identity.account_unsuspended in the workspace, likewise; a lift that leaves them as they were (a replay, an older change) tracks nothing.</t>
   </si>
   <si>
     <t>workspaces.signup_code_minted</t>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5010" uniqueCount="1659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5011" uniqueCount="1660">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -5007,6 +5007,9 @@
   </si>
   <si>
     <t>The connectors module instrumented (campbooks-cloud#329): 10 events for connections added, reconnected, removed, their health changed and a sync asked for, sync runs (one summary per run, with counts), the outbound changes a run made (counts by end), calendar changes completed, and sends succeeded or failed; records connection, stream and send; Coverage for every operation, job, schedule and handler of the module; the identity operations that hand it a grant name the connection events.</t>
+  </si>
+  <si>
+    <t>#659</t>
   </si>
 </sst>
 </file>
@@ -23689,6 +23692,9 @@
       <c r="C7" s="3" t="s">
         <v>1658</v>
       </c>
+      <c r="D7" s="3" t="s">
+        <v>1659</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6018" uniqueCount="2013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6019" uniqueCount="2014">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -6069,6 +6069,9 @@
   </si>
   <si>
     <t>The assistant, attention, search and system modules instrumented (campbooks-cloud#330): 15 events for chats with Scout started, continued, answered and deleted, its proposals confirmed, declined and undone, a member's profile updated, an item snoozed and unsnoozed, a workspace's daily AI limit reached, and (the kernel's queue, from the system admin actions) a dead job retried or discarded, a kind's dead jobs retried and a schedule's stuck run discarded; records chat, answer, proposal, profile, item and job; Coverage for every operation, job, schedule and handler of the four modules (search and the telemetry reports exempt).</t>
+  </si>
+  <si>
+    <t>#661</t>
   </si>
 </sst>
 </file>
@@ -28354,6 +28357,9 @@
       <c r="C8" s="3" t="s">
         <v>2012</v>
       </c>
+      <c r="D8" s="3" t="s">
+        <v>2013</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D8"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$181</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$333</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$114</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$243</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Records!$A$1:$I$189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6019" uniqueCount="2014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6011" uniqueCount="2014">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -2609,940 +2609,940 @@
     <t>Calls of the cap kept for what people ask, which background work may not use.</t>
   </si>
   <si>
+    <t>workspaces.invitation</t>
+  </si>
+  <si>
+    <t>The new invitation.</t>
+  </si>
+  <si>
+    <t>replaced</t>
+  </si>
+  <si>
+    <t>The pending invitations to the same address it replaced (deleted), by id; usually none.</t>
+  </si>
+  <si>
+    <t>The invitation they accepted, when they joined by one.</t>
+  </si>
+  <si>
+    <t>workspaces.member</t>
+  </si>
+  <si>
+    <t>The new member.</t>
+  </si>
+  <si>
+    <t>via</t>
+  </si>
+  <si>
+    <t>workspaces.joined_via</t>
+  </si>
+  <si>
+    <t>How they joined.</t>
+  </si>
+  <si>
+    <t>how</t>
+  </si>
+  <si>
+    <t>workspaces.departure</t>
+  </si>
+  <si>
+    <t>Whether they left or were removed.</t>
+  </si>
+  <si>
+    <t>workspaces.mail_choice</t>
+  </si>
+  <si>
+    <t>What becomes of the mail of the mailboxes they connected.</t>
+  </si>
+  <si>
+    <t>The membership as it stood when it ended.</t>
+  </si>
+  <si>
+    <t>workspaces.role</t>
+  </si>
+  <si>
+    <t>The role they had.</t>
+  </si>
+  <si>
+    <t>The member with their new role.</t>
+  </si>
+  <si>
+    <t>The member, suspended.</t>
+  </si>
+  <si>
+    <t>The member, no longer suspended.</t>
+  </si>
+  <si>
+    <t>workspaces.signup_code</t>
+  </si>
+  <si>
+    <t>The new code, without the code itself or its label.</t>
+  </si>
+  <si>
+    <t>The code after the use was spent.</t>
+  </si>
+  <si>
+    <t>The code, revoked.</t>
+  </si>
+  <si>
+    <t>workspaces.signup_request_status</t>
+  </si>
+  <si>
+    <t>Where it stood before.</t>
+  </si>
+  <si>
+    <t>workspaces.signup_request</t>
+  </si>
+  <si>
+    <t>The request, approved.</t>
+  </si>
+  <si>
+    <t>The new request.</t>
+  </si>
+  <si>
+    <t>The request, rejected.</t>
+  </si>
+  <si>
+    <t>workspace_snapshot</t>
+  </si>
+  <si>
+    <t>workspaces.workspace</t>
+  </si>
+  <si>
+    <t>The new workspace.</t>
+  </si>
+  <si>
+    <t>The workspace, deleted.</t>
+  </si>
+  <si>
+    <t>The workspace as it stood when purged.</t>
+  </si>
+  <si>
+    <t>workspaces.workspace_setting</t>
+  </si>
+  <si>
+    <t>The workspace afterwards.</t>
+  </si>
+  <si>
+    <t>Record</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Enum</t>
+  </si>
+  <si>
+    <t>chat_id</t>
+  </si>
+  <si>
+    <t>The chat it is in.</t>
+  </si>
+  <si>
+    <t>assistant.answer_failure</t>
+  </si>
+  <si>
+    <t>Why it failed, when it did and the kind is known.</t>
+  </si>
+  <si>
+    <t>finish</t>
+  </si>
+  <si>
+    <t>assistant.answer_finish</t>
+  </si>
+  <si>
+    <t>The answer's id (its message).</t>
+  </si>
+  <si>
+    <t>proposals</t>
+  </si>
+  <si>
+    <t>How many proposals it holds.</t>
+  </si>
+  <si>
+    <t>tools</t>
+  </si>
+  <si>
+    <t>assistant.chat_tool</t>
+  </si>
+  <si>
+    <t>The tools Scout used to answer, in order.</t>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>record_ref</t>
+  </si>
+  <si>
+    <t>The record it is about (a conversation, a task, a rule, a calendar event), by reference; none for a chat about nothing in particular.</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>When it was started.</t>
+  </si>
+  <si>
+    <t>The chat's id.</t>
+  </si>
+  <si>
+    <t>last_message_at</t>
+  </si>
+  <si>
+    <t>When its last message was written.</t>
+  </si>
+  <si>
+    <t>questions</t>
+  </si>
+  <si>
+    <t>How many questions it holds.</t>
+  </si>
+  <si>
+    <t>asked</t>
+  </si>
+  <si>
+    <t>Whether the member answered or put off the questions.</t>
+  </si>
+  <si>
+    <t>asked_at</t>
+  </si>
+  <si>
+    <t>When they first did.</t>
+  </si>
+  <si>
+    <t>proactivity</t>
+  </si>
+  <si>
+    <t>assistant.proactivity</t>
+  </si>
+  <si>
+    <t>How rules Scout proposes from the member's corrections start.</t>
+  </si>
+  <si>
+    <t>revision</t>
+  </si>
+  <si>
+    <t>Grows by one on every save.</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>The member: their user id.</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>assistant.proposal_action</t>
+  </si>
+  <si>
+    <t>The change it names (a change only).</t>
+  </si>
+  <si>
+    <t>The chat it was made in.</t>
+  </si>
+  <si>
+    <t>The proposal's id.</t>
+  </si>
+  <si>
+    <t>assistant.proposal_kind</t>
+  </si>
+  <si>
+    <t>What kind of thing Scout proposed.</t>
+  </si>
+  <si>
+    <t>The conversation, task or event it is about, by reference.</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>assistant.proposal_state</t>
+  </si>
+  <si>
+    <t>Where it stands.</t>
+  </si>
+  <si>
+    <t>due_on</t>
+  </si>
+  <si>
+    <t>When it is due.</t>
+  </si>
+  <si>
+    <t>The item's id.</t>
+  </si>
+  <si>
+    <t>attention.reason</t>
+  </si>
+  <si>
+    <t>Why it needs someone.</t>
+  </si>
+  <si>
+    <t>The record it is about (a conversation, a task), by reference.</t>
+  </si>
+  <si>
+    <t>since</t>
+  </si>
+  <si>
+    <t>When its cause arrived.</t>
+  </si>
+  <si>
+    <t>snoozed_until</t>
+  </si>
+  <si>
+    <t>Until when the acting member put it off, when they did.</t>
+  </si>
+  <si>
+    <t>attention.item_state</t>
+  </si>
+  <si>
+    <t>Whether it still needs someone.</t>
+  </si>
+  <si>
+    <t>trust</t>
+  </si>
+  <si>
+    <t>attention.trust</t>
+  </si>
+  <si>
+    <t>How much the producing module stands behind it.</t>
+  </si>
+  <si>
+    <t>urgent</t>
+  </si>
+  <si>
+    <t>Whether it is for today.</t>
+  </si>
+  <si>
+    <t>address_verified</t>
+  </si>
+  <si>
+    <t>Whether the provider verified the account's address (never the address).</t>
+  </si>
+  <si>
+    <t>capabilities</t>
+  </si>
+  <si>
+    <t>What it lets Campbooks do.</t>
+  </si>
+  <si>
+    <t>When it was connected.</t>
+  </si>
+  <si>
+    <t>granted_by</t>
+  </si>
+  <si>
+    <t>The member who granted it: their user id.</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>How it is doing.</t>
+  </si>
+  <si>
+    <t>health_changed_at</t>
+  </si>
+  <si>
+    <t>Since when it has had this health.</t>
+  </si>
+  <si>
+    <t>health_reason</t>
+  </si>
+  <si>
+    <t>connectors.health_reason</t>
+  </si>
+  <si>
+    <t>Why, when it is not ok.</t>
+  </si>
+  <si>
+    <t>The connection's id.</t>
+  </si>
+  <si>
+    <t>mailboxes</t>
+  </si>
+  <si>
+    <t>Mailboxes it reads: its messages streams.</t>
+  </si>
+  <si>
+    <t>attempts</t>
+  </si>
+  <si>
+    <t>Calls made to the provider.</t>
+  </si>
+  <si>
+    <t>When it was asked for.</t>
+  </si>
+  <si>
+    <t>The send's id (minted by conversations).</t>
+  </si>
+  <si>
+    <t>The inbox it is sent from.</t>
+  </si>
+  <si>
+    <t>The provider it goes through, while the inbox has a connection.</t>
+  </si>
+  <si>
+    <t>sent_copy</t>
+  </si>
+  <si>
+    <t>connectors.sent_copy</t>
+  </si>
+  <si>
+    <t>What becomes of its copy in Sent (IMAP only).</t>
+  </si>
+  <si>
+    <t>connectors.send_state</t>
+  </si>
+  <si>
+    <t>The stream it goes through, while the inbox has one.</t>
+  </si>
+  <si>
+    <t>capability</t>
+  </si>
+  <si>
+    <t>What it reads.</t>
+  </si>
+  <si>
+    <t>The stream's id.</t>
+  </si>
+  <si>
+    <t>The conversations inbox it feeds (messages).</t>
+  </si>
+  <si>
+    <t>last_change_at</t>
+  </si>
+  <si>
+    <t>When a run last found a change.</t>
+  </si>
+  <si>
+    <t>last_synced_at</t>
+  </si>
+  <si>
+    <t>When a run last finished.</t>
+  </si>
+  <si>
+    <t>paused</t>
+  </si>
+  <si>
+    <t>Paused until the member connects again.</t>
+  </si>
+  <si>
+    <t>phase</t>
+  </si>
+  <si>
+    <t>Where it is in its reading.</t>
+  </si>
+  <si>
+    <t>The conversation's id.</t>
+  </si>
+  <si>
+    <t>The inbox it belongs to.</t>
+  </si>
+  <si>
+    <t>When its newest message was sent: its last activity.</t>
+  </si>
+  <si>
+    <t>How many messages it holds.</t>
+  </si>
+  <si>
+    <t>Whether any of its messages is starred.</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>conversations.conversation_status</t>
+  </si>
+  <si>
+    <t>Where it is: the inbox, the archive, the trash or spam.</t>
+  </si>
+  <si>
+    <t>conversations.stream</t>
+  </si>
+  <si>
+    <t>The stream it is in.</t>
+  </si>
+  <si>
+    <t>stream_source</t>
+  </si>
+  <si>
+    <t>conversations.stream_source</t>
+  </si>
+  <si>
+    <t>Who put it in that stream.</t>
+  </si>
+  <si>
+    <t>unread_count</t>
+  </si>
+  <si>
+    <t>How many of its inbound messages are unread.</t>
+  </si>
+  <si>
+    <t>attachment_count</t>
+  </si>
+  <si>
+    <t>How many forwarded attachments.</t>
+  </si>
+  <si>
+    <t>bcc_count</t>
+  </si>
+  <si>
+    <t>How many blind-copied recipients.</t>
+  </si>
+  <si>
+    <t>cc_count</t>
+  </si>
+  <si>
+    <t>How many copied recipients.</t>
+  </si>
+  <si>
+    <t>The conversation it answers, if any.</t>
+  </si>
+  <si>
+    <t>Why its last send failed, while it is failed.</t>
+  </si>
+  <si>
+    <t>The draft.</t>
+  </si>
+  <si>
+    <t>conversations.draft_kind</t>
+  </si>
+  <si>
+    <t>What it answers.</t>
+  </si>
+  <si>
+    <t>The message it replies to or forwards, if any.</t>
+  </si>
+  <si>
+    <t>send_at</t>
+  </si>
+  <si>
+    <t>When a scheduled send leaves.</t>
+  </si>
+  <si>
+    <t>conversations.draft_state</t>
+  </si>
+  <si>
+    <t>Where it is in its life.</t>
+  </si>
+  <si>
+    <t>to_count</t>
+  </si>
+  <si>
+    <t>How many recipients (never who).</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Its save count.</t>
+  </si>
+  <si>
+    <t>basis</t>
+  </si>
+  <si>
+    <t>conversations.need_basis</t>
+  </si>
+  <si>
+    <t>Whose answer raised it.</t>
+  </si>
+  <si>
+    <t>cleared_because</t>
+  </si>
+  <si>
+    <t>conversations.clear_cause</t>
+  </si>
+  <si>
+    <t>Why it was cleared, once cleared.</t>
+  </si>
+  <si>
+    <t>The conversation it belongs to.</t>
+  </si>
+  <si>
+    <t>has_due_date</t>
+  </si>
+  <si>
+    <t>Whether it has a date to act by (the date itself is not tracked).</t>
+  </si>
+  <si>
+    <t>The inbound message it comes from.</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>conversations.need_question</t>
+  </si>
+  <si>
+    <t>The question that raised it.</t>
+  </si>
+  <si>
+    <t>conversations.need_reason</t>
+  </si>
+  <si>
+    <t>Why the conversation needs its members.</t>
+  </si>
+  <si>
+    <t>conversations.need_state</t>
+  </si>
+  <si>
+    <t>Open, or cleared.</t>
+  </si>
+  <si>
+    <t>conversations.need_trust</t>
+  </si>
+  <si>
+    <t>How much Campbooks stands behind it.</t>
+  </si>
+  <si>
+    <t>Whether it is urgent.</t>
+  </si>
+  <si>
+    <t>verdict</t>
+  </si>
+  <si>
+    <t>conversations.need_verdict</t>
+  </si>
+  <si>
+    <t>A member's verdict on it, if any.</t>
+  </si>
+  <si>
+    <t>actions</t>
+  </si>
+  <si>
+    <t>conversations.rule_action</t>
+  </si>
+  <si>
+    <t>The kinds of its actions (never their values).</t>
+  </si>
+  <si>
+    <t>applied_count</t>
+  </si>
+  <si>
+    <t>How often it acted on arriving mail.</t>
+  </si>
+  <si>
+    <t>condition_count</t>
+  </si>
+  <si>
+    <t>How many conditions it has (never what they match).</t>
+  </si>
+  <si>
+    <t>The rule.</t>
+  </si>
+  <si>
+    <t>The inbox it acts in.</t>
+  </si>
+  <si>
+    <t>origin</t>
+  </si>
+  <si>
+    <t>conversations.rule_origin</t>
+  </si>
+  <si>
+    <t>How it was taught.</t>
+  </si>
+  <si>
+    <t>paused_reason</t>
+  </si>
+  <si>
+    <t>conversations.paused_reason</t>
+  </si>
+  <si>
+    <t>Why it is paused, when it is.</t>
+  </si>
+  <si>
+    <t>conversations.rule_state</t>
+  </si>
+  <si>
+    <t>Its state as readers see it (paused while its author may not act).</t>
+  </si>
+  <si>
+    <t>changed</t>
+  </si>
+  <si>
+    <t>Conversations it changed.</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>Conversations it went through.</t>
+  </si>
+  <si>
+    <t>The run.</t>
+  </si>
+  <si>
+    <t>conversations.run_kind</t>
+  </si>
+  <si>
+    <t>Applying, or putting back.</t>
+  </si>
+  <si>
+    <t>rule_id</t>
+  </si>
+  <si>
+    <t>Its rule.</t>
+  </si>
+  <si>
+    <t>skipped_member</t>
+  </si>
+  <si>
+    <t>Conversations a member had changed, left alone.</t>
+  </si>
+  <si>
+    <t>skipped_suspicious</t>
+  </si>
+  <si>
+    <t>Suspicious mail it left alone.</t>
+  </si>
+  <si>
+    <t>conversations.run_state</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>Conversations it matched.</t>
+  </si>
+  <si>
+    <t>When it was created.</t>
+  </si>
+  <si>
+    <t>The account's id.</t>
+  </si>
+  <si>
+    <t>passkeys</t>
+  </si>
+  <si>
+    <t>How many passkeys are ways into it.</t>
+  </si>
+  <si>
+    <t>provider_ways_in</t>
+  </si>
+  <si>
+    <t>How many provider identities are ways into it.</t>
+  </si>
+  <si>
+    <t>Whether an administrator suspended it.</t>
+  </si>
+  <si>
+    <t>Its client id, when Campbooks minted it; absent for a metadata-document client, whose id is a URL.</t>
+  </si>
+  <si>
+    <t>confidential</t>
+  </si>
+  <si>
+    <t>Whether it authenticates with a secret.</t>
+  </si>
+  <si>
+    <t>When it was registered.</t>
+  </si>
+  <si>
+    <t>redirect_uri_count</t>
+  </si>
+  <si>
+    <t>How many redirect URIs it registered (never the URIs).</t>
+  </si>
+  <si>
+    <t>How many scopes it may ask for.</t>
+  </si>
+  <si>
+    <t>secret_rotated_at</t>
+  </si>
+  <si>
+    <t>When its secret was last rotated.</t>
+  </si>
+  <si>
+    <t>The account that gave it.</t>
+  </si>
+  <si>
+    <t>bound_workspace_id</t>
+  </si>
+  <si>
+    <t>The workspace the client may use, when it binds one.</t>
+  </si>
+  <si>
+    <t>The client it lets in, when Campbooks minted its id; absent for a metadata-document client.</t>
+  </si>
+  <si>
+    <t>What kind of client it lets in.</t>
+  </si>
+  <si>
+    <t>granted_at</t>
+  </si>
+  <si>
+    <t>When it was given.</t>
+  </si>
+  <si>
+    <t>The consent's id.</t>
+  </si>
+  <si>
+    <t>remembered</t>
+  </si>
+  <si>
+    <t>Whether a later authorization may skip the screen.</t>
+  </si>
+  <si>
+    <t>revoked_at</t>
+  </si>
+  <si>
+    <t>When it was revoked, if it was.</t>
+  </si>
+  <si>
+    <t>How many scopes it allows (never their names).</t>
+  </si>
+  <si>
+    <t>The account it is a way into.</t>
+  </si>
+  <si>
+    <t>added_via</t>
+  </si>
+  <si>
+    <t>identity.passkey_added_via</t>
+  </si>
+  <si>
+    <t>How it was added.</t>
+  </si>
+  <si>
+    <t>backup_eligible</t>
+  </si>
+  <si>
+    <t>Whether it may be synced (a multi-device passkey).</t>
+  </si>
+  <si>
+    <t>backup_state</t>
+  </si>
+  <si>
+    <t>Whether it is synced now.</t>
+  </si>
+  <si>
+    <t>When it was added.</t>
+  </si>
+  <si>
+    <t>The passkey's id (never its credential id).</t>
+  </si>
+  <si>
+    <t>last_used_at</t>
+  </si>
+  <si>
+    <t>When it was last used to sign in.</t>
+  </si>
+  <si>
+    <t>The account signed in.</t>
+  </si>
+  <si>
+    <t>auth_time</t>
+  </si>
+  <si>
+    <t>When the person authenticated.</t>
+  </si>
+  <si>
+    <t>ended_at</t>
+  </si>
+  <si>
+    <t>When it was ended, if it was.</t>
+  </si>
+  <si>
+    <t>expires_at</t>
+  </si>
+  <si>
+    <t>When it ends at the latest.</t>
+  </si>
+  <si>
+    <t>The issuer session's id.</t>
+  </si>
+  <si>
+    <t>How the person signed in.</t>
+  </si>
+  <si>
+    <t>The provider signed in with, for a provider sign-in whose way in still exists.</t>
+  </si>
+  <si>
+    <t>Whether the provider verified its address when it was linked (the address is never kept).</t>
+  </si>
+  <si>
+    <t>The provider identity's id (never its subject).</t>
+  </si>
+  <si>
+    <t>linked_at</t>
+  </si>
+  <si>
+    <t>When it was linked.</t>
+  </si>
+  <si>
+    <t>linked_via</t>
+  </si>
+  <si>
+    <t>identity.linked_via</t>
+  </si>
+  <si>
+    <t>How it was linked.</t>
+  </si>
+  <si>
+    <t>Its provider.</t>
+  </si>
+  <si>
+    <t>Attempts made.</t>
+  </si>
+  <si>
+    <t>When it was enqueued.</t>
+  </si>
+  <si>
+    <t>The job's id.</t>
+  </si>
+  <si>
+    <t>The job's kind (`&lt;module&gt;.&lt;job&gt;`).</t>
+  </si>
+  <si>
+    <t>max_attempts</t>
+  </si>
+  <si>
+    <t>Attempts it is allowed.</t>
+  </si>
+  <si>
+    <t>The queue it runs on.</t>
+  </si>
+  <si>
+    <t>kernel.job_state</t>
+  </si>
+  <si>
+    <t>workspace_id</t>
+  </si>
+  <si>
+    <t>The workspace it belongs to; none for instance-wide work.</t>
+  </si>
+  <si>
+    <t>accepted_at</t>
+  </si>
+  <si>
+    <t>When it was accepted.</t>
+  </si>
+  <si>
+    <t>accepted_by</t>
+  </si>
+  <si>
+    <t>Who accepted it: their user id.</t>
+  </si>
+  <si>
+    <t>When it was sent.</t>
+  </si>
+  <si>
+    <t>When it stops working.</t>
+  </si>
+  <si>
+    <t>The invitation's id.</t>
+  </si>
+  <si>
+    <t>invited_by</t>
+  </si>
+  <si>
+    <t>Who invited: their user id.</t>
+  </si>
+  <si>
     <t>role</t>
-  </si>
-  <si>
-    <t>workspaces.invitation</t>
-  </si>
-  <si>
-    <t>The new invitation.</t>
-  </si>
-  <si>
-    <t>replaced</t>
-  </si>
-  <si>
-    <t>The pending invitations to the same address it replaced (deleted), by id; usually none.</t>
-  </si>
-  <si>
-    <t>The invitation they accepted, when they joined by one.</t>
-  </si>
-  <si>
-    <t>workspaces.member</t>
-  </si>
-  <si>
-    <t>The new member.</t>
-  </si>
-  <si>
-    <t>via</t>
-  </si>
-  <si>
-    <t>workspaces.joined_via</t>
-  </si>
-  <si>
-    <t>How they joined.</t>
-  </si>
-  <si>
-    <t>how</t>
-  </si>
-  <si>
-    <t>workspaces.departure</t>
-  </si>
-  <si>
-    <t>Whether they left or were removed.</t>
-  </si>
-  <si>
-    <t>workspaces.mail_choice</t>
-  </si>
-  <si>
-    <t>What becomes of the mail of the mailboxes they connected.</t>
-  </si>
-  <si>
-    <t>The membership as it stood when it ended.</t>
-  </si>
-  <si>
-    <t>workspaces.role</t>
-  </si>
-  <si>
-    <t>The role they had.</t>
-  </si>
-  <si>
-    <t>The member with their new role.</t>
-  </si>
-  <si>
-    <t>The member, suspended.</t>
-  </si>
-  <si>
-    <t>The member, no longer suspended.</t>
-  </si>
-  <si>
-    <t>workspaces.signup_code</t>
-  </si>
-  <si>
-    <t>The new code, without the code itself or its label.</t>
-  </si>
-  <si>
-    <t>The code after the use was spent.</t>
-  </si>
-  <si>
-    <t>The code, revoked.</t>
-  </si>
-  <si>
-    <t>workspaces.signup_request_status</t>
-  </si>
-  <si>
-    <t>Where it stood before.</t>
-  </si>
-  <si>
-    <t>workspaces.signup_request</t>
-  </si>
-  <si>
-    <t>The request, approved.</t>
-  </si>
-  <si>
-    <t>The new request.</t>
-  </si>
-  <si>
-    <t>The request, rejected.</t>
-  </si>
-  <si>
-    <t>workspace_snapshot</t>
-  </si>
-  <si>
-    <t>workspaces.workspace</t>
-  </si>
-  <si>
-    <t>The new workspace.</t>
-  </si>
-  <si>
-    <t>The workspace, deleted.</t>
-  </si>
-  <si>
-    <t>The workspace as it stood when purged.</t>
-  </si>
-  <si>
-    <t>workspaces.workspace_setting</t>
-  </si>
-  <si>
-    <t>The workspace afterwards.</t>
-  </si>
-  <si>
-    <t>Record</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Enum</t>
-  </si>
-  <si>
-    <t>chat_id</t>
-  </si>
-  <si>
-    <t>The chat it is in.</t>
-  </si>
-  <si>
-    <t>assistant.answer_failure</t>
-  </si>
-  <si>
-    <t>Why it failed, when it did and the kind is known.</t>
-  </si>
-  <si>
-    <t>finish</t>
-  </si>
-  <si>
-    <t>assistant.answer_finish</t>
-  </si>
-  <si>
-    <t>The answer's id (its message).</t>
-  </si>
-  <si>
-    <t>proposals</t>
-  </si>
-  <si>
-    <t>How many proposals it holds.</t>
-  </si>
-  <si>
-    <t>tools</t>
-  </si>
-  <si>
-    <t>assistant.chat_tool</t>
-  </si>
-  <si>
-    <t>The tools Scout used to answer, in order.</t>
-  </si>
-  <si>
-    <t>about</t>
-  </si>
-  <si>
-    <t>record_ref</t>
-  </si>
-  <si>
-    <t>The record it is about (a conversation, a task, a rule, a calendar event), by reference; none for a chat about nothing in particular.</t>
-  </si>
-  <si>
-    <t>created_at</t>
-  </si>
-  <si>
-    <t>When it was started.</t>
-  </si>
-  <si>
-    <t>The chat's id.</t>
-  </si>
-  <si>
-    <t>last_message_at</t>
-  </si>
-  <si>
-    <t>When its last message was written.</t>
-  </si>
-  <si>
-    <t>questions</t>
-  </si>
-  <si>
-    <t>How many questions it holds.</t>
-  </si>
-  <si>
-    <t>asked</t>
-  </si>
-  <si>
-    <t>Whether the member answered or put off the questions.</t>
-  </si>
-  <si>
-    <t>asked_at</t>
-  </si>
-  <si>
-    <t>When they first did.</t>
-  </si>
-  <si>
-    <t>proactivity</t>
-  </si>
-  <si>
-    <t>assistant.proactivity</t>
-  </si>
-  <si>
-    <t>How rules Scout proposes from the member's corrections start.</t>
-  </si>
-  <si>
-    <t>revision</t>
-  </si>
-  <si>
-    <t>Grows by one on every save.</t>
-  </si>
-  <si>
-    <t>user_id</t>
-  </si>
-  <si>
-    <t>The member: their user id.</t>
-  </si>
-  <si>
-    <t>action</t>
-  </si>
-  <si>
-    <t>assistant.proposal_action</t>
-  </si>
-  <si>
-    <t>The change it names (a change only).</t>
-  </si>
-  <si>
-    <t>The chat it was made in.</t>
-  </si>
-  <si>
-    <t>The proposal's id.</t>
-  </si>
-  <si>
-    <t>assistant.proposal_kind</t>
-  </si>
-  <si>
-    <t>What kind of thing Scout proposed.</t>
-  </si>
-  <si>
-    <t>The conversation, task or event it is about, by reference.</t>
-  </si>
-  <si>
-    <t>state</t>
-  </si>
-  <si>
-    <t>assistant.proposal_state</t>
-  </si>
-  <si>
-    <t>Where it stands.</t>
-  </si>
-  <si>
-    <t>due_on</t>
-  </si>
-  <si>
-    <t>When it is due.</t>
-  </si>
-  <si>
-    <t>The item's id.</t>
-  </si>
-  <si>
-    <t>attention.reason</t>
-  </si>
-  <si>
-    <t>Why it needs someone.</t>
-  </si>
-  <si>
-    <t>The record it is about (a conversation, a task), by reference.</t>
-  </si>
-  <si>
-    <t>since</t>
-  </si>
-  <si>
-    <t>When its cause arrived.</t>
-  </si>
-  <si>
-    <t>snoozed_until</t>
-  </si>
-  <si>
-    <t>Until when the acting member put it off, when they did.</t>
-  </si>
-  <si>
-    <t>attention.item_state</t>
-  </si>
-  <si>
-    <t>Whether it still needs someone.</t>
-  </si>
-  <si>
-    <t>trust</t>
-  </si>
-  <si>
-    <t>attention.trust</t>
-  </si>
-  <si>
-    <t>How much the producing module stands behind it.</t>
-  </si>
-  <si>
-    <t>urgent</t>
-  </si>
-  <si>
-    <t>Whether it is for today.</t>
-  </si>
-  <si>
-    <t>address_verified</t>
-  </si>
-  <si>
-    <t>Whether the provider verified the account's address (never the address).</t>
-  </si>
-  <si>
-    <t>capabilities</t>
-  </si>
-  <si>
-    <t>What it lets Campbooks do.</t>
-  </si>
-  <si>
-    <t>When it was connected.</t>
-  </si>
-  <si>
-    <t>granted_by</t>
-  </si>
-  <si>
-    <t>The member who granted it: their user id.</t>
-  </si>
-  <si>
-    <t>health</t>
-  </si>
-  <si>
-    <t>How it is doing.</t>
-  </si>
-  <si>
-    <t>health_changed_at</t>
-  </si>
-  <si>
-    <t>Since when it has had this health.</t>
-  </si>
-  <si>
-    <t>health_reason</t>
-  </si>
-  <si>
-    <t>connectors.health_reason</t>
-  </si>
-  <si>
-    <t>Why, when it is not ok.</t>
-  </si>
-  <si>
-    <t>The connection's id.</t>
-  </si>
-  <si>
-    <t>mailboxes</t>
-  </si>
-  <si>
-    <t>Mailboxes it reads: its messages streams.</t>
-  </si>
-  <si>
-    <t>attempts</t>
-  </si>
-  <si>
-    <t>Calls made to the provider.</t>
-  </si>
-  <si>
-    <t>When it was asked for.</t>
-  </si>
-  <si>
-    <t>The send's id (minted by conversations).</t>
-  </si>
-  <si>
-    <t>The inbox it is sent from.</t>
-  </si>
-  <si>
-    <t>The provider it goes through, while the inbox has a connection.</t>
-  </si>
-  <si>
-    <t>sent_copy</t>
-  </si>
-  <si>
-    <t>connectors.sent_copy</t>
-  </si>
-  <si>
-    <t>What becomes of its copy in Sent (IMAP only).</t>
-  </si>
-  <si>
-    <t>connectors.send_state</t>
-  </si>
-  <si>
-    <t>The stream it goes through, while the inbox has one.</t>
-  </si>
-  <si>
-    <t>capability</t>
-  </si>
-  <si>
-    <t>What it reads.</t>
-  </si>
-  <si>
-    <t>The stream's id.</t>
-  </si>
-  <si>
-    <t>The conversations inbox it feeds (messages).</t>
-  </si>
-  <si>
-    <t>last_change_at</t>
-  </si>
-  <si>
-    <t>When a run last found a change.</t>
-  </si>
-  <si>
-    <t>last_synced_at</t>
-  </si>
-  <si>
-    <t>When a run last finished.</t>
-  </si>
-  <si>
-    <t>paused</t>
-  </si>
-  <si>
-    <t>Paused until the member connects again.</t>
-  </si>
-  <si>
-    <t>phase</t>
-  </si>
-  <si>
-    <t>Where it is in its reading.</t>
-  </si>
-  <si>
-    <t>The conversation's id.</t>
-  </si>
-  <si>
-    <t>The inbox it belongs to.</t>
-  </si>
-  <si>
-    <t>When its newest message was sent: its last activity.</t>
-  </si>
-  <si>
-    <t>How many messages it holds.</t>
-  </si>
-  <si>
-    <t>Whether any of its messages is starred.</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>conversations.conversation_status</t>
-  </si>
-  <si>
-    <t>Where it is: the inbox, the archive, the trash or spam.</t>
-  </si>
-  <si>
-    <t>conversations.stream</t>
-  </si>
-  <si>
-    <t>The stream it is in.</t>
-  </si>
-  <si>
-    <t>stream_source</t>
-  </si>
-  <si>
-    <t>conversations.stream_source</t>
-  </si>
-  <si>
-    <t>Who put it in that stream.</t>
-  </si>
-  <si>
-    <t>unread_count</t>
-  </si>
-  <si>
-    <t>How many of its inbound messages are unread.</t>
-  </si>
-  <si>
-    <t>attachment_count</t>
-  </si>
-  <si>
-    <t>How many forwarded attachments.</t>
-  </si>
-  <si>
-    <t>bcc_count</t>
-  </si>
-  <si>
-    <t>How many blind-copied recipients.</t>
-  </si>
-  <si>
-    <t>cc_count</t>
-  </si>
-  <si>
-    <t>How many copied recipients.</t>
-  </si>
-  <si>
-    <t>The conversation it answers, if any.</t>
-  </si>
-  <si>
-    <t>Why its last send failed, while it is failed.</t>
-  </si>
-  <si>
-    <t>The draft.</t>
-  </si>
-  <si>
-    <t>conversations.draft_kind</t>
-  </si>
-  <si>
-    <t>What it answers.</t>
-  </si>
-  <si>
-    <t>The message it replies to or forwards, if any.</t>
-  </si>
-  <si>
-    <t>send_at</t>
-  </si>
-  <si>
-    <t>When a scheduled send leaves.</t>
-  </si>
-  <si>
-    <t>conversations.draft_state</t>
-  </si>
-  <si>
-    <t>Where it is in its life.</t>
-  </si>
-  <si>
-    <t>to_count</t>
-  </si>
-  <si>
-    <t>How many recipients (never who).</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>Its save count.</t>
-  </si>
-  <si>
-    <t>basis</t>
-  </si>
-  <si>
-    <t>conversations.need_basis</t>
-  </si>
-  <si>
-    <t>Whose answer raised it.</t>
-  </si>
-  <si>
-    <t>cleared_because</t>
-  </si>
-  <si>
-    <t>conversations.clear_cause</t>
-  </si>
-  <si>
-    <t>Why it was cleared, once cleared.</t>
-  </si>
-  <si>
-    <t>The conversation it belongs to.</t>
-  </si>
-  <si>
-    <t>has_due_date</t>
-  </si>
-  <si>
-    <t>Whether it has a date to act by (the date itself is not tracked).</t>
-  </si>
-  <si>
-    <t>The inbound message it comes from.</t>
-  </si>
-  <si>
-    <t>question</t>
-  </si>
-  <si>
-    <t>conversations.need_question</t>
-  </si>
-  <si>
-    <t>The question that raised it.</t>
-  </si>
-  <si>
-    <t>conversations.need_reason</t>
-  </si>
-  <si>
-    <t>Why the conversation needs its members.</t>
-  </si>
-  <si>
-    <t>conversations.need_state</t>
-  </si>
-  <si>
-    <t>Open, or cleared.</t>
-  </si>
-  <si>
-    <t>conversations.need_trust</t>
-  </si>
-  <si>
-    <t>How much Campbooks stands behind it.</t>
-  </si>
-  <si>
-    <t>Whether it is urgent.</t>
-  </si>
-  <si>
-    <t>verdict</t>
-  </si>
-  <si>
-    <t>conversations.need_verdict</t>
-  </si>
-  <si>
-    <t>A member's verdict on it, if any.</t>
-  </si>
-  <si>
-    <t>actions</t>
-  </si>
-  <si>
-    <t>conversations.rule_action</t>
-  </si>
-  <si>
-    <t>The kinds of its actions (never their values).</t>
-  </si>
-  <si>
-    <t>applied_count</t>
-  </si>
-  <si>
-    <t>How often it acted on arriving mail.</t>
-  </si>
-  <si>
-    <t>condition_count</t>
-  </si>
-  <si>
-    <t>How many conditions it has (never what they match).</t>
-  </si>
-  <si>
-    <t>The rule.</t>
-  </si>
-  <si>
-    <t>The inbox it acts in.</t>
-  </si>
-  <si>
-    <t>origin</t>
-  </si>
-  <si>
-    <t>conversations.rule_origin</t>
-  </si>
-  <si>
-    <t>How it was taught.</t>
-  </si>
-  <si>
-    <t>paused_reason</t>
-  </si>
-  <si>
-    <t>conversations.paused_reason</t>
-  </si>
-  <si>
-    <t>Why it is paused, when it is.</t>
-  </si>
-  <si>
-    <t>conversations.rule_state</t>
-  </si>
-  <si>
-    <t>Its state as readers see it (paused while its author may not act).</t>
-  </si>
-  <si>
-    <t>changed</t>
-  </si>
-  <si>
-    <t>Conversations it changed.</t>
-  </si>
-  <si>
-    <t>done</t>
-  </si>
-  <si>
-    <t>Conversations it went through.</t>
-  </si>
-  <si>
-    <t>The run.</t>
-  </si>
-  <si>
-    <t>conversations.run_kind</t>
-  </si>
-  <si>
-    <t>Applying, or putting back.</t>
-  </si>
-  <si>
-    <t>rule_id</t>
-  </si>
-  <si>
-    <t>Its rule.</t>
-  </si>
-  <si>
-    <t>skipped_member</t>
-  </si>
-  <si>
-    <t>Conversations a member had changed, left alone.</t>
-  </si>
-  <si>
-    <t>skipped_suspicious</t>
-  </si>
-  <si>
-    <t>Suspicious mail it left alone.</t>
-  </si>
-  <si>
-    <t>conversations.run_state</t>
-  </si>
-  <si>
-    <t>total</t>
-  </si>
-  <si>
-    <t>Conversations it matched.</t>
-  </si>
-  <si>
-    <t>When it was created.</t>
-  </si>
-  <si>
-    <t>The account's id.</t>
-  </si>
-  <si>
-    <t>passkeys</t>
-  </si>
-  <si>
-    <t>How many passkeys are ways into it.</t>
-  </si>
-  <si>
-    <t>provider_ways_in</t>
-  </si>
-  <si>
-    <t>How many provider identities are ways into it.</t>
-  </si>
-  <si>
-    <t>Whether an administrator suspended it.</t>
-  </si>
-  <si>
-    <t>Its client id, when Campbooks minted it; absent for a metadata-document client, whose id is a URL.</t>
-  </si>
-  <si>
-    <t>confidential</t>
-  </si>
-  <si>
-    <t>Whether it authenticates with a secret.</t>
-  </si>
-  <si>
-    <t>When it was registered.</t>
-  </si>
-  <si>
-    <t>redirect_uri_count</t>
-  </si>
-  <si>
-    <t>How many redirect URIs it registered (never the URIs).</t>
-  </si>
-  <si>
-    <t>How many scopes it may ask for.</t>
-  </si>
-  <si>
-    <t>secret_rotated_at</t>
-  </si>
-  <si>
-    <t>When its secret was last rotated.</t>
-  </si>
-  <si>
-    <t>The account that gave it.</t>
-  </si>
-  <si>
-    <t>bound_workspace_id</t>
-  </si>
-  <si>
-    <t>The workspace the client may use, when it binds one.</t>
-  </si>
-  <si>
-    <t>The client it lets in, when Campbooks minted its id; absent for a metadata-document client.</t>
-  </si>
-  <si>
-    <t>What kind of client it lets in.</t>
-  </si>
-  <si>
-    <t>granted_at</t>
-  </si>
-  <si>
-    <t>When it was given.</t>
-  </si>
-  <si>
-    <t>The consent's id.</t>
-  </si>
-  <si>
-    <t>remembered</t>
-  </si>
-  <si>
-    <t>Whether a later authorization may skip the screen.</t>
-  </si>
-  <si>
-    <t>revoked_at</t>
-  </si>
-  <si>
-    <t>When it was revoked, if it was.</t>
-  </si>
-  <si>
-    <t>How many scopes it allows (never their names).</t>
-  </si>
-  <si>
-    <t>The account it is a way into.</t>
-  </si>
-  <si>
-    <t>added_via</t>
-  </si>
-  <si>
-    <t>identity.passkey_added_via</t>
-  </si>
-  <si>
-    <t>How it was added.</t>
-  </si>
-  <si>
-    <t>backup_eligible</t>
-  </si>
-  <si>
-    <t>Whether it may be synced (a multi-device passkey).</t>
-  </si>
-  <si>
-    <t>backup_state</t>
-  </si>
-  <si>
-    <t>Whether it is synced now.</t>
-  </si>
-  <si>
-    <t>When it was added.</t>
-  </si>
-  <si>
-    <t>The passkey's id (never its credential id).</t>
-  </si>
-  <si>
-    <t>last_used_at</t>
-  </si>
-  <si>
-    <t>When it was last used to sign in.</t>
-  </si>
-  <si>
-    <t>The account signed in.</t>
-  </si>
-  <si>
-    <t>auth_time</t>
-  </si>
-  <si>
-    <t>When the person authenticated.</t>
-  </si>
-  <si>
-    <t>ended_at</t>
-  </si>
-  <si>
-    <t>When it was ended, if it was.</t>
-  </si>
-  <si>
-    <t>expires_at</t>
-  </si>
-  <si>
-    <t>When it ends at the latest.</t>
-  </si>
-  <si>
-    <t>The issuer session's id.</t>
-  </si>
-  <si>
-    <t>How the person signed in.</t>
-  </si>
-  <si>
-    <t>The provider signed in with, for a provider sign-in whose way in still exists.</t>
-  </si>
-  <si>
-    <t>Whether the provider verified its address when it was linked (the address is never kept).</t>
-  </si>
-  <si>
-    <t>The provider identity's id (never its subject).</t>
-  </si>
-  <si>
-    <t>linked_at</t>
-  </si>
-  <si>
-    <t>When it was linked.</t>
-  </si>
-  <si>
-    <t>linked_via</t>
-  </si>
-  <si>
-    <t>identity.linked_via</t>
-  </si>
-  <si>
-    <t>How it was linked.</t>
-  </si>
-  <si>
-    <t>Its provider.</t>
-  </si>
-  <si>
-    <t>Attempts made.</t>
-  </si>
-  <si>
-    <t>When it was enqueued.</t>
-  </si>
-  <si>
-    <t>The job's id.</t>
-  </si>
-  <si>
-    <t>The job's kind (`&lt;module&gt;.&lt;job&gt;`).</t>
-  </si>
-  <si>
-    <t>max_attempts</t>
-  </si>
-  <si>
-    <t>Attempts it is allowed.</t>
-  </si>
-  <si>
-    <t>The queue it runs on.</t>
-  </si>
-  <si>
-    <t>kernel.job_state</t>
-  </si>
-  <si>
-    <t>workspace_id</t>
-  </si>
-  <si>
-    <t>The workspace it belongs to; none for instance-wide work.</t>
-  </si>
-  <si>
-    <t>accepted_at</t>
-  </si>
-  <si>
-    <t>When it was accepted.</t>
-  </si>
-  <si>
-    <t>accepted_by</t>
-  </si>
-  <si>
-    <t>Who accepted it: their user id.</t>
-  </si>
-  <si>
-    <t>When it was sent.</t>
-  </si>
-  <si>
-    <t>When it stops working.</t>
-  </si>
-  <si>
-    <t>The invitation's id.</t>
-  </si>
-  <si>
-    <t>invited_by</t>
-  </si>
-  <si>
-    <t>Who invited: their user id.</t>
   </si>
   <si>
     <t>The role the invitee gets on accepting (admin or member).</t>
@@ -11028,7 +11028,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K244"/>
+  <dimension ref="A1:K243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -17086,23 +17086,23 @@
     </row>
     <row r="219" spans="1:10">
       <c r="A219" s="3" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B219" s="3">
         <v>1</v>
       </c>
       <c r="C219" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="F219" s="3" t="s">
         <v>859</v>
       </c>
-      <c r="D219" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="E219" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="F219" s="3" t="s">
-        <v>848</v>
-      </c>
       <c r="G219" s="3" t="s">
         <v>562</v>
       </c>
@@ -17110,7 +17110,7 @@
         <v>17</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>849</v>
+        <v>860</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -17121,48 +17121,48 @@
         <v>1</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>490</v>
+        <v>861</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>559</v>
+        <v>13</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="F220" s="3" t="s">
-        <v>860</v>
+        <v>562</v>
       </c>
       <c r="G220" s="3" t="s">
         <v>562</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="221" spans="1:10">
       <c r="A221" s="3" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B221" s="3">
         <v>1</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>862</v>
+        <v>490</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>13</v>
+        <v>559</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>859</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J221" s="3" t="s">
         <v>863</v>
@@ -17176,7 +17176,7 @@
         <v>1</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D222" s="3" t="s">
         <v>559</v>
@@ -17185,16 +17185,16 @@
         <v>560</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H222" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J222" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -17205,16 +17205,16 @@
         <v>1</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>495</v>
+        <v>866</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>560</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="G223" s="3" t="s">
         <v>562</v>
@@ -17223,18 +17223,18 @@
         <v>17</v>
       </c>
       <c r="J223" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="224" spans="1:10">
       <c r="A224" s="3" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B224" s="3">
         <v>1</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>569</v>
@@ -17243,7 +17243,7 @@
         <v>560</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="G224" s="3" t="s">
         <v>562</v>
@@ -17252,7 +17252,7 @@
         <v>17</v>
       </c>
       <c r="J224" s="3" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="225" spans="1:10">
@@ -17263,7 +17263,7 @@
         <v>1</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>870</v>
+        <v>632</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>569</v>
@@ -17272,7 +17272,7 @@
         <v>560</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G225" s="3" t="s">
         <v>562</v>
@@ -17281,7 +17281,7 @@
         <v>17</v>
       </c>
       <c r="J225" s="3" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -17292,16 +17292,16 @@
         <v>1</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>632</v>
+        <v>495</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>560</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="G226" s="3" t="s">
         <v>562</v>
@@ -17315,22 +17315,22 @@
     </row>
     <row r="227" spans="1:10">
       <c r="A227" s="3" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B227" s="3">
         <v>1</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>495</v>
+        <v>578</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>560</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>865</v>
+        <v>875</v>
       </c>
       <c r="G227" s="3" t="s">
         <v>562</v>
@@ -17339,7 +17339,7 @@
         <v>17</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -17350,16 +17350,16 @@
         <v>1</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>578</v>
+        <v>495</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>560</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="G228" s="3" t="s">
         <v>562</v>
@@ -17373,7 +17373,7 @@
     </row>
     <row r="229" spans="1:10">
       <c r="A229" s="3" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B229" s="3">
         <v>1</v>
@@ -17388,7 +17388,7 @@
         <v>560</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G229" s="3" t="s">
         <v>562</v>
@@ -17402,7 +17402,7 @@
     </row>
     <row r="230" spans="1:10">
       <c r="A230" s="3" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B230" s="3">
         <v>1</v>
@@ -17417,7 +17417,7 @@
         <v>560</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G230" s="3" t="s">
         <v>562</v>
@@ -17431,13 +17431,13 @@
     </row>
     <row r="231" spans="1:10">
       <c r="A231" s="3" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B231" s="3">
         <v>1</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>559</v>
@@ -17446,7 +17446,7 @@
         <v>560</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="G231" s="3" t="s">
         <v>562</v>
@@ -17455,12 +17455,12 @@
         <v>17</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="232" spans="1:10">
       <c r="A232" s="3" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B232" s="3">
         <v>1</v>
@@ -17475,7 +17475,7 @@
         <v>560</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G232" s="3" t="s">
         <v>562</v>
@@ -17489,7 +17489,7 @@
     </row>
     <row r="233" spans="1:10">
       <c r="A233" s="3" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B233" s="3">
         <v>1</v>
@@ -17504,7 +17504,7 @@
         <v>560</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G233" s="3" t="s">
         <v>562</v>
@@ -17518,22 +17518,22 @@
     </row>
     <row r="234" spans="1:10">
       <c r="A234" s="3" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B234" s="3">
         <v>1</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>514</v>
+        <v>578</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>560</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="G234" s="3" t="s">
         <v>562</v>
@@ -17542,7 +17542,7 @@
         <v>17</v>
       </c>
       <c r="J234" s="3" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -17553,16 +17553,16 @@
         <v>1</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>578</v>
+        <v>526</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>560</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G235" s="3" t="s">
         <v>562</v>
@@ -17571,12 +17571,12 @@
         <v>17</v>
       </c>
       <c r="J235" s="3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="236" spans="1:10">
       <c r="A236" s="3" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B236" s="3">
         <v>1</v>
@@ -17591,7 +17591,7 @@
         <v>560</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G236" s="3" t="s">
         <v>562</v>
@@ -17605,22 +17605,22 @@
     </row>
     <row r="237" spans="1:10">
       <c r="A237" s="3" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B237" s="3">
         <v>1</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>526</v>
+        <v>578</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>560</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="G237" s="3" t="s">
         <v>562</v>
@@ -17629,7 +17629,7 @@
         <v>17</v>
       </c>
       <c r="J237" s="3" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
     </row>
     <row r="238" spans="1:10">
@@ -17640,16 +17640,16 @@
         <v>1</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>578</v>
+        <v>526</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="E238" s="3" t="s">
         <v>560</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G238" s="3" t="s">
         <v>562</v>
@@ -17658,18 +17658,18 @@
         <v>17</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
     </row>
     <row r="239" spans="1:10">
       <c r="A239" s="3" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B239" s="3">
         <v>1</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>526</v>
+        <v>890</v>
       </c>
       <c r="D239" s="3" t="s">
         <v>559</v>
@@ -17678,7 +17678,7 @@
         <v>560</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="G239" s="3" t="s">
         <v>562</v>
@@ -17687,18 +17687,18 @@
         <v>17</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="240" spans="1:10">
       <c r="A240" s="3" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B240" s="3">
         <v>1</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D240" s="3" t="s">
         <v>559</v>
@@ -17707,7 +17707,7 @@
         <v>560</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G240" s="3" t="s">
         <v>562</v>
@@ -17721,13 +17721,13 @@
     </row>
     <row r="241" spans="1:10">
       <c r="A241" s="3" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B241" s="3">
         <v>1</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D241" s="3" t="s">
         <v>559</v>
@@ -17736,7 +17736,7 @@
         <v>560</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>562</v>
@@ -17750,22 +17750,22 @@
     </row>
     <row r="242" spans="1:10">
       <c r="A242" s="3" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B242" s="3">
         <v>1</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>891</v>
+        <v>568</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="G242" s="3" t="s">
         <v>562</v>
@@ -17774,7 +17774,7 @@
         <v>17</v>
       </c>
       <c r="J242" s="3" t="s">
-        <v>895</v>
+        <v>571</v>
       </c>
     </row>
     <row r="243" spans="1:10">
@@ -17785,58 +17785,29 @@
         <v>1</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>568</v>
+        <v>890</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F243" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="H243" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J243" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="G243" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="H243" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J243" s="3" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10">
-      <c r="A244" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="B244" s="3">
-        <v>1</v>
-      </c>
-      <c r="C244" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="D244" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="E244" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="F244" s="3" t="s">
-        <v>892</v>
-      </c>
-      <c r="G244" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="H244" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J244" s="3" t="s">
-        <v>897</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K244"/>
+  <autoFilter ref="A1:K243"/>
   <dataValidations count="11">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Event" prompt="The event's name." sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Version" prompt="The event's version." sqref="B2:B2001"/>
@@ -17880,10 +17851,10 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>898</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>899</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>552</v>
@@ -17892,7 +17863,7 @@
         <v>553</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>555</v>
@@ -17912,7 +17883,7 @@
         <v>561</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>13</v>
@@ -17927,7 +17898,7 @@
         <v>13</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -17944,16 +17915,16 @@
         <v>560</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>903</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -17961,7 +17932,7 @@
         <v>561</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>569</v>
@@ -17970,7 +17941,7 @@
         <v>560</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>562</v>
@@ -18002,7 +17973,7 @@
         <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -18010,7 +17981,7 @@
         <v>561</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>597</v>
@@ -18025,7 +17996,7 @@
         <v>17</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -18033,7 +18004,7 @@
         <v>561</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>569</v>
@@ -18042,16 +18013,16 @@
         <v>562</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>911</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -18059,10 +18030,10 @@
         <v>564</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>913</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>914</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>560</v>
@@ -18074,7 +18045,7 @@
         <v>13</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -18082,7 +18053,7 @@
         <v>564</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>579</v>
@@ -18097,7 +18068,7 @@
         <v>17</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -18120,7 +18091,7 @@
         <v>13</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -18128,7 +18099,7 @@
         <v>564</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>579</v>
@@ -18143,7 +18114,7 @@
         <v>17</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -18151,7 +18122,7 @@
         <v>564</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>597</v>
@@ -18166,7 +18137,7 @@
         <v>17</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -18174,7 +18145,7 @@
         <v>572</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>670</v>
@@ -18189,7 +18160,7 @@
         <v>17</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -18197,7 +18168,7 @@
         <v>572</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>579</v>
@@ -18212,7 +18183,7 @@
         <v>17</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -18220,7 +18191,7 @@
         <v>572</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>569</v>
@@ -18229,16 +18200,16 @@
         <v>560</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>927</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>928</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -18246,7 +18217,7 @@
         <v>572</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>597</v>
@@ -18261,7 +18232,7 @@
         <v>17</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -18269,7 +18240,7 @@
         <v>572</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>13</v>
@@ -18284,7 +18255,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -18292,7 +18263,7 @@
         <v>574</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>569</v>
@@ -18301,16 +18272,16 @@
         <v>560</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>935</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -18318,7 +18289,7 @@
         <v>574</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>13</v>
@@ -18333,7 +18304,7 @@
         <v>13</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -18356,7 +18327,7 @@
         <v>13</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -18373,16 +18344,16 @@
         <v>560</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>939</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -18393,7 +18364,7 @@
         <v>559</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>560</v>
@@ -18405,7 +18376,7 @@
         <v>13</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -18413,7 +18384,7 @@
         <v>574</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>569</v>
@@ -18422,16 +18393,16 @@
         <v>560</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>943</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -18439,7 +18410,7 @@
         <v>581</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>853</v>
@@ -18454,7 +18425,7 @@
         <v>17</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -18477,7 +18448,7 @@
         <v>13</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -18494,16 +18465,16 @@
         <v>560</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>948</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -18514,7 +18485,7 @@
         <v>559</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>560</v>
@@ -18526,7 +18497,7 @@
         <v>13</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -18534,7 +18505,7 @@
         <v>581</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>579</v>
@@ -18549,7 +18520,7 @@
         <v>17</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -18557,7 +18528,7 @@
         <v>581</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>579</v>
@@ -18572,7 +18543,7 @@
         <v>17</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -18580,7 +18551,7 @@
         <v>581</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>569</v>
@@ -18589,16 +18560,16 @@
         <v>560</v>
       </c>
       <c r="E30" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>955</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -18606,7 +18577,7 @@
         <v>581</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>569</v>
@@ -18615,16 +18586,16 @@
         <v>560</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>958</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -18632,7 +18603,7 @@
         <v>581</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>670</v>
@@ -18647,7 +18618,7 @@
         <v>17</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -18655,7 +18626,7 @@
         <v>616</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>670</v>
@@ -18670,7 +18641,7 @@
         <v>17</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -18678,7 +18649,7 @@
         <v>616</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>569</v>
@@ -18696,7 +18667,7 @@
         <v>17</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -18704,7 +18675,7 @@
         <v>616</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>579</v>
@@ -18719,7 +18690,7 @@
         <v>17</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -18727,7 +18698,7 @@
         <v>616</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>13</v>
@@ -18742,7 +18713,7 @@
         <v>15</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -18750,7 +18721,7 @@
         <v>616</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>569</v>
@@ -18768,7 +18739,7 @@
         <v>17</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -18776,7 +18747,7 @@
         <v>616</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>579</v>
@@ -18791,7 +18762,7 @@
         <v>17</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -18799,7 +18770,7 @@
         <v>616</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>569</v>
@@ -18808,16 +18779,16 @@
         <v>560</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>974</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -18840,7 +18811,7 @@
         <v>13</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -18848,7 +18819,7 @@
         <v>616</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>597</v>
@@ -18863,7 +18834,7 @@
         <v>17</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -18897,7 +18868,7 @@
         <v>653</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>597</v>
@@ -18912,7 +18883,7 @@
         <v>17</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -18920,7 +18891,7 @@
         <v>653</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>579</v>
@@ -18935,7 +18906,7 @@
         <v>17</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -18958,7 +18929,7 @@
         <v>13</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -18981,7 +18952,7 @@
         <v>13</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -19007,7 +18978,7 @@
         <v>17</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -19015,7 +18986,7 @@
         <v>653</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>569</v>
@@ -19024,16 +18995,16 @@
         <v>560</v>
       </c>
       <c r="E48" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>986</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -19041,7 +19012,7 @@
         <v>653</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>569</v>
@@ -19050,7 +19021,7 @@
         <v>560</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>562</v>
@@ -19059,7 +19030,7 @@
         <v>17</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -19082,7 +19053,7 @@
         <v>13</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -19090,7 +19061,7 @@
         <v>664</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>569</v>
@@ -19108,7 +19079,7 @@
         <v>17</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -19154,7 +19125,7 @@
         <v>13</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -19177,7 +19148,7 @@
         <v>13</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -19185,7 +19156,7 @@
         <v>664</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>579</v>
@@ -19200,7 +19171,7 @@
         <v>17</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -19208,7 +19179,7 @@
         <v>664</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>579</v>
@@ -19223,7 +19194,7 @@
         <v>17</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -19231,7 +19202,7 @@
         <v>664</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>670</v>
@@ -19246,7 +19217,7 @@
         <v>17</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -19254,7 +19225,7 @@
         <v>664</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>569</v>
@@ -19272,7 +19243,7 @@
         <v>17</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -19295,7 +19266,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -19318,7 +19289,7 @@
         <v>13</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -19326,7 +19297,7 @@
         <v>666</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>579</v>
@@ -19341,7 +19312,7 @@
         <v>17</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -19364,7 +19335,7 @@
         <v>17</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -19387,7 +19358,7 @@
         <v>17</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -19395,7 +19366,7 @@
         <v>666</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>569</v>
@@ -19404,16 +19375,16 @@
         <v>560</v>
       </c>
       <c r="E64" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" s="3" t="s">
         <v>1008</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -19430,16 +19401,16 @@
         <v>560</v>
       </c>
       <c r="E65" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>1010</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -19447,7 +19418,7 @@
         <v>666</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>569</v>
@@ -19456,16 +19427,16 @@
         <v>560</v>
       </c>
       <c r="E66" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>1013</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -19473,7 +19444,7 @@
         <v>666</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>597</v>
@@ -19488,7 +19459,7 @@
         <v>17</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -19496,7 +19467,7 @@
         <v>677</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>597</v>
@@ -19511,7 +19482,7 @@
         <v>17</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -19519,7 +19490,7 @@
         <v>677</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>597</v>
@@ -19534,7 +19505,7 @@
         <v>17</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -19542,7 +19513,7 @@
         <v>677</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>597</v>
@@ -19557,7 +19528,7 @@
         <v>17</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -19580,7 +19551,7 @@
         <v>13</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -19606,7 +19577,7 @@
         <v>17</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -19629,7 +19600,7 @@
         <v>13</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -19652,7 +19623,7 @@
         <v>13</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -19669,16 +19640,16 @@
         <v>560</v>
       </c>
       <c r="E75" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I75" s="3" t="s">
         <v>1026</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -19701,7 +19672,7 @@
         <v>13</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -19709,7 +19680,7 @@
         <v>677</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>579</v>
@@ -19724,7 +19695,7 @@
         <v>17</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -19732,7 +19703,7 @@
         <v>677</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>569</v>
@@ -19741,16 +19712,16 @@
         <v>560</v>
       </c>
       <c r="E78" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I78" s="3" t="s">
         <v>1031</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -19758,7 +19729,7 @@
         <v>677</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>597</v>
@@ -19773,7 +19744,7 @@
         <v>17</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -19781,7 +19752,7 @@
         <v>677</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>597</v>
@@ -19796,7 +19767,7 @@
         <v>17</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -19804,7 +19775,7 @@
         <v>735</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>569</v>
@@ -19813,16 +19784,16 @@
         <v>560</v>
       </c>
       <c r="E81" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" s="3" t="s">
         <v>1038</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -19830,7 +19801,7 @@
         <v>735</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>569</v>
@@ -19839,16 +19810,16 @@
         <v>560</v>
       </c>
       <c r="E82" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I82" s="3" t="s">
         <v>1041</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -19871,7 +19842,7 @@
         <v>13</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -19879,7 +19850,7 @@
         <v>735</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>670</v>
@@ -19894,7 +19865,7 @@
         <v>17</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -19917,7 +19888,7 @@
         <v>13</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -19925,7 +19896,7 @@
         <v>735</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>569</v>
@@ -19934,16 +19905,16 @@
         <v>560</v>
       </c>
       <c r="E86" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I86" s="3" t="s">
         <v>1048</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -19960,16 +19931,16 @@
         <v>560</v>
       </c>
       <c r="E87" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I87" s="3" t="s">
         <v>1050</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -19977,7 +19948,7 @@
         <v>735</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>569</v>
@@ -19986,16 +19957,16 @@
         <v>560</v>
       </c>
       <c r="E88" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I88" s="3" t="s">
         <v>1052</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -20003,7 +19974,7 @@
         <v>735</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>569</v>
@@ -20012,16 +19983,16 @@
         <v>560</v>
       </c>
       <c r="E89" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89" s="3" t="s">
         <v>1054</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -20029,7 +20000,7 @@
         <v>735</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>670</v>
@@ -20044,7 +20015,7 @@
         <v>17</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -20052,7 +20023,7 @@
         <v>735</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>569</v>
@@ -20061,16 +20032,16 @@
         <v>560</v>
       </c>
       <c r="E91" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91" s="3" t="s">
         <v>1058</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -20078,7 +20049,7 @@
         <v>740</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>569</v>
@@ -20087,16 +20058,16 @@
         <v>562</v>
       </c>
       <c r="E92" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I92" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -20104,7 +20075,7 @@
         <v>740</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>597</v>
@@ -20119,7 +20090,7 @@
         <v>17</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -20127,7 +20098,7 @@
         <v>740</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>597</v>
@@ -20142,7 +20113,7 @@
         <v>17</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -20165,7 +20136,7 @@
         <v>13</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -20188,7 +20159,7 @@
         <v>13</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -20196,7 +20167,7 @@
         <v>740</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>569</v>
@@ -20205,16 +20176,16 @@
         <v>560</v>
       </c>
       <c r="E97" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I97" s="3" t="s">
         <v>1070</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -20222,7 +20193,7 @@
         <v>740</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>569</v>
@@ -20231,16 +20202,16 @@
         <v>560</v>
       </c>
       <c r="E98" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I98" s="3" t="s">
         <v>1073</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -20248,7 +20219,7 @@
         <v>740</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>569</v>
@@ -20257,16 +20228,16 @@
         <v>560</v>
       </c>
       <c r="E99" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99" s="3" t="s">
         <v>1075</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -20274,7 +20245,7 @@
         <v>756</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>597</v>
@@ -20289,7 +20260,7 @@
         <v>17</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -20297,7 +20268,7 @@
         <v>756</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>597</v>
@@ -20312,7 +20283,7 @@
         <v>17</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -20335,7 +20306,7 @@
         <v>13</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -20352,16 +20323,16 @@
         <v>560</v>
       </c>
       <c r="E103" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103" s="3" t="s">
         <v>1082</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -20369,7 +20340,7 @@
         <v>756</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>13</v>
@@ -20384,7 +20355,7 @@
         <v>13</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -20392,7 +20363,7 @@
         <v>756</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>597</v>
@@ -20407,7 +20378,7 @@
         <v>17</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -20415,7 +20386,7 @@
         <v>756</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>597</v>
@@ -20430,7 +20401,7 @@
         <v>17</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -20438,7 +20409,7 @@
         <v>756</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>569</v>
@@ -20447,7 +20418,7 @@
         <v>560</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>562</v>
@@ -20464,7 +20435,7 @@
         <v>756</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>597</v>
@@ -20479,7 +20450,7 @@
         <v>17</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -20487,7 +20458,7 @@
         <v>761</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>579</v>
@@ -20502,7 +20473,7 @@
         <v>17</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -20525,7 +20496,7 @@
         <v>15</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -20533,7 +20504,7 @@
         <v>761</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>597</v>
@@ -20548,7 +20519,7 @@
         <v>17</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -20556,7 +20527,7 @@
         <v>761</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>597</v>
@@ -20571,7 +20542,7 @@
         <v>17</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -20594,7 +20565,7 @@
         <v>17</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -20620,7 +20591,7 @@
         <v>777</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -20628,7 +20599,7 @@
         <v>771</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>670</v>
@@ -20643,7 +20614,7 @@
         <v>17</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -20651,7 +20622,7 @@
         <v>771</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>579</v>
@@ -20666,7 +20637,7 @@
         <v>17</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -20700,7 +20671,7 @@
         <v>771</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>597</v>
@@ -20715,7 +20686,7 @@
         <v>17</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -20738,7 +20709,7 @@
         <v>17</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -20746,7 +20717,7 @@
         <v>771</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>579</v>
@@ -20761,7 +20732,7 @@
         <v>17</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -20784,7 +20755,7 @@
         <v>15</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -20792,7 +20763,7 @@
         <v>792</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>13</v>
@@ -20807,7 +20778,7 @@
         <v>15</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -20833,7 +20804,7 @@
         <v>777</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -20859,7 +20830,7 @@
         <v>17</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -20867,7 +20838,7 @@
         <v>792</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>579</v>
@@ -20882,7 +20853,7 @@
         <v>17</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -20905,7 +20876,7 @@
         <v>13</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -20913,7 +20884,7 @@
         <v>792</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>670</v>
@@ -20928,7 +20899,7 @@
         <v>17</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -20936,7 +20907,7 @@
         <v>792</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>579</v>
@@ -20951,7 +20922,7 @@
         <v>17</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -20974,7 +20945,7 @@
         <v>17</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -20997,7 +20968,7 @@
         <v>15</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -21005,7 +20976,7 @@
         <v>803</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>569</v>
@@ -21014,16 +20985,16 @@
         <v>560</v>
       </c>
       <c r="E131" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I131" s="3" t="s">
         <v>1124</v>
-      </c>
-      <c r="F131" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G131" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I131" s="3" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -21031,7 +21002,7 @@
         <v>803</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>670</v>
@@ -21046,7 +21017,7 @@
         <v>17</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -21054,7 +21025,7 @@
         <v>803</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>670</v>
@@ -21069,7 +21040,7 @@
         <v>17</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -21077,7 +21048,7 @@
         <v>803</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>579</v>
@@ -21092,7 +21063,7 @@
         <v>17</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -21115,7 +21086,7 @@
         <v>13</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -21123,7 +21094,7 @@
         <v>803</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>579</v>
@@ -21138,7 +21109,7 @@
         <v>17</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -21161,7 +21132,7 @@
         <v>15</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -21169,7 +21140,7 @@
         <v>811</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>579</v>
@@ -21184,7 +21155,7 @@
         <v>17</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -21192,7 +21163,7 @@
         <v>811</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>579</v>
@@ -21207,7 +21178,7 @@
         <v>17</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -21215,7 +21186,7 @@
         <v>811</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>579</v>
@@ -21230,7 +21201,7 @@
         <v>17</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -21253,7 +21224,7 @@
         <v>13</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -21279,7 +21250,7 @@
         <v>17</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -21305,7 +21276,7 @@
         <v>17</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -21328,7 +21299,7 @@
         <v>15</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -21336,7 +21307,7 @@
         <v>831</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>670</v>
@@ -21351,7 +21322,7 @@
         <v>17</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -21374,7 +21345,7 @@
         <v>13</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -21382,7 +21353,7 @@
         <v>831</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>579</v>
@@ -21397,7 +21368,7 @@
         <v>17</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -21405,7 +21376,7 @@
         <v>831</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>579</v>
@@ -21420,7 +21391,7 @@
         <v>17</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -21428,7 +21399,7 @@
         <v>831</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>569</v>
@@ -21437,16 +21408,16 @@
         <v>560</v>
       </c>
       <c r="E149" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149" s="3" t="s">
         <v>1149</v>
-      </c>
-      <c r="F149" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G149" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I149" s="3" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -21472,7 +21443,7 @@
         <v>17</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -21480,7 +21451,7 @@
         <v>834</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>597</v>
@@ -21495,7 +21466,7 @@
         <v>17</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -21503,7 +21474,7 @@
         <v>834</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>579</v>
@@ -21518,7 +21489,7 @@
         <v>17</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -21541,7 +21512,7 @@
         <v>13</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -21567,7 +21538,7 @@
         <v>837</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -21575,7 +21546,7 @@
         <v>834</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>597</v>
@@ -21590,7 +21561,7 @@
         <v>17</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -21616,7 +21587,7 @@
         <v>842</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -21624,7 +21595,7 @@
         <v>834</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>569</v>
@@ -21633,7 +21604,7 @@
         <v>560</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>562</v>
@@ -21642,7 +21613,7 @@
         <v>17</v>
       </c>
       <c r="I157" s="3" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -21650,7 +21621,7 @@
         <v>834</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>13</v>
@@ -21665,15 +21636,15 @@
         <v>15</v>
       </c>
       <c r="I158" s="3" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="A159" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>579</v>
@@ -21688,15 +21659,15 @@
         <v>17</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="160" spans="1:9">
       <c r="A160" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>13</v>
@@ -21711,15 +21682,15 @@
         <v>15</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>579</v>
@@ -21734,15 +21705,15 @@
         <v>17</v>
       </c>
       <c r="I161" s="3" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>579</v>
@@ -21757,12 +21728,12 @@
         <v>17</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>13</v>
@@ -21780,15 +21751,15 @@
         <v>13</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>13</v>
@@ -21803,15 +21774,15 @@
         <v>15</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>859</v>
+        <v>1170</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>569</v>
@@ -21820,7 +21791,7 @@
         <v>560</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>562</v>
@@ -21834,10 +21805,10 @@
     </row>
     <row r="166" spans="1:9">
       <c r="A166" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>569</v>
@@ -21855,12 +21826,12 @@
         <v>17</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>1173</v>
@@ -21883,10 +21854,10 @@
     </row>
     <row r="168" spans="1:9">
       <c r="A168" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>859</v>
+        <v>1170</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>569</v>
@@ -21895,7 +21866,7 @@
         <v>560</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>562</v>
@@ -21909,7 +21880,7 @@
     </row>
     <row r="169" spans="1:9">
       <c r="A169" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>359</v>
@@ -21932,10 +21903,10 @@
     </row>
     <row r="170" spans="1:9">
       <c r="A170" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>13</v>
@@ -21950,15 +21921,15 @@
         <v>15</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>579</v>
@@ -21978,10 +21949,10 @@
     </row>
     <row r="172" spans="1:9">
       <c r="A172" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>579</v>
@@ -22001,7 +21972,7 @@
     </row>
     <row r="173" spans="1:9">
       <c r="A173" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>13</v>
@@ -22024,7 +21995,7 @@
     </row>
     <row r="174" spans="1:9">
       <c r="A174" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>1180</v>
@@ -22047,10 +22018,10 @@
     </row>
     <row r="175" spans="1:9">
       <c r="A175" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>579</v>
@@ -22070,10 +22041,10 @@
     </row>
     <row r="176" spans="1:9">
       <c r="A176" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>569</v>
@@ -22096,7 +22067,7 @@
     </row>
     <row r="177" spans="1:9">
       <c r="A177" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>1185</v>
@@ -22119,7 +22090,7 @@
     </row>
     <row r="178" spans="1:9">
       <c r="A178" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>1187</v>
@@ -22142,7 +22113,7 @@
     </row>
     <row r="179" spans="1:9">
       <c r="A179" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>1189</v>
@@ -22165,10 +22136,10 @@
     </row>
     <row r="180" spans="1:9">
       <c r="A180" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>569</v>
@@ -22177,7 +22148,7 @@
         <v>560</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>562</v>
@@ -22186,15 +22157,15 @@
         <v>17</v>
       </c>
       <c r="I180" s="3" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="A181" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>13</v>
@@ -22214,7 +22185,7 @@
     </row>
     <row r="182" spans="1:9">
       <c r="A182" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>1192</v>
@@ -22237,7 +22208,7 @@
     </row>
     <row r="183" spans="1:9">
       <c r="A183" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>1194</v>
@@ -22263,10 +22234,10 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>579</v>
@@ -22281,12 +22252,12 @@
         <v>17</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>1197</v>
@@ -22309,7 +22280,7 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>13</v>
@@ -22332,7 +22303,7 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>745</v>
@@ -22358,7 +22329,7 @@
     </row>
     <row r="188" spans="1:9">
       <c r="A188" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>1202</v>
@@ -22381,7 +22352,7 @@
     </row>
     <row r="189" spans="1:9">
       <c r="A189" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>1204</v>
@@ -22439,7 +22410,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1206</v>
@@ -22450,7 +22421,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>1207</v>
@@ -22461,7 +22432,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1209</v>
@@ -22472,7 +22443,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>1211</v>
@@ -22483,7 +22454,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>1213</v>
@@ -22494,7 +22465,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>1215</v>
@@ -22505,7 +22476,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>1217</v>
@@ -22516,7 +22487,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>642</v>
@@ -22527,7 +22498,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>1220</v>
@@ -22538,7 +22509,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>1222</v>
@@ -22549,10 +22520,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1224</v>
@@ -22560,7 +22531,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>1225</v>
@@ -22571,7 +22542,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>1227</v>
@@ -22582,7 +22553,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>1229</v>
@@ -22593,7 +22564,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>1231</v>
@@ -22604,7 +22575,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>1233</v>
@@ -22615,10 +22586,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1235</v>
@@ -22626,7 +22597,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>164</v>
@@ -22637,7 +22608,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>1237</v>
@@ -22648,7 +22619,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>1239</v>
@@ -22659,7 +22630,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>1241</v>
@@ -22670,7 +22641,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>1243</v>
@@ -22681,7 +22652,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>1245</v>
@@ -22692,7 +22663,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>1247</v>
@@ -22703,7 +22674,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>1249</v>
@@ -22714,7 +22685,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>1251</v>
@@ -22725,7 +22696,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>1253</v>
@@ -22736,7 +22707,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>1255</v>
@@ -22747,7 +22718,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>1257</v>
@@ -22758,7 +22729,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>1259</v>
@@ -22769,7 +22740,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>1261</v>
@@ -22783,10 +22754,10 @@
         <v>570</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>923</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -22794,7 +22765,7 @@
         <v>570</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1263</v>
@@ -22802,7 +22773,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>1264</v>
@@ -22813,7 +22784,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>1266</v>
@@ -22824,7 +22795,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>1268</v>
@@ -22835,7 +22806,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>1270</v>
@@ -22846,7 +22817,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>1272</v>
@@ -22857,10 +22828,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>1274</v>
@@ -22868,7 +22839,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>1275</v>
@@ -22879,7 +22850,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>1277</v>
@@ -22890,7 +22861,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>1279</v>
@@ -22901,7 +22872,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>1281</v>
@@ -22912,7 +22883,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>1283</v>
@@ -22923,7 +22894,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>1285</v>
@@ -22934,7 +22905,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>1287</v>
@@ -22945,7 +22916,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>1289</v>
@@ -22956,7 +22927,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>1291</v>
@@ -22967,7 +22938,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>1293</v>
@@ -22978,7 +22949,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>1295</v>
@@ -22989,7 +22960,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>1297</v>
@@ -23000,7 +22971,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>1299</v>
@@ -23011,7 +22982,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>1301</v>
@@ -23022,7 +22993,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>1303</v>
@@ -23033,7 +23004,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>1305</v>
@@ -23044,7 +23015,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>1307</v>
@@ -23055,7 +23026,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>1309</v>
@@ -23066,7 +23037,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>1311</v>
@@ -23077,7 +23048,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>1313</v>
@@ -23088,7 +23059,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>1315</v>
@@ -23099,7 +23070,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>1317</v>
@@ -23110,7 +23081,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>1319</v>
@@ -23121,7 +23092,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>1321</v>
@@ -23132,7 +23103,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>1323</v>
@@ -23143,7 +23114,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>601</v>
@@ -23154,7 +23125,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>1326</v>
@@ -23165,7 +23136,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>315</v>
@@ -23176,7 +23147,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="3" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>91</v>
@@ -23187,10 +23158,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="3" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>1330</v>
@@ -23198,7 +23169,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="3" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>164</v>
@@ -23209,7 +23180,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="3" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>1332</v>
@@ -23220,7 +23191,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="3" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>95</v>
@@ -23231,7 +23202,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>1335</v>
@@ -23242,7 +23213,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>1337</v>
@@ -23253,7 +23224,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>1339</v>
@@ -23264,7 +23235,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>1341</v>
@@ -23275,7 +23246,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>1343</v>
@@ -23286,7 +23257,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>1345</v>
@@ -23297,7 +23268,7 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>1326</v>
@@ -23308,7 +23279,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>1348</v>
@@ -23319,7 +23290,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>1350</v>
@@ -23330,7 +23301,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>1352</v>
@@ -23341,7 +23312,7 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>1354</v>
@@ -23352,7 +23323,7 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>1356</v>
@@ -23410,7 +23381,7 @@
         <v>588</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>1366</v>
@@ -23759,7 +23730,7 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>1420</v>
@@ -23770,7 +23741,7 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>1422</v>
@@ -23781,7 +23752,7 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>1424</v>
@@ -23792,7 +23763,7 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>1426</v>
@@ -23803,7 +23774,7 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>1428</v>
@@ -23814,7 +23785,7 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>1430</v>
@@ -23825,7 +23796,7 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>1432</v>
@@ -23836,7 +23807,7 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>1434</v>
@@ -23847,7 +23818,7 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>1436</v>
@@ -24045,7 +24016,7 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>164</v>
@@ -24056,7 +24027,7 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>1332</v>
@@ -24067,7 +24038,7 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>256</v>
@@ -24078,7 +24049,7 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>1467</v>
@@ -24089,7 +24060,7 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>164</v>
@@ -24100,7 +24071,7 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>1470</v>
@@ -24111,7 +24082,7 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>1332</v>
@@ -24122,7 +24093,7 @@
     </row>
     <row r="154" spans="1:3">
       <c r="A154" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>642</v>
@@ -24133,7 +24104,7 @@
     </row>
     <row r="155" spans="1:3">
       <c r="A155" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>645</v>
@@ -24144,7 +24115,7 @@
     </row>
     <row r="156" spans="1:3">
       <c r="A156" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>179</v>
@@ -24155,10 +24126,10 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>1476</v>
@@ -24166,7 +24137,7 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>1477</v>
@@ -24177,7 +24148,7 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>1479</v>
@@ -24188,7 +24159,7 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>1287</v>
@@ -24199,7 +24170,7 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>1482</v>
@@ -24210,7 +24181,7 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>1484</v>
@@ -24221,7 +24192,7 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>315</v>
@@ -24232,7 +24203,7 @@
     </row>
     <row r="164" spans="1:3">
       <c r="A164" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>648</v>
@@ -24243,7 +24214,7 @@
     </row>
     <row r="165" spans="1:3">
       <c r="A165" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>206</v>
@@ -24276,7 +24247,7 @@
     </row>
     <row r="168" spans="1:3">
       <c r="A168" s="3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>179</v>
@@ -24287,7 +24258,7 @@
     </row>
     <row r="169" spans="1:3">
       <c r="A169" s="3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>268</v>
@@ -24298,7 +24269,7 @@
     </row>
     <row r="170" spans="1:3">
       <c r="A170" s="3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>1494</v>
@@ -24309,7 +24280,7 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171" s="3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>1311</v>
@@ -24342,7 +24313,7 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>1501</v>
@@ -24353,7 +24324,7 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>1503</v>
@@ -24364,7 +24335,7 @@
     </row>
     <row r="176" spans="1:3">
       <c r="A176" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>1343</v>
@@ -24375,7 +24346,7 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>1326</v>
@@ -24386,7 +24357,7 @@
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>1507</v>
@@ -24397,7 +24368,7 @@
     </row>
     <row r="179" spans="1:3">
       <c r="A179" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>234</v>
@@ -24408,7 +24379,7 @@
     </row>
     <row r="180" spans="1:3">
       <c r="A180" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>164</v>
@@ -24419,7 +24390,7 @@
     </row>
     <row r="181" spans="1:3">
       <c r="A181" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>248</v>
@@ -24430,7 +24401,7 @@
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>1512</v>
@@ -24441,7 +24412,7 @@
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>256</v>
@@ -24452,7 +24423,7 @@
     </row>
     <row r="184" spans="1:3">
       <c r="A184" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>495</v>
@@ -24463,7 +24434,7 @@
     </row>
     <row r="185" spans="1:3">
       <c r="A185" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>1516</v>
@@ -24474,7 +24445,7 @@
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>1518</v>
@@ -24485,7 +24456,7 @@
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>1520</v>
@@ -24496,7 +24467,7 @@
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>1522</v>
@@ -24507,7 +24478,7 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>1524</v>
@@ -24518,7 +24489,7 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>1526</v>
@@ -24529,7 +24500,7 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>1528</v>
@@ -24540,7 +24511,7 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>1530</v>
@@ -24551,7 +24522,7 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>1532</v>
@@ -24562,7 +24533,7 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>1534</v>
@@ -24573,7 +24544,7 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>1352</v>
@@ -24584,7 +24555,7 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>1341</v>
@@ -24595,7 +24566,7 @@
     </row>
     <row r="197" spans="1:3">
       <c r="A197" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>1343</v>
@@ -24606,7 +24577,7 @@
     </row>
     <row r="198" spans="1:3">
       <c r="A198" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>1345</v>
@@ -24617,7 +24588,7 @@
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>1326</v>
@@ -24628,7 +24599,7 @@
     </row>
     <row r="200" spans="1:3">
       <c r="A200" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>1348</v>
@@ -24639,7 +24610,7 @@
     </row>
     <row r="201" spans="1:3">
       <c r="A201" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>1350</v>
@@ -24650,7 +24621,7 @@
     </row>
     <row r="202" spans="1:3">
       <c r="A202" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>1352</v>
@@ -24661,7 +24632,7 @@
     </row>
     <row r="203" spans="1:3">
       <c r="A203" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>1335</v>
@@ -24672,7 +24643,7 @@
     </row>
     <row r="204" spans="1:3">
       <c r="A204" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>1337</v>
@@ -24683,7 +24654,7 @@
     </row>
     <row r="205" spans="1:3">
       <c r="A205" s="3" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>1354</v>
@@ -24694,7 +24665,7 @@
     </row>
     <row r="206" spans="1:3">
       <c r="A206" s="3" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>1356</v>
@@ -24705,7 +24676,7 @@
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>1266</v>
@@ -24716,7 +24687,7 @@
     </row>
     <row r="208" spans="1:3">
       <c r="A208" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>87</v>
@@ -24727,10 +24698,10 @@
     </row>
     <row r="209" spans="1:3">
       <c r="A209" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>1547</v>
@@ -24738,7 +24709,7 @@
     </row>
     <row r="210" spans="1:3">
       <c r="A210" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>1287</v>
@@ -24749,7 +24720,7 @@
     </row>
     <row r="211" spans="1:3">
       <c r="A211" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>1303</v>
@@ -24804,7 +24775,7 @@
     </row>
     <row r="216" spans="1:3">
       <c r="A216" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>1558</v>
@@ -24815,7 +24786,7 @@
     </row>
     <row r="217" spans="1:3">
       <c r="A217" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>1560</v>
@@ -24826,7 +24797,7 @@
     </row>
     <row r="218" spans="1:3">
       <c r="A218" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>1562</v>
@@ -24837,7 +24808,7 @@
     </row>
     <row r="219" spans="1:3">
       <c r="A219" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>1564</v>
@@ -24848,7 +24819,7 @@
     </row>
     <row r="220" spans="1:3">
       <c r="A220" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>1566</v>
@@ -24925,7 +24896,7 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>1264</v>
@@ -24936,7 +24907,7 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>1268</v>
@@ -24947,7 +24918,7 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>1522</v>
@@ -24958,7 +24929,7 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>1578</v>
@@ -24969,7 +24940,7 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>1281</v>
@@ -24980,7 +24951,7 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>1285</v>
@@ -24991,7 +24962,7 @@
     </row>
     <row r="233" spans="1:3">
       <c r="A233" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>1526</v>
@@ -25002,7 +24973,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>1582</v>
@@ -25013,7 +24984,7 @@
     </row>
     <row r="235" spans="1:3">
       <c r="A235" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>1494</v>
@@ -25024,7 +24995,7 @@
     </row>
     <row r="236" spans="1:3">
       <c r="A236" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>1584</v>
@@ -25035,7 +25006,7 @@
     </row>
     <row r="237" spans="1:3">
       <c r="A237" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>1311</v>
@@ -25046,7 +25017,7 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>1352</v>
@@ -25057,10 +25028,10 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>1588</v>
@@ -25068,7 +25039,7 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>1589</v>
@@ -25079,7 +25050,7 @@
     </row>
     <row r="241" spans="1:3">
       <c r="A241" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>1591</v>
@@ -25090,7 +25061,7 @@
     </row>
     <row r="242" spans="1:3">
       <c r="A242" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>1593</v>
@@ -25101,7 +25072,7 @@
     </row>
     <row r="243" spans="1:3">
       <c r="A243" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>1595</v>
@@ -25126,7 +25097,7 @@
         <v>752</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>1598</v>
@@ -25134,7 +25105,7 @@
     </row>
     <row r="246" spans="1:3">
       <c r="A246" s="3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>1599</v>
@@ -25145,10 +25116,10 @@
     </row>
     <row r="247" spans="1:3">
       <c r="A247" s="3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>1601</v>
@@ -25156,7 +25127,7 @@
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>1602</v>
@@ -25167,7 +25138,7 @@
     </row>
     <row r="249" spans="1:3">
       <c r="A249" s="3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>149</v>
@@ -25178,7 +25149,7 @@
     </row>
     <row r="250" spans="1:3">
       <c r="A250" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>1605</v>
@@ -25189,7 +25160,7 @@
     </row>
     <row r="251" spans="1:3">
       <c r="A251" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>1607</v>
@@ -25200,7 +25171,7 @@
     </row>
     <row r="252" spans="1:3">
       <c r="A252" s="3" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>1609</v>
@@ -25211,10 +25182,10 @@
     </row>
     <row r="253" spans="1:3">
       <c r="A253" s="3" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>1547</v>
@@ -25222,7 +25193,7 @@
     </row>
     <row r="254" spans="1:3">
       <c r="A254" s="3" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>1611</v>
@@ -25310,7 +25281,7 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>1617</v>
@@ -25321,7 +25292,7 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>1619</v>
@@ -25332,7 +25303,7 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>1621</v>
@@ -25343,7 +25314,7 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>1623</v>
@@ -25354,7 +25325,7 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>1625</v>
@@ -25365,7 +25336,7 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>495</v>
@@ -25376,7 +25347,7 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>1516</v>
@@ -25387,7 +25358,7 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>1518</v>
@@ -25398,7 +25369,7 @@
     </row>
     <row r="270" spans="1:3">
       <c r="A270" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>1520</v>
@@ -25497,7 +25468,7 @@
     </row>
     <row r="279" spans="1:3">
       <c r="A279" s="3" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>1642</v>
@@ -25508,7 +25479,7 @@
     </row>
     <row r="280" spans="1:3">
       <c r="A280" s="3" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>1644</v>
@@ -25519,7 +25490,7 @@
     </row>
     <row r="281" spans="1:3">
       <c r="A281" s="3" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>1646</v>
@@ -25530,7 +25501,7 @@
     </row>
     <row r="282" spans="1:3">
       <c r="A282" s="3" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>419</v>
@@ -25541,7 +25512,7 @@
     </row>
     <row r="283" spans="1:3">
       <c r="A283" s="3" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>1646</v>
@@ -25739,7 +25710,7 @@
     </row>
     <row r="301" spans="1:3">
       <c r="A301" s="3" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>164</v>
@@ -25750,7 +25721,7 @@
     </row>
     <row r="302" spans="1:3">
       <c r="A302" s="3" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>1332</v>
@@ -25761,7 +25732,7 @@
     </row>
     <row r="303" spans="1:3">
       <c r="A303" s="3" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>1611</v>
@@ -25849,7 +25820,7 @@
     </row>
     <row r="311" spans="1:3">
       <c r="A311" s="3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>500</v>
@@ -25860,7 +25831,7 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312" s="3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>149</v>
@@ -25904,7 +25875,7 @@
     </row>
     <row r="316" spans="1:3">
       <c r="A316" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>235</v>
@@ -25915,7 +25886,7 @@
     </row>
     <row r="317" spans="1:3">
       <c r="A317" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>490</v>
@@ -25948,7 +25919,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>1379</v>
@@ -25959,7 +25930,7 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>1439</v>
@@ -25970,7 +25941,7 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>360</v>
@@ -25981,7 +25952,7 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>495</v>
@@ -25992,7 +25963,7 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>1708</v>
@@ -26047,7 +26018,7 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>527</v>
@@ -26058,7 +26029,7 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>1332</v>
@@ -26069,7 +26040,7 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>535</v>
@@ -26080,7 +26051,7 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>1194</v>
@@ -26091,7 +26062,7 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>1718</v>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6155" uniqueCount="2057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6156" uniqueCount="2058">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -6201,6 +6201,9 @@
   </si>
   <si>
     <t>The admin module instrumented (campbooks-cloud#331): 2 instance-wide events for an administrator's profile granted (created or given more permissions) and revoked (permissions taken away or the profile removed) by the server's admin command, as system; record profile and enum permission; no Coverage rows (the module serves no operation and runs no job, schedule or handler).</t>
+  </si>
+  <si>
+    <t>#662</t>
   </si>
 </sst>
 </file>
@@ -28976,6 +28979,9 @@
       <c r="C9" s="3" t="s">
         <v>2056</v>
       </c>
+      <c r="D9" s="3" t="s">
+        <v>2057</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D9"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7082" uniqueCount="2333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7083" uniqueCount="2334">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -7029,6 +7029,9 @@
   </si>
   <si>
     <t>The schedule module instrumented (campbooks-cloud#349): 16 events for events of a calendar created, edited (which fields), moved (the times before), cancelled by a later email, deleted, restored, answered (the answer before), pushed to a provider calendar and unpushed, calendars added by a grant, enabled, disabled, recoloured and removed with their connection, settings updated (which settings), and one summary per batch of a provider's changes applied (counts); records calendar_event, calendar_event_times, calendar and settings; Coverage for every operation, job and handler of the module, apply_outcome and release_delete naming connectors.calendar_change_completed.</t>
+  </si>
+  <si>
+    <t>#663</t>
   </si>
 </sst>
 </file>
@@ -33089,6 +33092,9 @@
       <c r="C10" s="3" t="s">
         <v>2332</v>
       </c>
+      <c r="D10" s="3" t="s">
+        <v>2333</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6608" uniqueCount="2187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6609" uniqueCount="2188">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -6591,6 +6591,9 @@
   </si>
   <si>
     <t>The tasks module instrumented (campbooks-cloud#340): 8 events for a task created (by a member, or by Scout from an ask), edited (which fields), its due date changed (the date before), planned (the plan before), done, not needed, reopened (the state before) and reassigned (handed off or taken back, with the member who had it); records task, task_due and task_plan; Coverage for every operation, job and handler of the module.</t>
+  </si>
+  <si>
+    <t>#665</t>
   </si>
 </sst>
 </file>
@@ -30972,6 +30975,9 @@
       <c r="C10" s="3" t="s">
         <v>2186</v>
       </c>
+      <c r="D10" s="3" t="s">
+        <v>2187</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D10"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7209" uniqueCount="2389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7210" uniqueCount="2390">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -7197,6 +7197,9 @@
   </si>
   <si>
     <t>Coverage required with no baseline (campbooks-cloud#332): 2 connectors events for an IMAP mailbox's address check asked for again and its message sent or not (with why); Coverage rows for connectors.check_address, connectors.send_address_check and the kernel's maintenance schedules and change-feed sequencer.</t>
+  </si>
+  <si>
+    <t>#666</t>
   </si>
 </sst>
 </file>
@@ -33727,6 +33730,9 @@
       <c r="C11" s="3" t="s">
         <v>2388</v>
       </c>
+      <c r="D11" s="3" t="s">
+        <v>2389</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D11"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Actors!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$245</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$426</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$321</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8087" uniqueCount="2639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8090" uniqueCount="2641">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -7022,6 +7022,12 @@
     <t>projection of conversations.message_sent: the conversation's entries in the index refreshed</t>
   </si>
   <si>
+    <t>search.on_page_changed</t>
+  </si>
+  <si>
+    <t>projection of pages.page_changed: the page's entry in the index refreshed (removed when trashed or gone)</t>
+  </si>
+  <si>
     <t>search.schedule_workspace_purge</t>
   </si>
   <si>
@@ -7943,7 +7949,7 @@
     <t>#672</t>
   </si>
   <si>
-    <t>Coverage required with no baseline (campbooks-cloud#332): 2 connectors events for an IMAP mailbox's address check asked for again and its message sent or not (with why); Coverage rows for connectors.check_address, connectors.send_address_check and the kernel's maintenance schedules and change-feed sequencer.</t>
+    <t>Coverage required with no baseline (campbooks-cloud#332): 2 connectors events for an IMAP mailbox's address check asked for again and its message sent or not (with why); Coverage rows for connectors.check_address, connectors.send_address_check, search.on_page_changed and the kernel's maintenance schedules and change-feed sequencer.</t>
   </si>
   <si>
     <t>#666</t>
@@ -34721,7 +34727,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D244"/>
+  <dimension ref="A1:D245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -35224,7 +35230,7 @@
       <c r="B45" s="3" t="s">
         <v>2332</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>2333</v>
       </c>
     </row>
@@ -35236,7 +35242,7 @@
         <v>2334</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>620</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -35244,10 +35250,10 @@
         <v>2261</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>2336</v>
+        <v>620</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -35258,7 +35264,7 @@
         <v>2337</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>615</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -35266,10 +35272,10 @@
         <v>2261</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>2338</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>2265</v>
+        <v>2339</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -35277,10 +35283,10 @@
         <v>2261</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>2339</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>658</v>
+        <v>2340</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>2265</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -35288,21 +35294,21 @@
         <v>2261</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="3" t="s">
-        <v>484</v>
+        <v>2261</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>2341</v>
-      </c>
-      <c r="D52" s="3" t="s">
         <v>2342</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -35345,8 +35351,8 @@
       <c r="B56" s="3" t="s">
         <v>2349</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>144</v>
+      <c r="D56" s="3" t="s">
+        <v>2350</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -35354,10 +35360,10 @@
         <v>484</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>2351</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -35379,7 +35385,7 @@
         <v>2354</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>295</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -35387,10 +35393,10 @@
         <v>484</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>359</v>
+        <v>295</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -35398,10 +35404,10 @@
         <v>484</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>2356</v>
-      </c>
-      <c r="D61" s="3" t="s">
         <v>2357</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -35411,8 +35417,8 @@
       <c r="B62" s="3" t="s">
         <v>2358</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>271</v>
+      <c r="D62" s="3" t="s">
+        <v>2359</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -35420,10 +35426,10 @@
         <v>484</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>300</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -35431,10 +35437,10 @@
         <v>484</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>2360</v>
-      </c>
-      <c r="D64" s="3" t="s">
         <v>2361</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -35466,8 +35472,8 @@
       <c r="B67" s="3" t="s">
         <v>2366</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>305</v>
+      <c r="D67" s="3" t="s">
+        <v>2367</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -35475,7 +35481,7 @@
         <v>484</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>305</v>
@@ -35486,10 +35492,10 @@
         <v>484</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>2368</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>2357</v>
+        <v>2369</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -35497,10 +35503,10 @@
         <v>484</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>2369</v>
-      </c>
-      <c r="C70" s="3" t="s">
         <v>2370</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>2359</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -35510,7 +35516,7 @@
       <c r="B71" s="3" t="s">
         <v>2371</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>2372</v>
       </c>
     </row>
@@ -35533,7 +35539,7 @@
         <v>2375</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>2357</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -35541,10 +35547,10 @@
         <v>484</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2377</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -35598,8 +35604,8 @@
       <c r="B79" s="3" t="s">
         <v>2386</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>149</v>
+      <c r="D79" s="3" t="s">
+        <v>2387</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -35607,10 +35613,10 @@
         <v>484</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>2387</v>
-      </c>
-      <c r="D80" s="3" t="s">
         <v>2388</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -35653,126 +35659,126 @@
       <c r="B84" s="3" t="s">
         <v>2395</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>695</v>
+      <c r="D84" s="3" t="s">
+        <v>2396</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="3" t="s">
-        <v>2396</v>
+        <v>484</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>2397</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>2398</v>
+        <v>695</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>2399</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>2400</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>2401</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>85</v>
+      <c r="D87" s="3" t="s">
+        <v>2402</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>2403</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>2404</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>89</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>2398</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>93</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>121</v>
@@ -35780,10 +35786,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>121</v>
@@ -35791,10 +35797,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>121</v>
@@ -35802,10 +35808,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>121</v>
@@ -35813,10 +35819,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>121</v>
@@ -35824,10 +35830,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>121</v>
@@ -35835,10 +35841,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>121</v>
@@ -35846,10 +35852,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>121</v>
@@ -35857,10 +35863,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>121</v>
@@ -35868,54 +35874,54 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>2421</v>
+        <v>132</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>2422</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="C106" s="3" t="s">
         <v>2423</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>2424</v>
       </c>
-      <c r="C107" s="3" t="s">
-        <v>121</v>
+      <c r="D107" s="3" t="s">
+        <v>2425</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>121</v>
@@ -35923,513 +35929,513 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>2428</v>
+        <v>137</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>2429</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>168</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>2430</v>
-      </c>
-      <c r="D112" s="3" t="s">
         <v>2431</v>
       </c>
-    </row>
-    <row r="113" spans="1:3">
+      <c r="C112" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
       <c r="A113" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>2432</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="D113" s="3" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>2434</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>2433</v>
-      </c>
-      <c r="C114" s="3" t="s">
+    <row r="115" spans="1:4">
+      <c r="A115" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>2435</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>2434</v>
-      </c>
-      <c r="C115" s="3" t="s">
+    <row r="116" spans="1:4">
+      <c r="A116" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>2436</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>2435</v>
-      </c>
-      <c r="C116" s="3" t="s">
+    <row r="117" spans="1:4">
+      <c r="A117" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>2437</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>2436</v>
-      </c>
-      <c r="C117" s="3" t="s">
+    <row r="118" spans="1:4">
+      <c r="A118" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>2438</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>2437</v>
-      </c>
-      <c r="C118" s="3" t="s">
+    <row r="119" spans="1:4">
+      <c r="A119" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>2439</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>2438</v>
-      </c>
-      <c r="C119" s="3" t="s">
+    <row r="120" spans="1:4">
+      <c r="A120" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>2440</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>2439</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>2440</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:4">
       <c r="A121" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>2441</v>
       </c>
       <c r="C121" s="3" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>2443</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>2442</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>2443</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:4">
       <c r="A123" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>2444</v>
       </c>
       <c r="C123" s="3" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>2446</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>2445</v>
-      </c>
-      <c r="C124" s="3" t="s">
+    <row r="125" spans="1:4">
+      <c r="A125" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>2447</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>2446</v>
-      </c>
-      <c r="C125" s="3" t="s">
+    <row r="126" spans="1:4">
+      <c r="A126" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>2448</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>2447</v>
-      </c>
-      <c r="C126" s="3" t="s">
+    <row r="127" spans="1:4">
+      <c r="A127" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>2449</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>2448</v>
-      </c>
-      <c r="C127" s="3" t="s">
+    <row r="128" spans="1:4">
+      <c r="A128" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>2450</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>213</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="3" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>2449</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>2452</v>
-      </c>
-      <c r="D131" s="3" t="s">
         <v>2453</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>2454</v>
       </c>
-      <c r="C132" s="3" t="s">
-        <v>233</v>
+      <c r="D132" s="3" t="s">
+        <v>2455</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>352</v>
+        <v>233</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>217</v>
+        <v>316</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>309</v>
+        <v>217</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>2461</v>
+        <v>320</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>2462</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>267</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>329</v>
+        <v>267</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>221</v>
+        <v>329</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>2465</v>
-      </c>
-      <c r="D142" s="3" t="s">
         <v>2466</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>2467</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B144" s="3" t="s">
+        <v>2469</v>
+      </c>
+      <c r="D144" s="3" t="s">
         <v>2468</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>284</v>
+        <v>249</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>2474</v>
+        <v>284</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>2475</v>
       </c>
-      <c r="D150" s="3" t="s">
-        <v>2466</v>
+      <c r="C150" s="3" t="s">
+        <v>2476</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>2477</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>377</v>
+        <v>2478</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>2468</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>2480</v>
+        <v>381</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>2481</v>
@@ -36440,54 +36446,54 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>2483</v>
       </c>
-      <c r="D156" s="3" t="s">
+      <c r="C156" s="3" t="s">
         <v>2484</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>2485</v>
       </c>
-      <c r="C157" s="3" t="s">
+      <c r="D157" s="3" t="s">
         <v>2486</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>2487</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>426</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>454</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>454</v>
@@ -36495,18 +36501,18 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>2491</v>
+        <v>454</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>2492</v>
@@ -36517,7 +36523,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>2494</v>
@@ -36528,139 +36534,139 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>2496</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>417</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>434</v>
+        <v>385</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>390</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>438</v>
+        <v>390</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>478</v>
+        <v>438</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>441</v>
+        <v>478</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>410</v>
+        <v>450</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>2507</v>
-      </c>
-      <c r="D175" s="3" t="s">
         <v>2508</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>2509</v>
@@ -36671,7 +36677,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>2511</v>
@@ -36682,7 +36688,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>2513</v>
@@ -36693,7 +36699,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>2515</v>
@@ -36704,205 +36710,205 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>2517</v>
       </c>
-      <c r="C180" s="3" t="s">
+      <c r="D180" s="3" t="s">
         <v>2518</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>2519</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>499</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>2524</v>
-      </c>
-      <c r="D186" s="3" t="s">
         <v>2525</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>2526</v>
       </c>
-      <c r="C187" s="3" t="s">
-        <v>524</v>
+      <c r="D187" s="3" t="s">
+        <v>2527</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>2529</v>
-      </c>
-      <c r="D190" s="3" t="s">
         <v>2530</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>2531</v>
       </c>
-      <c r="C191" s="3" t="s">
-        <v>550</v>
+      <c r="D191" s="3" t="s">
+        <v>2532</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>2538</v>
+        <v>574</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>2539</v>
@@ -36913,73 +36919,73 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>2541</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>589</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>482</v>
+        <v>589</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>2546</v>
-      </c>
-      <c r="D204" s="3" t="s">
         <v>2547</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>2548</v>
@@ -36990,29 +36996,29 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>2550</v>
       </c>
-      <c r="C206" s="3" t="s">
-        <v>598</v>
+      <c r="D206" s="3" t="s">
+        <v>2551</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>2552</v>
+        <v>598</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>2553</v>
@@ -37023,197 +37029,197 @@
     </row>
     <row r="209" spans="1:3">
       <c r="A209" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>2555</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>615</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>2557</v>
+        <v>615</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>2558</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>628</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>2563</v>
+        <v>632</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>2564</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>645</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>676</v>
+        <v>645</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>685</v>
+        <v>664</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>654</v>
+        <v>673</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>2571</v>
+        <v>654</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>2572</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>692</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>639</v>
+        <v>692</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>650</v>
@@ -37221,24 +37227,24 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="3" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>698</v>
+        <v>650</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="3" t="s">
-        <v>532</v>
+        <v>2398</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>2577</v>
-      </c>
-      <c r="D228" s="3" t="s">
         <v>2578</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -37271,7 +37277,7 @@
         <v>2583</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>2578</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -37279,10 +37285,10 @@
         <v>532</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -37290,10 +37296,10 @@
         <v>532</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -37301,10 +37307,10 @@
         <v>532</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>2586</v>
-      </c>
-      <c r="C234" s="3" t="s">
-        <v>478</v>
+        <v>2587</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>2580</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -37312,10 +37318,10 @@
         <v>532</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>2587</v>
-      </c>
-      <c r="D235" s="3" t="s">
         <v>2588</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -37417,8 +37423,19 @@
         <v>2606</v>
       </c>
     </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>2607</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>2608</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D244"/>
+  <autoFilter ref="A1:D245"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not in the list" error="Pick one of: operation, job, schedule, handler." promptTitle="Kind" prompt="operation, job, schedule or handler" sqref="A2:A2001">
       <formula1>"operation,job,schedule,handler"</formula1>
@@ -37443,198 +37460,198 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2608</v>
+        <v>2610</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2609</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>2610</v>
+        <v>2612</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2611</v>
+        <v>2613</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2612</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>2613</v>
+        <v>2615</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2614</v>
+        <v>2616</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2615</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>2613</v>
+        <v>2615</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2616</v>
+        <v>2618</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2617</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>2613</v>
+        <v>2615</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2618</v>
+        <v>2620</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2619</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2621</v>
+        <v>2623</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2622</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="B7" s="3">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2623</v>
+        <v>2625</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2624</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="B8" s="3">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2625</v>
+        <v>2627</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2626</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>2627</v>
+        <v>2629</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2628</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2629</v>
+        <v>2631</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2630</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>2631</v>
+        <v>2633</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2632</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2633</v>
+        <v>2635</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2634</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>2635</v>
+        <v>2637</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2636</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="B14" s="3">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>2637</v>
+        <v>2639</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2638</v>
+        <v>2640</v>
       </c>
     </row>
   </sheetData>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Actors!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$249</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$426</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$321</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8090" uniqueCount="2641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8105" uniqueCount="2649">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Plan version</t>
   </si>
   <si>
-    <t>13 (2026-10-25)</t>
+    <t>14 (2026-10-25)</t>
   </si>
   <si>
     <t>What this is</t>
@@ -6848,6 +6848,12 @@
     <t>projection of conversations.need_changed: one item per conversation's need (a new message from the sender ends its Laters)</t>
   </si>
   <si>
+    <t>attention.project_invitation</t>
+  </si>
+  <si>
+    <t>projection of schedule.invitation_changed: one Decide item per invitation awaiting an answer</t>
+  </si>
+  <si>
     <t>attention.project_task</t>
   </si>
   <si>
@@ -7190,6 +7196,12 @@
     <t>maintenance: a deleted workspace's pages and history deleted; the deletion is tracked by workspaces</t>
   </si>
   <si>
+    <t>schedule.announce_invitations</t>
+  </si>
+  <si>
+    <t>maintenance, no action of anyone: invitations stored before announced once</t>
+  </si>
+  <si>
     <t>schedule.purge_workspace</t>
   </si>
   <si>
@@ -7199,6 +7211,9 @@
     <t>schedule.release_delete</t>
   </si>
   <si>
+    <t>schedule.release_response</t>
+  </si>
+  <si>
     <t>schedule.retag_bindings</t>
   </si>
   <si>
@@ -7859,6 +7874,9 @@
     <t>maintenance, no action of anyone: only enqueues the purge of each workspace's old trash, which tracks nothing</t>
   </si>
   <si>
+    <t>schedule.dispatch_invitation_backfills</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -7953,6 +7971,12 @@
   </si>
   <si>
     <t>#666</t>
+  </si>
+  <si>
+    <t>Invitations awaiting an answer on Home (campbooks-cloud#360): Coverage for schedule.release_response (connectors.calendar_change_completed), schedule.dispatch_invitation_backfills, schedule.announce_invitations and attention.project_invitation; no new event.</t>
+  </si>
+  <si>
+    <t>#676</t>
   </si>
 </sst>
 </file>
@@ -34727,7 +34751,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D245"/>
+  <dimension ref="A1:D249"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -34824,7 +34848,7 @@
         <v>2274</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2265</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -34832,10 +34856,10 @@
         <v>2261</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2275</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>132</v>
+        <v>2276</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>2265</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -34843,7 +34867,7 @@
         <v>2261</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>132</v>
@@ -34854,10 +34878,10 @@
         <v>2261</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>2277</v>
-      </c>
-      <c r="D11" s="3" t="s">
         <v>2278</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -34878,8 +34902,8 @@
       <c r="B13" s="3" t="s">
         <v>2281</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>149</v>
+      <c r="D13" s="3" t="s">
+        <v>2282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -34887,10 +34911,10 @@
         <v>2261</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2282</v>
-      </c>
-      <c r="D14" s="3" t="s">
         <v>2283</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -34900,8 +34924,8 @@
       <c r="B15" s="3" t="s">
         <v>2284</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>168</v>
+      <c r="D15" s="3" t="s">
+        <v>2285</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -34909,10 +34933,10 @@
         <v>2261</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2285</v>
-      </c>
-      <c r="D16" s="3" t="s">
         <v>2286</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -34922,8 +34946,8 @@
       <c r="B17" s="3" t="s">
         <v>2287</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>292</v>
+      <c r="D17" s="3" t="s">
+        <v>2288</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -34931,10 +34955,10 @@
         <v>2261</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -34942,10 +34966,10 @@
         <v>2261</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -34953,10 +34977,10 @@
         <v>2261</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2290</v>
-      </c>
-      <c r="D20" s="3" t="s">
         <v>2291</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -34988,7 +35012,7 @@
       <c r="B23" s="3" t="s">
         <v>2296</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>2297</v>
       </c>
     </row>
@@ -34999,7 +35023,7 @@
       <c r="B24" s="3" t="s">
         <v>2298</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>2299</v>
       </c>
     </row>
@@ -35011,7 +35035,7 @@
         <v>2300</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2265</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -35019,10 +35043,10 @@
         <v>2261</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2301</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>398</v>
+        <v>2302</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>2265</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -35030,10 +35054,10 @@
         <v>2261</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>2302</v>
-      </c>
-      <c r="D27" s="3" t="s">
         <v>2303</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -35065,7 +35089,7 @@
       <c r="B30" s="3" t="s">
         <v>2308</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>2309</v>
       </c>
     </row>
@@ -35076,7 +35100,7 @@
       <c r="B31" s="3" t="s">
         <v>2310</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>2311</v>
       </c>
     </row>
@@ -35088,7 +35112,7 @@
         <v>2312</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2265</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -35096,10 +35120,10 @@
         <v>2261</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>2313</v>
-      </c>
-      <c r="C33" s="3" t="s">
         <v>2314</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>2265</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -35110,7 +35134,7 @@
         <v>2315</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>585</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -35118,10 +35142,10 @@
         <v>2261</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>149</v>
+        <v>585</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -35129,10 +35153,10 @@
         <v>2261</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>582</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -35140,10 +35164,10 @@
         <v>2261</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>2318</v>
-      </c>
-      <c r="D37" s="3" t="s">
         <v>2319</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -35153,8 +35177,8 @@
       <c r="B38" s="3" t="s">
         <v>2320</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>531</v>
+      <c r="D38" s="3" t="s">
+        <v>2321</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -35162,10 +35186,10 @@
         <v>2261</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>2321</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>2265</v>
+        <v>2322</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -35173,10 +35197,10 @@
         <v>2261</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>2323</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -35241,7 +35265,7 @@
       <c r="B46" s="3" t="s">
         <v>2334</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>2335</v>
       </c>
     </row>
@@ -35253,7 +35277,7 @@
         <v>2336</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>620</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -35261,10 +35285,10 @@
         <v>2261</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>2338</v>
+        <v>620</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -35275,7 +35299,7 @@
         <v>2339</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>615</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -35283,10 +35307,10 @@
         <v>2261</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>2340</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>2265</v>
+        <v>2341</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -35294,10 +35318,10 @@
         <v>2261</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>2341</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>658</v>
+        <v>2342</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>2265</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -35305,21 +35329,21 @@
         <v>2261</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="3" t="s">
-        <v>484</v>
+        <v>2261</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>2343</v>
-      </c>
-      <c r="D53" s="3" t="s">
         <v>2344</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -35362,8 +35386,8 @@
       <c r="B57" s="3" t="s">
         <v>2351</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>144</v>
+      <c r="D57" s="3" t="s">
+        <v>2352</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -35371,10 +35395,10 @@
         <v>484</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>2353</v>
+        <v>144</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -35396,7 +35420,7 @@
         <v>2356</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>295</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -35404,10 +35428,10 @@
         <v>484</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>359</v>
+        <v>295</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -35415,10 +35439,10 @@
         <v>484</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>2358</v>
-      </c>
-      <c r="D62" s="3" t="s">
         <v>2359</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -35428,8 +35452,8 @@
       <c r="B63" s="3" t="s">
         <v>2360</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>271</v>
+      <c r="D63" s="3" t="s">
+        <v>2361</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -35437,10 +35461,10 @@
         <v>484</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>300</v>
+        <v>271</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -35448,10 +35472,10 @@
         <v>484</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>2362</v>
-      </c>
-      <c r="D65" s="3" t="s">
         <v>2363</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -35483,8 +35507,8 @@
       <c r="B68" s="3" t="s">
         <v>2368</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>305</v>
+      <c r="D68" s="3" t="s">
+        <v>2369</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -35492,7 +35516,7 @@
         <v>484</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>305</v>
@@ -35503,10 +35527,10 @@
         <v>484</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>2370</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>2359</v>
+        <v>2371</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -35514,10 +35538,10 @@
         <v>484</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>2371</v>
-      </c>
-      <c r="C71" s="3" t="s">
         <v>2372</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>2361</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -35527,7 +35551,7 @@
       <c r="B72" s="3" t="s">
         <v>2373</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>2374</v>
       </c>
     </row>
@@ -35550,7 +35574,7 @@
         <v>2377</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2359</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -35558,10 +35582,10 @@
         <v>484</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>2379</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -35615,8 +35639,8 @@
       <c r="B80" s="3" t="s">
         <v>2388</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>149</v>
+      <c r="D80" s="3" t="s">
+        <v>2389</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -35624,10 +35648,10 @@
         <v>484</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -35635,10 +35659,10 @@
         <v>484</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>2391</v>
-      </c>
-      <c r="D82" s="3" t="s">
         <v>2392</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -35648,8 +35672,8 @@
       <c r="B83" s="3" t="s">
         <v>2393</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>2394</v>
+      <c r="C83" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -35657,10 +35681,10 @@
         <v>484</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>2394</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>2395</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>2396</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -35668,48 +35692,48 @@
         <v>484</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>2396</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>2397</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>2398</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="D86" s="3" t="s">
         <v>2399</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>2400</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="3" t="s">
-        <v>2398</v>
+        <v>484</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>2400</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>2401</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>2402</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="3" t="s">
-        <v>2398</v>
+        <v>484</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>85</v>
+        <v>695</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>2404</v>
@@ -35720,98 +35744,98 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>2406</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>89</v>
+      <c r="D90" s="3" t="s">
+        <v>2407</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>2400</v>
+        <v>85</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>93</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>117</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>121</v>
@@ -35819,10 +35843,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>121</v>
@@ -35830,10 +35854,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>121</v>
@@ -35841,10 +35865,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>121</v>
@@ -35852,10 +35876,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>121</v>
@@ -35863,10 +35887,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>121</v>
@@ -35874,10 +35898,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>121</v>
@@ -35885,1173 +35909,1173 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>2423</v>
+        <v>121</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>2424</v>
-      </c>
-      <c r="D107" s="3" t="s">
         <v>2425</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>2426</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>2427</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>121</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>2428</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>137</v>
+        <v>2429</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>2430</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>2430</v>
+        <v>121</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>2432</v>
-      </c>
-      <c r="D113" s="3" t="s">
         <v>2433</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>2434</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>173</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>2436</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>348</v>
+        <v>2437</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>2438</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>279</v>
+        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>2442</v>
+        <v>279</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>253</v>
+        <v>343</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>2445</v>
+        <v>312</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>2446</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>340</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>324</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>213</v>
+        <v>259</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>237</v>
+        <v>324</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>209</v>
+        <v>363</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>2454</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>2455</v>
+        <v>2456</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>352</v>
+        <v>241</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>2458</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>316</v>
+        <v>2459</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>2460</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>2463</v>
+        <v>217</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>267</v>
+        <v>309</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>221</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>2467</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>2468</v>
+        <v>2469</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>2469</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>2468</v>
+        <v>2470</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>2471</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>229</v>
+        <v>2472</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>2473</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>2472</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>245</v>
+        <v>2474</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>2473</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>284</v>
+        <v>229</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>2476</v>
+        <v>245</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>2477</v>
-      </c>
-      <c r="D151" s="3" t="s">
-        <v>2468</v>
+        <v>2478</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>2478</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>2468</v>
+        <v>2479</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>377</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>2480</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>381</v>
+        <v>2482</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>2473</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>2481</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>2482</v>
+        <v>2483</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>2473</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>2484</v>
+        <v>377</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>2485</v>
       </c>
-      <c r="D157" s="3" t="s">
-        <v>2486</v>
+      <c r="C157" s="3" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B158" s="3" t="s">
+        <v>2486</v>
+      </c>
+      <c r="C158" s="3" t="s">
         <v>2487</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>2488</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B159" s="3" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C159" s="3" t="s">
         <v>2489</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>2490</v>
       </c>
-      <c r="C160" s="3" t="s">
+      <c r="D160" s="3" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>2492</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>2494</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>2495</v>
+      </c>
+      <c r="C163" s="3" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="161" spans="1:4">
-      <c r="A161" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>2491</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4">
-      <c r="A162" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>2492</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>2493</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4">
-      <c r="A163" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>2494</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>2495</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:3">
       <c r="A164" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>2496</v>
       </c>
       <c r="C164" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B165" s="3" t="s">
         <v>2497</v>
       </c>
-    </row>
-    <row r="165" spans="1:4">
-      <c r="A165" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B165" s="3" t="s">
+      <c r="C165" s="3" t="s">
         <v>2498</v>
       </c>
-      <c r="C165" s="3" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
+    </row>
+    <row r="166" spans="1:3">
       <c r="A166" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>2499</v>
       </c>
       <c r="C166" s="3" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>2501</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>2504</v>
+      </c>
+      <c r="C169" s="3" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
-      <c r="A167" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>2500</v>
-      </c>
-      <c r="C167" s="3" t="s">
+    <row r="170" spans="1:3">
+      <c r="A170" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>2505</v>
+      </c>
+      <c r="C170" s="3" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="168" spans="1:4">
-      <c r="A168" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>2501</v>
-      </c>
-      <c r="C168" s="3" t="s">
+    <row r="171" spans="1:3">
+      <c r="A171" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>2506</v>
+      </c>
+      <c r="C171" s="3" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="169" spans="1:4">
-      <c r="A169" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>2502</v>
-      </c>
-      <c r="C169" s="3" t="s">
+    <row r="172" spans="1:3">
+      <c r="A172" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>2507</v>
+      </c>
+      <c r="C172" s="3" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="170" spans="1:4">
-      <c r="A170" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>2503</v>
-      </c>
-      <c r="C170" s="3" t="s">
+    <row r="173" spans="1:3">
+      <c r="A173" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>2508</v>
+      </c>
+      <c r="C173" s="3" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="171" spans="1:4">
-      <c r="A171" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>2504</v>
-      </c>
-      <c r="C171" s="3" t="s">
+    <row r="174" spans="1:3">
+      <c r="A174" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>2509</v>
+      </c>
+      <c r="C174" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="172" spans="1:4">
-      <c r="A172" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>2505</v>
-      </c>
-      <c r="C172" s="3" t="s">
+    <row r="175" spans="1:3">
+      <c r="A175" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>2510</v>
+      </c>
+      <c r="C175" s="3" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="173" spans="1:4">
-      <c r="A173" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>2506</v>
-      </c>
-      <c r="C173" s="3" t="s">
+    <row r="176" spans="1:3">
+      <c r="A176" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>2511</v>
+      </c>
+      <c r="C176" s="3" t="s">
         <v>410</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4">
-      <c r="A174" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>2507</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4">
-      <c r="A175" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>2508</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4">
-      <c r="A176" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>2509</v>
-      </c>
-      <c r="D176" s="3" t="s">
-        <v>2510</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>2511</v>
-      </c>
-      <c r="D177" s="3" t="s">
         <v>2512</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>2513</v>
       </c>
-      <c r="D178" s="3" t="s">
-        <v>2514</v>
+      <c r="C178" s="3" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B179" s="3" t="s">
+        <v>2514</v>
+      </c>
+      <c r="D179" s="3" t="s">
         <v>2515</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>2516</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B180" s="3" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D180" s="3" t="s">
         <v>2517</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>2518</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B181" s="3" t="s">
+        <v>2518</v>
+      </c>
+      <c r="D181" s="3" t="s">
         <v>2519</v>
-      </c>
-      <c r="C181" s="3" t="s">
-        <v>2520</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B182" s="3" t="s">
+        <v>2520</v>
+      </c>
+      <c r="D182" s="3" t="s">
         <v>2521</v>
-      </c>
-      <c r="C182" s="3" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>2522</v>
       </c>
-      <c r="C183" s="3" t="s">
-        <v>510</v>
+      <c r="D183" s="3" t="s">
+        <v>2523</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>513</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>2526</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>2527</v>
+        <v>2528</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>2530</v>
-      </c>
-      <c r="C190" s="3" t="s">
-        <v>506</v>
+        <v>2531</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>2532</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>2531</v>
-      </c>
-      <c r="D191" s="3" t="s">
-        <v>2532</v>
+        <v>2533</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>550</v>
+        <v>527</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>554</v>
+        <v>506</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>2535</v>
-      </c>
-      <c r="C194" s="3" t="s">
-        <v>563</v>
+        <v>2536</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>2537</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>571</v>
+        <v>554</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>2540</v>
+        <v>567</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>2542</v>
+        <v>571</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>2543</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>589</v>
+        <v>574</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>2544</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>482</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>495</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>487</v>
+        <v>589</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>2548</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>2549</v>
+        <v>2550</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>2550</v>
-      </c>
-      <c r="D206" s="3" t="s">
         <v>2551</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>2552</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>598</v>
+        <v>491</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>2553</v>
       </c>
-      <c r="C208" s="3" t="s">
+      <c r="D208" s="3" t="s">
         <v>2554</v>
       </c>
     </row>
-    <row r="209" spans="1:3">
+    <row r="209" spans="1:4">
       <c r="A209" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>2555</v>
       </c>
-      <c r="C209" s="3" t="s">
+      <c r="D209" s="3" t="s">
         <v>2556</v>
       </c>
     </row>
-    <row r="210" spans="1:3">
+    <row r="210" spans="1:4">
       <c r="A210" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>2557</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
       <c r="A211" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>2558</v>
@@ -37060,224 +37084,224 @@
         <v>2559</v>
       </c>
     </row>
-    <row r="212" spans="1:3">
+    <row r="212" spans="1:4">
       <c r="A212" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>2560</v>
       </c>
       <c r="C212" s="3" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>2562</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>2565</v>
+      </c>
+      <c r="C215" s="3" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="213" spans="1:3">
-      <c r="A213" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B213" s="3" t="s">
-        <v>2561</v>
-      </c>
-      <c r="C213" s="3" t="s">
+    <row r="216" spans="1:4">
+      <c r="A216" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>2566</v>
+      </c>
+      <c r="C216" s="3" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="214" spans="1:3">
-      <c r="A214" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>2562</v>
-      </c>
-      <c r="C214" s="3" t="s">
+    <row r="217" spans="1:4">
+      <c r="A217" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>2567</v>
+      </c>
+      <c r="C217" s="3" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="215" spans="1:3">
-      <c r="A215" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B215" s="3" t="s">
-        <v>2563</v>
-      </c>
-      <c r="C215" s="3" t="s">
+    <row r="218" spans="1:4">
+      <c r="A218" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>2568</v>
+      </c>
+      <c r="C218" s="3" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="216" spans="1:3">
-      <c r="A216" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B216" s="3" t="s">
-        <v>2564</v>
-      </c>
-      <c r="C216" s="3" t="s">
-        <v>2565</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3">
-      <c r="A217" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B217" s="3" t="s">
-        <v>2566</v>
-      </c>
-      <c r="C217" s="3" t="s">
+    <row r="219" spans="1:4">
+      <c r="A219" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>2569</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>2571</v>
+      </c>
+      <c r="C220" s="3" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="218" spans="1:3">
-      <c r="A218" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>2567</v>
-      </c>
-      <c r="C218" s="3" t="s">
+    <row r="221" spans="1:4">
+      <c r="A221" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>2572</v>
+      </c>
+      <c r="C221" s="3" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="219" spans="1:3">
-      <c r="A219" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B219" s="3" t="s">
-        <v>2568</v>
-      </c>
-      <c r="C219" s="3" t="s">
+    <row r="222" spans="1:4">
+      <c r="A222" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C222" s="3" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="220" spans="1:3">
-      <c r="A220" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B220" s="3" t="s">
-        <v>2569</v>
-      </c>
-      <c r="C220" s="3" t="s">
+    <row r="223" spans="1:4">
+      <c r="A223" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>2574</v>
+      </c>
+      <c r="C223" s="3" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="221" spans="1:3">
-      <c r="A221" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B221" s="3" t="s">
-        <v>2570</v>
-      </c>
-      <c r="C221" s="3" t="s">
+    <row r="224" spans="1:4">
+      <c r="A224" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C224" s="3" t="s">
         <v>673</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3">
-      <c r="A222" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>2571</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3">
-      <c r="A223" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B223" s="3" t="s">
-        <v>2572</v>
-      </c>
-      <c r="C223" s="3" t="s">
-        <v>2573</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3">
-      <c r="A224" s="3" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>2574</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>639</v>
+        <v>654</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>650</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>650</v>
+        <v>692</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="3" t="s">
-        <v>2398</v>
+        <v>2403</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>698</v>
+        <v>639</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="3" t="s">
-        <v>532</v>
+        <v>2403</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>2579</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>2580</v>
+        <v>2581</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="3" t="s">
-        <v>532</v>
+        <v>2403</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>2581</v>
-      </c>
-      <c r="D230" s="3" t="s">
         <v>2582</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="3" t="s">
-        <v>532</v>
+        <v>2403</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>2583</v>
       </c>
-      <c r="D231" s="3" t="s">
-        <v>2584</v>
+      <c r="C231" s="3" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -37285,10 +37309,10 @@
         <v>532</v>
       </c>
       <c r="B232" s="3" t="s">
+        <v>2584</v>
+      </c>
+      <c r="D232" s="3" t="s">
         <v>2585</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>2580</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -37299,7 +37323,7 @@
         <v>2586</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>2580</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -37307,10 +37331,10 @@
         <v>532</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>2580</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -37318,10 +37342,10 @@
         <v>532</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>2588</v>
-      </c>
-      <c r="C235" s="3" t="s">
-        <v>478</v>
+        <v>2590</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>2585</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -37329,10 +37353,10 @@
         <v>532</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>2590</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -37340,10 +37364,10 @@
         <v>532</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>2592</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -37353,8 +37377,8 @@
       <c r="B238" s="3" t="s">
         <v>2593</v>
       </c>
-      <c r="D238" s="3" t="s">
-        <v>2594</v>
+      <c r="C238" s="3" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -37362,10 +37386,10 @@
         <v>532</v>
       </c>
       <c r="B239" s="3" t="s">
+        <v>2594</v>
+      </c>
+      <c r="D239" s="3" t="s">
         <v>2595</v>
-      </c>
-      <c r="D239" s="3" t="s">
-        <v>2596</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -37373,10 +37397,10 @@
         <v>532</v>
       </c>
       <c r="B240" s="3" t="s">
+        <v>2596</v>
+      </c>
+      <c r="D240" s="3" t="s">
         <v>2597</v>
-      </c>
-      <c r="D240" s="3" t="s">
-        <v>2598</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -37384,10 +37408,10 @@
         <v>532</v>
       </c>
       <c r="B241" s="3" t="s">
+        <v>2598</v>
+      </c>
+      <c r="D241" s="3" t="s">
         <v>2599</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>2600</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -37395,10 +37419,10 @@
         <v>532</v>
       </c>
       <c r="B242" s="3" t="s">
+        <v>2600</v>
+      </c>
+      <c r="D242" s="3" t="s">
         <v>2601</v>
-      </c>
-      <c r="D242" s="3" t="s">
-        <v>2602</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -37406,10 +37430,10 @@
         <v>532</v>
       </c>
       <c r="B243" s="3" t="s">
+        <v>2602</v>
+      </c>
+      <c r="D243" s="3" t="s">
         <v>2603</v>
-      </c>
-      <c r="D243" s="3" t="s">
-        <v>2604</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -37417,10 +37441,10 @@
         <v>532</v>
       </c>
       <c r="B244" s="3" t="s">
+        <v>2604</v>
+      </c>
+      <c r="D244" s="3" t="s">
         <v>2605</v>
-      </c>
-      <c r="D244" s="3" t="s">
-        <v>2606</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -37428,14 +37452,58 @@
         <v>532</v>
       </c>
       <c r="B245" s="3" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D245" s="3" t="s">
         <v>2607</v>
       </c>
-      <c r="D245" s="3" t="s">
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B246" s="3" t="s">
         <v>2608</v>
       </c>
+      <c r="D246" s="3" t="s">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>2610</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>2585</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D245"/>
+  <autoFilter ref="A1:D249"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not in the list" error="Pick one of: operation, job, schedule, handler." promptTitle="Kind" prompt="operation, job, schedule or handler" sqref="A2:A2001">
       <formula1>"operation,job,schedule,handler"</formula1>
@@ -37450,7 +37518,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -37460,202 +37528,216 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>2609</v>
+        <v>2615</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2610</v>
+        <v>2616</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2611</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>2612</v>
+        <v>2618</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2613</v>
+        <v>2619</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2614</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>2615</v>
+        <v>2621</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2616</v>
+        <v>2622</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2617</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>2615</v>
+        <v>2621</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2618</v>
+        <v>2624</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2619</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>2615</v>
+        <v>2621</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2620</v>
+        <v>2626</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2621</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>2622</v>
+        <v>2628</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2623</v>
+        <v>2629</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2624</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>2622</v>
+        <v>2628</v>
       </c>
       <c r="B7" s="3">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2625</v>
+        <v>2631</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2626</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>2622</v>
+        <v>2628</v>
       </c>
       <c r="B8" s="3">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2627</v>
+        <v>2633</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2628</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>2622</v>
+        <v>2628</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>2629</v>
+        <v>2635</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2630</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>2622</v>
+        <v>2628</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2631</v>
+        <v>2637</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2632</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>2622</v>
+        <v>2628</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>2633</v>
+        <v>2639</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2634</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>2622</v>
+        <v>2628</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2635</v>
+        <v>2641</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2636</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>2622</v>
+        <v>2628</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>2637</v>
+        <v>2643</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2638</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>2622</v>
+        <v>2628</v>
       </c>
       <c r="B14" s="3">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>2639</v>
+        <v>2645</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2640</v>
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3" t="s">
+        <v>2628</v>
+      </c>
+      <c r="B15" s="3">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>2647</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>2648</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D14"/>
+  <autoFilter ref="A1:D15"/>
   <dataValidations count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Date" prompt="YYYY-MM-DD" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Plan version" prompt="From 1, one per change." sqref="B2:B2001"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Actors!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$282</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$283</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$469</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$169</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$358</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8801" uniqueCount="2897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8807" uniqueCount="2901">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Plan version</t>
   </si>
   <si>
-    <t>19 (2026-10-27)</t>
+    <t>20 (2026-10-28)</t>
   </si>
   <si>
     <t>What this is</t>
@@ -8102,6 +8102,9 @@
     <t>conversations.rule_updated, conversations.rule_removed</t>
   </si>
   <si>
+    <t>conversations.upload_draft_attachment</t>
+  </si>
+  <si>
     <t>conversations.write_nudge</t>
   </si>
   <si>
@@ -8721,6 +8724,15 @@
   </si>
   <si>
     <t>#685</t>
+  </si>
+  <si>
+    <t>2026-10-28</t>
+  </si>
+  <si>
+    <t>Attaching a file to a draft (campbooks-cloud#391): Coverage for conversations.upload_draft_attachment, which tracks conversations.draft_updated as a save does.</t>
+  </si>
+  <si>
+    <t>#391</t>
   </si>
 </sst>
 </file>
@@ -37657,7 +37669,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D282"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -39502,8 +39514,8 @@
       <c r="B167" s="3" t="s">
         <v>2690</v>
       </c>
-      <c r="D167" s="3" t="s">
-        <v>2681</v>
+      <c r="C167" s="3" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -39524,8 +39536,8 @@
       <c r="B169" s="3" t="s">
         <v>2692</v>
       </c>
-      <c r="C169" s="3" t="s">
-        <v>377</v>
+      <c r="D169" s="3" t="s">
+        <v>2681</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -39536,7 +39548,7 @@
         <v>2693</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -39547,7 +39559,7 @@
         <v>2694</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>2695</v>
+        <v>381</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -39555,10 +39567,10 @@
         <v>2609</v>
       </c>
       <c r="B172" s="3" t="s">
+        <v>2695</v>
+      </c>
+      <c r="C172" s="3" t="s">
         <v>2696</v>
-      </c>
-      <c r="C172" s="3" t="s">
-        <v>2697</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -39566,10 +39578,10 @@
         <v>2609</v>
       </c>
       <c r="B173" s="3" t="s">
+        <v>2697</v>
+      </c>
+      <c r="C173" s="3" t="s">
         <v>2698</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>2699</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -39577,10 +39589,10 @@
         <v>2609</v>
       </c>
       <c r="B174" s="3" t="s">
+        <v>2699</v>
+      </c>
+      <c r="D174" s="3" t="s">
         <v>2700</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>2701</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -39588,10 +39600,10 @@
         <v>2609</v>
       </c>
       <c r="B175" s="3" t="s">
+        <v>2701</v>
+      </c>
+      <c r="C175" s="3" t="s">
         <v>2702</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -39602,10 +39614,10 @@
         <v>2703</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
       <c r="A177" s="3" t="s">
         <v>2609</v>
       </c>
@@ -39616,7 +39628,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="178" spans="1:4">
+    <row r="178" spans="1:3">
       <c r="A178" s="3" t="s">
         <v>2609</v>
       </c>
@@ -39624,43 +39636,43 @@
         <v>2705</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>2706</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
       <c r="A179" s="3" t="s">
         <v>2609</v>
       </c>
       <c r="B179" s="3" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C179" s="3" t="s">
         <v>2707</v>
       </c>
-      <c r="C179" s="3" t="s">
-        <v>2708</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4">
+    </row>
+    <row r="180" spans="1:3">
       <c r="A180" s="3" t="s">
         <v>2609</v>
       </c>
       <c r="B180" s="3" t="s">
+        <v>2708</v>
+      </c>
+      <c r="C180" s="3" t="s">
         <v>2709</v>
       </c>
-      <c r="C180" s="3" t="s">
-        <v>2710</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4">
+    </row>
+    <row r="181" spans="1:3">
       <c r="A181" s="3" t="s">
         <v>2609</v>
       </c>
       <c r="B181" s="3" t="s">
+        <v>2710</v>
+      </c>
+      <c r="C181" s="3" t="s">
         <v>2711</v>
       </c>
-      <c r="C181" s="3" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4">
+    </row>
+    <row r="182" spans="1:3">
       <c r="A182" s="3" t="s">
         <v>2609</v>
       </c>
@@ -39668,10 +39680,10 @@
         <v>2712</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
       <c r="A183" s="3" t="s">
         <v>2609</v>
       </c>
@@ -39679,10 +39691,10 @@
         <v>2713</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
       <c r="A184" s="3" t="s">
         <v>2609</v>
       </c>
@@ -39690,10 +39702,10 @@
         <v>2714</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
       <c r="A185" s="3" t="s">
         <v>2609</v>
       </c>
@@ -39701,10 +39713,10 @@
         <v>2715</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
       <c r="A186" s="3" t="s">
         <v>2609</v>
       </c>
@@ -39712,10 +39724,10 @@
         <v>2716</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
       <c r="A187" s="3" t="s">
         <v>2609</v>
       </c>
@@ -39723,10 +39735,10 @@
         <v>2717</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
       <c r="A188" s="3" t="s">
         <v>2609</v>
       </c>
@@ -39734,10 +39746,10 @@
         <v>2718</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
       <c r="A189" s="3" t="s">
         <v>2609</v>
       </c>
@@ -39745,10 +39757,10 @@
         <v>2719</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
       <c r="A190" s="3" t="s">
         <v>2609</v>
       </c>
@@ -39756,10 +39768,10 @@
         <v>2720</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
       <c r="A191" s="3" t="s">
         <v>2609</v>
       </c>
@@ -39767,18 +39779,18 @@
         <v>2721</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
       <c r="A192" s="3" t="s">
         <v>2609</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>2722</v>
       </c>
-      <c r="D192" s="3" t="s">
-        <v>2723</v>
+      <c r="C192" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -39786,10 +39798,10 @@
         <v>2609</v>
       </c>
       <c r="B193" s="3" t="s">
+        <v>2723</v>
+      </c>
+      <c r="D193" s="3" t="s">
         <v>2724</v>
-      </c>
-      <c r="D193" s="3" t="s">
-        <v>2725</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -39797,10 +39809,10 @@
         <v>2609</v>
       </c>
       <c r="B194" s="3" t="s">
+        <v>2725</v>
+      </c>
+      <c r="D194" s="3" t="s">
         <v>2726</v>
-      </c>
-      <c r="D194" s="3" t="s">
-        <v>2727</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -39808,10 +39820,10 @@
         <v>2609</v>
       </c>
       <c r="B195" s="3" t="s">
+        <v>2727</v>
+      </c>
+      <c r="D195" s="3" t="s">
         <v>2728</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>2729</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -39819,10 +39831,10 @@
         <v>2609</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>2729</v>
+      </c>
+      <c r="D196" s="3" t="s">
         <v>2730</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>2731</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -39830,10 +39842,10 @@
         <v>2609</v>
       </c>
       <c r="B197" s="3" t="s">
+        <v>2731</v>
+      </c>
+      <c r="D197" s="3" t="s">
         <v>2732</v>
-      </c>
-      <c r="C197" s="3" t="s">
-        <v>2733</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -39841,10 +39853,10 @@
         <v>2609</v>
       </c>
       <c r="B198" s="3" t="s">
+        <v>2733</v>
+      </c>
+      <c r="C198" s="3" t="s">
         <v>2734</v>
-      </c>
-      <c r="C198" s="3" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -39855,7 +39867,7 @@
         <v>2735</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>2736</v>
+        <v>586</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -39863,10 +39875,10 @@
         <v>2609</v>
       </c>
       <c r="B200" s="3" t="s">
+        <v>2736</v>
+      </c>
+      <c r="C200" s="3" t="s">
         <v>2737</v>
-      </c>
-      <c r="C200" s="3" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -39877,7 +39889,7 @@
         <v>2738</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>2739</v>
+        <v>556</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -39885,10 +39897,10 @@
         <v>2609</v>
       </c>
       <c r="B202" s="3" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C202" s="3" t="s">
         <v>2740</v>
-      </c>
-      <c r="C202" s="3" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -39898,8 +39910,8 @@
       <c r="B203" s="3" t="s">
         <v>2741</v>
       </c>
-      <c r="D203" s="3" t="s">
-        <v>2742</v>
+      <c r="C203" s="3" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -39907,10 +39919,10 @@
         <v>2609</v>
       </c>
       <c r="B204" s="3" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D204" s="3" t="s">
         <v>2743</v>
-      </c>
-      <c r="C204" s="3" t="s">
-        <v>2744</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -39918,10 +39930,10 @@
         <v>2609</v>
       </c>
       <c r="B205" s="3" t="s">
+        <v>2744</v>
+      </c>
+      <c r="C205" s="3" t="s">
         <v>2745</v>
-      </c>
-      <c r="C205" s="3" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -39932,7 +39944,7 @@
         <v>2746</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -39943,7 +39955,7 @@
         <v>2747</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -39953,8 +39965,8 @@
       <c r="B208" s="3" t="s">
         <v>2748</v>
       </c>
-      <c r="D208" s="3" t="s">
-        <v>2749</v>
+      <c r="C208" s="3" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -39962,10 +39974,10 @@
         <v>2609</v>
       </c>
       <c r="B209" s="3" t="s">
+        <v>2749</v>
+      </c>
+      <c r="D209" s="3" t="s">
         <v>2750</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>2751</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -39973,10 +39985,10 @@
         <v>2609</v>
       </c>
       <c r="B210" s="3" t="s">
+        <v>2751</v>
+      </c>
+      <c r="D210" s="3" t="s">
         <v>2752</v>
-      </c>
-      <c r="C210" s="3" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -39987,7 +39999,7 @@
         <v>2753</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>549</v>
+        <v>524</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -39998,7 +40010,7 @@
         <v>2754</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>572</v>
+        <v>549</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -40008,8 +40020,8 @@
       <c r="B213" s="3" t="s">
         <v>2755</v>
       </c>
-      <c r="D213" s="3" t="s">
-        <v>2756</v>
+      <c r="C213" s="3" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -40017,10 +40029,10 @@
         <v>2609</v>
       </c>
       <c r="B214" s="3" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D214" s="3" t="s">
         <v>2757</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -40030,8 +40042,8 @@
       <c r="B215" s="3" t="s">
         <v>2758</v>
       </c>
-      <c r="D215" s="3" t="s">
-        <v>2759</v>
+      <c r="C215" s="3" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -40039,10 +40051,10 @@
         <v>2609</v>
       </c>
       <c r="B216" s="3" t="s">
+        <v>2759</v>
+      </c>
+      <c r="D216" s="3" t="s">
         <v>2760</v>
-      </c>
-      <c r="C216" s="3" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -40053,7 +40065,7 @@
         <v>2761</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>541</v>
+        <v>575</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -40074,8 +40086,8 @@
       <c r="B219" s="3" t="s">
         <v>2763</v>
       </c>
-      <c r="D219" s="3" t="s">
-        <v>2764</v>
+      <c r="C219" s="3" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -40083,10 +40095,10 @@
         <v>2609</v>
       </c>
       <c r="B220" s="3" t="s">
+        <v>2764</v>
+      </c>
+      <c r="D220" s="3" t="s">
         <v>2765</v>
-      </c>
-      <c r="C220" s="3" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -40097,7 +40109,7 @@
         <v>2766</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>518</v>
+        <v>579</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -40108,7 +40120,7 @@
         <v>2767</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -40119,7 +40131,7 @@
         <v>2768</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>582</v>
+        <v>545</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -40130,7 +40142,7 @@
         <v>2769</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>562</v>
+        <v>582</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -40140,8 +40152,8 @@
       <c r="B225" s="3" t="s">
         <v>2770</v>
       </c>
-      <c r="D225" s="3" t="s">
-        <v>2771</v>
+      <c r="C225" s="3" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -40149,10 +40161,10 @@
         <v>2609</v>
       </c>
       <c r="B226" s="3" t="s">
+        <v>2771</v>
+      </c>
+      <c r="D226" s="3" t="s">
         <v>2772</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>2773</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -40160,10 +40172,10 @@
         <v>2609</v>
       </c>
       <c r="B227" s="3" t="s">
+        <v>2773</v>
+      </c>
+      <c r="D227" s="3" t="s">
         <v>2774</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>2775</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -40171,10 +40183,10 @@
         <v>2609</v>
       </c>
       <c r="B228" s="3" t="s">
+        <v>2775</v>
+      </c>
+      <c r="D228" s="3" t="s">
         <v>2776</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -40185,7 +40197,7 @@
         <v>2777</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -40196,7 +40208,7 @@
         <v>2778</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -40207,7 +40219,7 @@
         <v>2779</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -40218,7 +40230,7 @@
         <v>2780</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -40229,7 +40241,7 @@
         <v>2781</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -40240,7 +40252,7 @@
         <v>2782</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>2783</v>
+        <v>646</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -40248,10 +40260,10 @@
         <v>2609</v>
       </c>
       <c r="B235" s="3" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C235" s="3" t="s">
         <v>2784</v>
-      </c>
-      <c r="C235" s="3" t="s">
-        <v>2785</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -40259,10 +40271,10 @@
         <v>2609</v>
       </c>
       <c r="B236" s="3" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C236" s="3" t="s">
         <v>2786</v>
-      </c>
-      <c r="C236" s="3" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -40273,7 +40285,7 @@
         <v>2787</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>494</v>
+        <v>661</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -40284,7 +40296,7 @@
         <v>2788</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -40295,7 +40307,7 @@
         <v>2789</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -40306,7 +40318,7 @@
         <v>2790</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -40316,8 +40328,8 @@
       <c r="B241" s="3" t="s">
         <v>2791</v>
       </c>
-      <c r="D241" s="3" t="s">
-        <v>2792</v>
+      <c r="C241" s="3" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -40325,10 +40337,10 @@
         <v>2609</v>
       </c>
       <c r="B242" s="3" t="s">
+        <v>2792</v>
+      </c>
+      <c r="D242" s="3" t="s">
         <v>2793</v>
-      </c>
-      <c r="D242" s="3" t="s">
-        <v>2794</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -40336,10 +40348,10 @@
         <v>2609</v>
       </c>
       <c r="B243" s="3" t="s">
+        <v>2794</v>
+      </c>
+      <c r="D243" s="3" t="s">
         <v>2795</v>
-      </c>
-      <c r="C243" s="3" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -40350,7 +40362,7 @@
         <v>2796</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>2797</v>
+        <v>670</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -40358,10 +40370,10 @@
         <v>2609</v>
       </c>
       <c r="B245" s="3" t="s">
+        <v>2797</v>
+      </c>
+      <c r="C245" s="3" t="s">
         <v>2798</v>
-      </c>
-      <c r="C245" s="3" t="s">
-        <v>2799</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -40369,10 +40381,10 @@
         <v>2609</v>
       </c>
       <c r="B246" s="3" t="s">
+        <v>2799</v>
+      </c>
+      <c r="C246" s="3" t="s">
         <v>2800</v>
-      </c>
-      <c r="C246" s="3" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -40383,7 +40395,7 @@
         <v>2801</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>2802</v>
+        <v>687</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -40391,10 +40403,10 @@
         <v>2609</v>
       </c>
       <c r="B248" s="3" t="s">
+        <v>2802</v>
+      </c>
+      <c r="C248" s="3" t="s">
         <v>2803</v>
-      </c>
-      <c r="C248" s="3" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -40405,7 +40417,7 @@
         <v>2804</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -40416,7 +40428,7 @@
         <v>2805</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -40427,7 +40439,7 @@
         <v>2806</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -40438,7 +40450,7 @@
         <v>2807</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>2808</v>
+        <v>704</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -40446,10 +40458,10 @@
         <v>2609</v>
       </c>
       <c r="B253" s="3" t="s">
+        <v>2808</v>
+      </c>
+      <c r="C253" s="3" t="s">
         <v>2809</v>
-      </c>
-      <c r="C253" s="3" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -40460,7 +40472,7 @@
         <v>2810</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>748</v>
+        <v>717</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -40471,7 +40483,7 @@
         <v>2811</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -40482,7 +40494,7 @@
         <v>2812</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>757</v>
+        <v>736</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -40493,7 +40505,7 @@
         <v>2813</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -40504,7 +40516,7 @@
         <v>2814</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>726</v>
+        <v>745</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -40515,7 +40527,7 @@
         <v>2815</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>2816</v>
+        <v>726</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -40523,10 +40535,10 @@
         <v>2609</v>
       </c>
       <c r="B260" s="3" t="s">
+        <v>2816</v>
+      </c>
+      <c r="C260" s="3" t="s">
         <v>2817</v>
-      </c>
-      <c r="C260" s="3" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -40537,7 +40549,7 @@
         <v>2818</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>711</v>
+        <v>764</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -40548,7 +40560,7 @@
         <v>2819</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -40570,18 +40582,18 @@
         <v>2821</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>770</v>
+        <v>722</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="3" t="s">
-        <v>604</v>
+        <v>2609</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>2822</v>
       </c>
-      <c r="D265" s="3" t="s">
-        <v>2823</v>
+      <c r="C265" s="3" t="s">
+        <v>770</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -40589,10 +40601,10 @@
         <v>604</v>
       </c>
       <c r="B266" s="3" t="s">
+        <v>2823</v>
+      </c>
+      <c r="D266" s="3" t="s">
         <v>2824</v>
-      </c>
-      <c r="D266" s="3" t="s">
-        <v>2825</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -40600,10 +40612,10 @@
         <v>604</v>
       </c>
       <c r="B267" s="3" t="s">
+        <v>2825</v>
+      </c>
+      <c r="D267" s="3" t="s">
         <v>2826</v>
-      </c>
-      <c r="D267" s="3" t="s">
-        <v>2827</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -40611,10 +40623,10 @@
         <v>604</v>
       </c>
       <c r="B268" s="3" t="s">
+        <v>2827</v>
+      </c>
+      <c r="D268" s="3" t="s">
         <v>2828</v>
-      </c>
-      <c r="D268" s="3" t="s">
-        <v>2823</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -40625,7 +40637,7 @@
         <v>2829</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>2823</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -40636,7 +40648,7 @@
         <v>2830</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>2823</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -40646,8 +40658,8 @@
       <c r="B271" s="3" t="s">
         <v>2831</v>
       </c>
-      <c r="C271" s="3" t="s">
-        <v>490</v>
+      <c r="D271" s="3" t="s">
+        <v>2824</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -40657,8 +40669,8 @@
       <c r="B272" s="3" t="s">
         <v>2832</v>
       </c>
-      <c r="D272" s="3" t="s">
-        <v>2833</v>
+      <c r="C272" s="3" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -40666,10 +40678,10 @@
         <v>604</v>
       </c>
       <c r="B273" s="3" t="s">
+        <v>2833</v>
+      </c>
+      <c r="D273" s="3" t="s">
         <v>2834</v>
-      </c>
-      <c r="D273" s="3" t="s">
-        <v>2835</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -40677,10 +40689,10 @@
         <v>604</v>
       </c>
       <c r="B274" s="3" t="s">
+        <v>2835</v>
+      </c>
+      <c r="D274" s="3" t="s">
         <v>2836</v>
-      </c>
-      <c r="D274" s="3" t="s">
-        <v>2837</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -40688,10 +40700,10 @@
         <v>604</v>
       </c>
       <c r="B275" s="3" t="s">
+        <v>2837</v>
+      </c>
+      <c r="D275" s="3" t="s">
         <v>2838</v>
-      </c>
-      <c r="D275" s="3" t="s">
-        <v>2839</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -40699,10 +40711,10 @@
         <v>604</v>
       </c>
       <c r="B276" s="3" t="s">
+        <v>2839</v>
+      </c>
+      <c r="D276" s="3" t="s">
         <v>2840</v>
-      </c>
-      <c r="D276" s="3" t="s">
-        <v>2841</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -40710,10 +40722,10 @@
         <v>604</v>
       </c>
       <c r="B277" s="3" t="s">
+        <v>2841</v>
+      </c>
+      <c r="D277" s="3" t="s">
         <v>2842</v>
-      </c>
-      <c r="D277" s="3" t="s">
-        <v>2843</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -40721,10 +40733,10 @@
         <v>604</v>
       </c>
       <c r="B278" s="3" t="s">
+        <v>2843</v>
+      </c>
+      <c r="D278" s="3" t="s">
         <v>2844</v>
-      </c>
-      <c r="D278" s="3" t="s">
-        <v>2845</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -40732,10 +40744,10 @@
         <v>604</v>
       </c>
       <c r="B279" s="3" t="s">
+        <v>2845</v>
+      </c>
+      <c r="D279" s="3" t="s">
         <v>2846</v>
-      </c>
-      <c r="D279" s="3" t="s">
-        <v>2847</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -40743,10 +40755,10 @@
         <v>604</v>
       </c>
       <c r="B280" s="3" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D280" s="3" t="s">
         <v>2848</v>
-      </c>
-      <c r="D280" s="3" t="s">
-        <v>2849</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -40754,10 +40766,10 @@
         <v>604</v>
       </c>
       <c r="B281" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D281" s="3" t="s">
         <v>2850</v>
-      </c>
-      <c r="D281" s="3" t="s">
-        <v>2851</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -40765,14 +40777,25 @@
         <v>604</v>
       </c>
       <c r="B282" s="3" t="s">
+        <v>2851</v>
+      </c>
+      <c r="D282" s="3" t="s">
         <v>2852</v>
       </c>
-      <c r="D282" s="3" t="s">
-        <v>2823</v>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>2853</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>2824</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D282"/>
+  <autoFilter ref="A1:D283"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not in the list" error="Pick one of: operation, job, schedule, handler." promptTitle="Kind" prompt="operation, job, schedule or handler" sqref="A2:A2001">
       <formula1>"operation,job,schedule,handler"</formula1>
@@ -40787,7 +40810,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -40797,272 +40820,286 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2855</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2857</v>
+        <v>2858</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2858</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2860</v>
+        <v>2861</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2861</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2863</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="B7" s="3">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="B8" s="3">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="B14" s="3">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="B15" s="3">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="B16" s="3">
         <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="B17" s="3">
         <v>17</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="B18" s="3">
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="B19" s="3">
         <v>19</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2896</v>
+        <v>2897</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="3" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B20" s="3">
+        <v>20</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>2899</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>2900</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D19"/>
+  <autoFilter ref="A1:D20"/>
   <dataValidations count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Date" prompt="YYYY-MM-DD" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Plan version" prompt="From 1, one per change." sqref="B2:B2001"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Actors!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$288</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$473</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$171</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$363</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8890" uniqueCount="2929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8893" uniqueCount="2931">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -8328,6 +8328,12 @@
   </si>
   <si>
     <t>takes back files that pages.attach_from_message made files of the page, for the ones no block names; nothing new is made, and the files were tracked when they were attached (pages.files_attached)</t>
+  </si>
+  <si>
+    <t>pages.get_sharing</t>
+  </si>
+  <si>
+    <t>reads who can read a page and whether Notion keeps a copy, for Scout's card; it changes nothing</t>
   </si>
   <si>
     <t>pages.get_table_sync</t>
@@ -38015,7 +38021,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D287"/>
+  <dimension ref="A1:D288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -40300,7 +40306,7 @@
       <c r="B207" s="3" t="s">
         <v>2768</v>
       </c>
-      <c r="C207" s="3" t="s">
+      <c r="D207" s="3" t="s">
         <v>2769</v>
       </c>
     </row>
@@ -40312,7 +40318,7 @@
         <v>2770</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>571</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -40320,10 +40326,10 @@
         <v>2630</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>2771</v>
+        <v>2772</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -40331,10 +40337,10 @@
         <v>2630</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>2772</v>
+        <v>2773</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>596</v>
+        <v>574</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -40342,10 +40348,10 @@
         <v>2630</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>2773</v>
-      </c>
-      <c r="D211" s="3" t="s">
         <v>2774</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -40377,8 +40383,8 @@
       <c r="B214" s="3" t="s">
         <v>2779</v>
       </c>
-      <c r="C214" s="3" t="s">
-        <v>530</v>
+      <c r="D214" s="3" t="s">
+        <v>2780</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -40386,10 +40392,10 @@
         <v>2630</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>2780</v>
+        <v>2781</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>555</v>
+        <v>530</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -40397,10 +40403,10 @@
         <v>2630</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>2781</v>
+        <v>2782</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>578</v>
+        <v>555</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -40408,10 +40414,10 @@
         <v>2630</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>2782</v>
-      </c>
-      <c r="D217" s="3" t="s">
         <v>2783</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -40421,8 +40427,8 @@
       <c r="B218" s="3" t="s">
         <v>2784</v>
       </c>
-      <c r="C218" s="3" t="s">
-        <v>511</v>
+      <c r="D218" s="3" t="s">
+        <v>2785</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -40430,10 +40436,10 @@
         <v>2630</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>2785</v>
-      </c>
-      <c r="D219" s="3" t="s">
         <v>2786</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -40443,8 +40449,8 @@
       <c r="B220" s="3" t="s">
         <v>2787</v>
       </c>
-      <c r="C220" s="3" t="s">
-        <v>581</v>
+      <c r="D220" s="3" t="s">
+        <v>2788</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -40452,10 +40458,10 @@
         <v>2630</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>2788</v>
+        <v>2789</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -40463,7 +40469,7 @@
         <v>2630</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>2789</v>
+        <v>2790</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>547</v>
@@ -40474,10 +40480,10 @@
         <v>2630</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>2790</v>
-      </c>
-      <c r="D223" s="3" t="s">
         <v>2791</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -40487,8 +40493,8 @@
       <c r="B224" s="3" t="s">
         <v>2792</v>
       </c>
-      <c r="C224" s="3" t="s">
-        <v>585</v>
+      <c r="D224" s="3" t="s">
+        <v>2793</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -40496,10 +40502,10 @@
         <v>2630</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>2793</v>
-      </c>
-      <c r="D225" s="3" t="s">
         <v>2794</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -40509,8 +40515,8 @@
       <c r="B226" s="3" t="s">
         <v>2795</v>
       </c>
-      <c r="C226" s="3" t="s">
-        <v>524</v>
+      <c r="D226" s="3" t="s">
+        <v>2796</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -40518,10 +40524,10 @@
         <v>2630</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>2796</v>
+        <v>2797</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>551</v>
+        <v>524</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -40529,10 +40535,10 @@
         <v>2630</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>2797</v>
+        <v>2798</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>588</v>
+        <v>551</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -40540,10 +40546,10 @@
         <v>2630</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>2798</v>
+        <v>2799</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -40551,10 +40557,10 @@
         <v>2630</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>2799</v>
-      </c>
-      <c r="D230" s="3" t="s">
         <v>2800</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -40586,8 +40592,8 @@
       <c r="B233" s="3" t="s">
         <v>2805</v>
       </c>
-      <c r="C233" s="3" t="s">
-        <v>633</v>
+      <c r="D233" s="3" t="s">
+        <v>2806</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -40595,10 +40601,10 @@
         <v>2630</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>2806</v>
+        <v>2807</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -40606,10 +40612,10 @@
         <v>2630</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>2807</v>
+        <v>2808</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -40617,10 +40623,10 @@
         <v>2630</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>2808</v>
+        <v>2809</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -40628,10 +40634,10 @@
         <v>2630</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>2809</v>
+        <v>2810</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -40639,10 +40645,10 @@
         <v>2630</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>2810</v>
+        <v>2811</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -40650,10 +40656,10 @@
         <v>2630</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>2811</v>
+        <v>2812</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>2812</v>
+        <v>657</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -40675,7 +40681,7 @@
         <v>2815</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>672</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -40683,10 +40689,10 @@
         <v>2630</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>2816</v>
+        <v>2817</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>494</v>
+        <v>672</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -40694,10 +40700,10 @@
         <v>2630</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>2817</v>
+        <v>2818</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -40705,10 +40711,10 @@
         <v>2630</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>2818</v>
+        <v>2819</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -40716,10 +40722,10 @@
         <v>2630</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>2819</v>
+        <v>2820</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -40727,10 +40733,10 @@
         <v>2630</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>2820</v>
-      </c>
-      <c r="D246" s="3" t="s">
         <v>2821</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -40751,8 +40757,8 @@
       <c r="B248" s="3" t="s">
         <v>2824</v>
       </c>
-      <c r="C248" s="3" t="s">
-        <v>681</v>
+      <c r="D248" s="3" t="s">
+        <v>2825</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -40760,10 +40766,10 @@
         <v>2630</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>2825</v>
+        <v>2826</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>2826</v>
+        <v>681</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -40785,7 +40791,7 @@
         <v>2829</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>698</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -40793,10 +40799,10 @@
         <v>2630</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>2830</v>
+        <v>2831</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>2831</v>
+        <v>698</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -40807,7 +40813,7 @@
         <v>2832</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>711</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -40815,10 +40821,10 @@
         <v>2630</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>2833</v>
+        <v>2834</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -40826,10 +40832,10 @@
         <v>2630</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>719</v>
+        <v>703</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -40837,10 +40843,10 @@
         <v>2630</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>2835</v>
+        <v>2836</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -40848,10 +40854,10 @@
         <v>2630</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>2836</v>
+        <v>2837</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>2837</v>
+        <v>715</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -40862,7 +40868,7 @@
         <v>2838</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>728</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -40870,10 +40876,10 @@
         <v>2630</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>759</v>
+        <v>728</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -40881,10 +40887,10 @@
         <v>2630</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -40892,10 +40898,10 @@
         <v>2630</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -40903,10 +40909,10 @@
         <v>2630</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -40914,10 +40920,10 @@
         <v>2630</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>737</v>
+        <v>756</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -40925,10 +40931,10 @@
         <v>2630</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>2845</v>
+        <v>737</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -40939,7 +40945,7 @@
         <v>2846</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>775</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -40947,10 +40953,10 @@
         <v>2630</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>722</v>
+        <v>775</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -40958,10 +40964,10 @@
         <v>2630</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -40969,7 +40975,7 @@
         <v>2630</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>2849</v>
+        <v>2850</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>733</v>
@@ -40980,21 +40986,21 @@
         <v>2630</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>2850</v>
+        <v>2851</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>781</v>
+        <v>733</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="3" t="s">
-        <v>615</v>
+        <v>2630</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>2851</v>
-      </c>
-      <c r="D270" s="3" t="s">
         <v>2852</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -41027,7 +41033,7 @@
         <v>2857</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>2852</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -41035,10 +41041,10 @@
         <v>615</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>2858</v>
+        <v>2859</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>2852</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -41046,10 +41052,10 @@
         <v>615</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>2852</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -41057,10 +41063,10 @@
         <v>615</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>2860</v>
-      </c>
-      <c r="C276" s="3" t="s">
-        <v>490</v>
+        <v>2861</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>2854</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -41068,10 +41074,10 @@
         <v>615</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>2861</v>
-      </c>
-      <c r="D277" s="3" t="s">
         <v>2862</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -41181,11 +41187,22 @@
         <v>2881</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>2852</v>
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>2883</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>2854</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D287"/>
+  <autoFilter ref="A1:D288"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not in the list" error="Pick one of: operation, job, schedule, handler." promptTitle="Kind" prompt="operation, job, schedule or handler" sqref="A2:A2001">
       <formula1>"operation,job,schedule,handler"</formula1>
@@ -41210,282 +41227,282 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>2882</v>
+        <v>2884</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2883</v>
+        <v>2885</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2884</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>2885</v>
+        <v>2887</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2886</v>
+        <v>2888</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2887</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>2888</v>
+        <v>2890</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2889</v>
+        <v>2891</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2890</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>2888</v>
+        <v>2890</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2891</v>
+        <v>2893</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2892</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>2888</v>
+        <v>2890</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2893</v>
+        <v>2895</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2896</v>
+        <v>2898</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2897</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="B7" s="3">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2898</v>
+        <v>2900</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2899</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="B8" s="3">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2900</v>
+        <v>2902</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2901</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>2902</v>
+        <v>2904</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2903</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2904</v>
+        <v>2906</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2905</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>2906</v>
+        <v>2908</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2907</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2908</v>
+        <v>2910</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2909</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>2910</v>
+        <v>2912</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2911</v>
+        <v>2913</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="B14" s="3">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>2912</v>
+        <v>2914</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2913</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="B15" s="3">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>2914</v>
+        <v>2916</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2915</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>2916</v>
+        <v>2918</v>
       </c>
       <c r="B16" s="3">
         <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>2917</v>
+        <v>2919</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2918</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>2916</v>
+        <v>2918</v>
       </c>
       <c r="B17" s="3">
         <v>17</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>2919</v>
+        <v>2921</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2920</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>2916</v>
+        <v>2918</v>
       </c>
       <c r="B18" s="3">
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>2921</v>
+        <v>2923</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2922</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>2923</v>
+        <v>2925</v>
       </c>
       <c r="B19" s="3">
         <v>19</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>2924</v>
+        <v>2926</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2925</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>2926</v>
+        <v>2928</v>
       </c>
       <c r="B20" s="3">
         <v>20</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>2927</v>
+        <v>2929</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2928</v>
+        <v>2930</v>
       </c>
     </row>
   </sheetData>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -8768,7 +8768,7 @@
     <t>You replied. Done? (campbooks-cloud#396): tasks.task_reply_noticed (a reply of the member in the conversation an open Do task came from) and tasks.task_reply_answered (the member answered Not yet); Coverage for tasks.notice_replies, tasks.answer_reply and tasks.unanswer_reply.</t>
   </si>
   <si>
-    <t>#693</t>
+    <t>#697</t>
   </si>
 </sst>
 </file>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -8756,7 +8756,7 @@
     <t>Calendar roles (campbooks-cloud#399): schedule.calendar_role_changed for a calendar a member set to mine or following (which); schedule.update_calendar's Coverage names it.</t>
   </si>
   <si>
-    <t>#700</t>
+    <t>#696</t>
   </si>
 </sst>
 </file>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Actors!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$291</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$473</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$173</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8938" uniqueCount="2944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8941" uniqueCount="2946">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Plan version</t>
   </si>
   <si>
-    <t>20 (2026-10-28)</t>
+    <t>21 (2026-10-28)</t>
   </si>
   <si>
     <t>What this is</t>
@@ -8856,6 +8856,12 @@
   </si>
   <si>
     <t>2026-10-28</t>
+  </si>
+  <si>
+    <t>You replied. Done? (campbooks-cloud#396): tasks.task_reply_noticed (a reply of the member in the conversation an open Do task came from) and tasks.task_reply_answered (the member answered Not yet); Coverage for tasks.notice_replies, tasks.answer_reply and tasks.unanswer_reply.</t>
+  </si>
+  <si>
+    <t>#697</t>
   </si>
   <si>
     <t>Mail and Scout in pages (campbooks-cloud#364): 2 pages events for files saved from a message (how many) and a section appended (how many blocks and sources, in buckets); 2 assistant tools (find_pages, read_page) and 2 proposal actions (append_section, new_page); Coverage for every operation of the change.</t>
@@ -13482,7 +13488,7 @@
         <v>522</v>
       </c>
       <c r="K106" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L106" s="3" t="s">
         <v>523</v>
@@ -14242,7 +14248,7 @@
         <v>605</v>
       </c>
       <c r="K126" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L126" s="3" t="s">
         <v>523</v>
@@ -41423,7 +41429,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -41711,8 +41717,22 @@
         <v>2943</v>
       </c>
     </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="3" t="s">
+        <v>2941</v>
+      </c>
+      <c r="B21" s="3">
+        <v>21</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>2944</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>2945</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D20"/>
+  <autoFilter ref="A1:D21"/>
   <dataValidations count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Date" prompt="YYYY-MM-DD" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Plan version" prompt="From 1, one per change." sqref="B2:B2001"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Actors!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$291</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$292</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$475</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$174</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$367</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8976" uniqueCount="2957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8982" uniqueCount="2960">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Plan version</t>
   </si>
   <si>
-    <t>22 (2026-10-28)</t>
+    <t>23 (2026-10-28)</t>
   </si>
   <si>
     <t>What this is</t>
@@ -8222,6 +8222,9 @@
     <t>conversations.rule_updated, conversations.rule_removed</t>
   </si>
   <si>
+    <t>conversations.upload_draft_attachment</t>
+  </si>
+  <si>
     <t>conversations.write_nudge</t>
   </si>
   <si>
@@ -8901,6 +8904,12 @@
   </si>
   <si>
     <t>#696</t>
+  </si>
+  <si>
+    <t>Attaching a file to a draft (campbooks-cloud#391): Coverage for conversations.upload_draft_attachment, which tracks conversations.draft_updated as a save does.</t>
+  </si>
+  <si>
+    <t>#699</t>
   </si>
 </sst>
 </file>
@@ -38351,7 +38360,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D291"/>
+  <dimension ref="A1:D292"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -40207,8 +40216,8 @@
       <c r="B168" s="3" t="s">
         <v>2730</v>
       </c>
-      <c r="D168" s="3" t="s">
-        <v>2721</v>
+      <c r="C168" s="3" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -40229,8 +40238,8 @@
       <c r="B170" s="3" t="s">
         <v>2732</v>
       </c>
-      <c r="C170" s="3" t="s">
-        <v>377</v>
+      <c r="D170" s="3" t="s">
+        <v>2721</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -40241,7 +40250,7 @@
         <v>2733</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -40252,7 +40261,7 @@
         <v>2734</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>2735</v>
+        <v>381</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -40260,10 +40269,10 @@
         <v>2649</v>
       </c>
       <c r="B173" s="3" t="s">
+        <v>2735</v>
+      </c>
+      <c r="C173" s="3" t="s">
         <v>2736</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>2737</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -40271,10 +40280,10 @@
         <v>2649</v>
       </c>
       <c r="B174" s="3" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C174" s="3" t="s">
         <v>2738</v>
-      </c>
-      <c r="D174" s="3" t="s">
-        <v>2739</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -40282,10 +40291,10 @@
         <v>2649</v>
       </c>
       <c r="B175" s="3" t="s">
+        <v>2739</v>
+      </c>
+      <c r="D175" s="3" t="s">
         <v>2740</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>2741</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -40293,10 +40302,10 @@
         <v>2649</v>
       </c>
       <c r="B176" s="3" t="s">
+        <v>2741</v>
+      </c>
+      <c r="C176" s="3" t="s">
         <v>2742</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -40307,7 +40316,7 @@
         <v>2743</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>466</v>
+        <v>426</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -40329,7 +40338,7 @@
         <v>2745</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>2746</v>
+        <v>466</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -40337,10 +40346,10 @@
         <v>2649</v>
       </c>
       <c r="B180" s="3" t="s">
+        <v>2746</v>
+      </c>
+      <c r="C180" s="3" t="s">
         <v>2747</v>
-      </c>
-      <c r="C180" s="3" t="s">
-        <v>2748</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -40348,10 +40357,10 @@
         <v>2649</v>
       </c>
       <c r="B181" s="3" t="s">
+        <v>2748</v>
+      </c>
+      <c r="C181" s="3" t="s">
         <v>2749</v>
-      </c>
-      <c r="C181" s="3" t="s">
-        <v>2750</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -40359,10 +40368,10 @@
         <v>2649</v>
       </c>
       <c r="B182" s="3" t="s">
+        <v>2750</v>
+      </c>
+      <c r="C182" s="3" t="s">
         <v>2751</v>
-      </c>
-      <c r="C182" s="3" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -40373,7 +40382,7 @@
         <v>2752</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -40384,7 +40393,7 @@
         <v>2753</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>446</v>
+        <v>385</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -40395,7 +40404,7 @@
         <v>2754</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>390</v>
+        <v>446</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -40406,7 +40415,7 @@
         <v>2755</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>450</v>
+        <v>390</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -40417,7 +40426,7 @@
         <v>2756</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -40428,7 +40437,7 @@
         <v>2757</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -40439,7 +40448,7 @@
         <v>2758</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -40450,7 +40459,7 @@
         <v>2759</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>410</v>
+        <v>462</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -40461,7 +40470,7 @@
         <v>2760</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -40472,7 +40481,7 @@
         <v>2761</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>470</v>
+        <v>393</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -40482,8 +40491,8 @@
       <c r="B193" s="3" t="s">
         <v>2762</v>
       </c>
-      <c r="D193" s="3" t="s">
-        <v>2763</v>
+      <c r="C193" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -40491,10 +40500,10 @@
         <v>2649</v>
       </c>
       <c r="B194" s="3" t="s">
+        <v>2763</v>
+      </c>
+      <c r="D194" s="3" t="s">
         <v>2764</v>
-      </c>
-      <c r="D194" s="3" t="s">
-        <v>2765</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -40502,10 +40511,10 @@
         <v>2649</v>
       </c>
       <c r="B195" s="3" t="s">
+        <v>2765</v>
+      </c>
+      <c r="D195" s="3" t="s">
         <v>2766</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>2767</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -40513,10 +40522,10 @@
         <v>2649</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>2767</v>
+      </c>
+      <c r="D196" s="3" t="s">
         <v>2768</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>2769</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -40524,10 +40533,10 @@
         <v>2649</v>
       </c>
       <c r="B197" s="3" t="s">
+        <v>2769</v>
+      </c>
+      <c r="D197" s="3" t="s">
         <v>2770</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>2771</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -40535,10 +40544,10 @@
         <v>2649</v>
       </c>
       <c r="B198" s="3" t="s">
+        <v>2771</v>
+      </c>
+      <c r="D198" s="3" t="s">
         <v>2772</v>
-      </c>
-      <c r="C198" s="3" t="s">
-        <v>2773</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -40546,10 +40555,10 @@
         <v>2649</v>
       </c>
       <c r="B199" s="3" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C199" s="3" t="s">
         <v>2774</v>
-      </c>
-      <c r="C199" s="3" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -40560,7 +40569,7 @@
         <v>2775</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>2776</v>
+        <v>592</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -40568,10 +40577,10 @@
         <v>2649</v>
       </c>
       <c r="B201" s="3" t="s">
+        <v>2776</v>
+      </c>
+      <c r="C201" s="3" t="s">
         <v>2777</v>
-      </c>
-      <c r="C201" s="3" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -40582,7 +40591,7 @@
         <v>2778</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>518</v>
+        <v>601</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -40593,7 +40602,7 @@
         <v>2779</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>562</v>
+        <v>518</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -40604,7 +40613,7 @@
         <v>2780</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>2781</v>
+        <v>562</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -40612,10 +40621,10 @@
         <v>2649</v>
       </c>
       <c r="B205" s="3" t="s">
+        <v>2781</v>
+      </c>
+      <c r="C205" s="3" t="s">
         <v>2782</v>
-      </c>
-      <c r="C205" s="3" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -40625,8 +40634,8 @@
       <c r="B206" s="3" t="s">
         <v>2783</v>
       </c>
-      <c r="D206" s="3" t="s">
-        <v>2784</v>
+      <c r="C206" s="3" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -40634,10 +40643,10 @@
         <v>2649</v>
       </c>
       <c r="B207" s="3" t="s">
+        <v>2784</v>
+      </c>
+      <c r="D207" s="3" t="s">
         <v>2785</v>
-      </c>
-      <c r="D207" s="3" t="s">
-        <v>2786</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -40645,10 +40654,10 @@
         <v>2649</v>
       </c>
       <c r="B208" s="3" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D208" s="3" t="s">
         <v>2787</v>
-      </c>
-      <c r="D208" s="3" t="s">
-        <v>2788</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -40656,10 +40665,10 @@
         <v>2649</v>
       </c>
       <c r="B209" s="3" t="s">
+        <v>2788</v>
+      </c>
+      <c r="D209" s="3" t="s">
         <v>2789</v>
-      </c>
-      <c r="C209" s="3" t="s">
-        <v>2790</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -40667,10 +40676,10 @@
         <v>2649</v>
       </c>
       <c r="B210" s="3" t="s">
+        <v>2790</v>
+      </c>
+      <c r="C210" s="3" t="s">
         <v>2791</v>
-      </c>
-      <c r="C210" s="3" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -40681,7 +40690,7 @@
         <v>2792</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -40692,7 +40701,7 @@
         <v>2793</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>596</v>
+        <v>574</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -40702,8 +40711,8 @@
       <c r="B213" s="3" t="s">
         <v>2794</v>
       </c>
-      <c r="D213" s="3" t="s">
-        <v>2795</v>
+      <c r="C213" s="3" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -40711,10 +40720,10 @@
         <v>2649</v>
       </c>
       <c r="B214" s="3" t="s">
+        <v>2795</v>
+      </c>
+      <c r="D214" s="3" t="s">
         <v>2796</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>2797</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -40722,10 +40731,10 @@
         <v>2649</v>
       </c>
       <c r="B215" s="3" t="s">
+        <v>2797</v>
+      </c>
+      <c r="D215" s="3" t="s">
         <v>2798</v>
-      </c>
-      <c r="D215" s="3" t="s">
-        <v>2799</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -40733,10 +40742,10 @@
         <v>2649</v>
       </c>
       <c r="B216" s="3" t="s">
+        <v>2799</v>
+      </c>
+      <c r="D216" s="3" t="s">
         <v>2800</v>
-      </c>
-      <c r="C216" s="3" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -40747,7 +40756,7 @@
         <v>2801</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>555</v>
+        <v>530</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -40758,7 +40767,7 @@
         <v>2802</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>578</v>
+        <v>555</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -40768,8 +40777,8 @@
       <c r="B219" s="3" t="s">
         <v>2803</v>
       </c>
-      <c r="D219" s="3" t="s">
-        <v>2804</v>
+      <c r="C219" s="3" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -40777,10 +40786,10 @@
         <v>2649</v>
       </c>
       <c r="B220" s="3" t="s">
+        <v>2804</v>
+      </c>
+      <c r="D220" s="3" t="s">
         <v>2805</v>
-      </c>
-      <c r="C220" s="3" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -40790,8 +40799,8 @@
       <c r="B221" s="3" t="s">
         <v>2806</v>
       </c>
-      <c r="D221" s="3" t="s">
-        <v>2807</v>
+      <c r="C221" s="3" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -40799,10 +40808,10 @@
         <v>2649</v>
       </c>
       <c r="B222" s="3" t="s">
+        <v>2807</v>
+      </c>
+      <c r="D222" s="3" t="s">
         <v>2808</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -40813,7 +40822,7 @@
         <v>2809</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -40834,8 +40843,8 @@
       <c r="B225" s="3" t="s">
         <v>2811</v>
       </c>
-      <c r="D225" s="3" t="s">
-        <v>2812</v>
+      <c r="C225" s="3" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -40843,10 +40852,10 @@
         <v>2649</v>
       </c>
       <c r="B226" s="3" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D226" s="3" t="s">
         <v>2813</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -40856,8 +40865,8 @@
       <c r="B227" s="3" t="s">
         <v>2814</v>
       </c>
-      <c r="D227" s="3" t="s">
-        <v>2815</v>
+      <c r="C227" s="3" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -40865,10 +40874,10 @@
         <v>2649</v>
       </c>
       <c r="B228" s="3" t="s">
+        <v>2815</v>
+      </c>
+      <c r="D228" s="3" t="s">
         <v>2816</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -40879,7 +40888,7 @@
         <v>2817</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>551</v>
+        <v>524</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -40890,7 +40899,7 @@
         <v>2818</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>588</v>
+        <v>551</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -40901,7 +40910,7 @@
         <v>2819</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -40911,8 +40920,8 @@
       <c r="B232" s="3" t="s">
         <v>2820</v>
       </c>
-      <c r="D232" s="3" t="s">
-        <v>2821</v>
+      <c r="C232" s="3" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -40920,10 +40929,10 @@
         <v>2649</v>
       </c>
       <c r="B233" s="3" t="s">
+        <v>2821</v>
+      </c>
+      <c r="D233" s="3" t="s">
         <v>2822</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>2823</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -40931,10 +40940,10 @@
         <v>2649</v>
       </c>
       <c r="B234" s="3" t="s">
+        <v>2823</v>
+      </c>
+      <c r="D234" s="3" t="s">
         <v>2824</v>
-      </c>
-      <c r="D234" s="3" t="s">
-        <v>2825</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -40942,10 +40951,10 @@
         <v>2649</v>
       </c>
       <c r="B235" s="3" t="s">
+        <v>2825</v>
+      </c>
+      <c r="D235" s="3" t="s">
         <v>2826</v>
-      </c>
-      <c r="C235" s="3" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -40956,7 +40965,7 @@
         <v>2827</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -40967,7 +40976,7 @@
         <v>2828</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -40978,7 +40987,7 @@
         <v>2829</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -40989,7 +40998,7 @@
         <v>2830</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -41000,7 +41009,7 @@
         <v>2831</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -41011,7 +41020,7 @@
         <v>2832</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>2833</v>
+        <v>657</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -41019,10 +41028,10 @@
         <v>2649</v>
       </c>
       <c r="B242" s="3" t="s">
+        <v>2833</v>
+      </c>
+      <c r="C242" s="3" t="s">
         <v>2834</v>
-      </c>
-      <c r="C242" s="3" t="s">
-        <v>2835</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -41030,10 +41039,10 @@
         <v>2649</v>
       </c>
       <c r="B243" s="3" t="s">
+        <v>2835</v>
+      </c>
+      <c r="C243" s="3" t="s">
         <v>2836</v>
-      </c>
-      <c r="C243" s="3" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -41044,7 +41053,7 @@
         <v>2837</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>494</v>
+        <v>677</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -41055,7 +41064,7 @@
         <v>2838</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -41066,7 +41075,7 @@
         <v>2839</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -41077,7 +41086,7 @@
         <v>2840</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -41087,8 +41096,8 @@
       <c r="B248" s="3" t="s">
         <v>2841</v>
       </c>
-      <c r="D248" s="3" t="s">
-        <v>2842</v>
+      <c r="C248" s="3" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -41096,10 +41105,10 @@
         <v>2649</v>
       </c>
       <c r="B249" s="3" t="s">
+        <v>2842</v>
+      </c>
+      <c r="D249" s="3" t="s">
         <v>2843</v>
-      </c>
-      <c r="D249" s="3" t="s">
-        <v>2844</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -41107,10 +41116,10 @@
         <v>2649</v>
       </c>
       <c r="B250" s="3" t="s">
+        <v>2844</v>
+      </c>
+      <c r="D250" s="3" t="s">
         <v>2845</v>
-      </c>
-      <c r="C250" s="3" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -41121,7 +41130,7 @@
         <v>2846</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>686</v>
+        <v>727</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -41132,7 +41141,7 @@
         <v>2847</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>2848</v>
+        <v>686</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -41140,10 +41149,10 @@
         <v>2649</v>
       </c>
       <c r="B253" s="3" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C253" s="3" t="s">
         <v>2849</v>
-      </c>
-      <c r="C253" s="3" t="s">
-        <v>2850</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -41151,10 +41160,10 @@
         <v>2649</v>
       </c>
       <c r="B254" s="3" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C254" s="3" t="s">
         <v>2851</v>
-      </c>
-      <c r="C254" s="3" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -41165,7 +41174,7 @@
         <v>2852</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>2853</v>
+        <v>703</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -41173,10 +41182,10 @@
         <v>2649</v>
       </c>
       <c r="B256" s="3" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C256" s="3" t="s">
         <v>2854</v>
-      </c>
-      <c r="C256" s="3" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -41187,7 +41196,7 @@
         <v>2855</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -41198,7 +41207,7 @@
         <v>2856</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>724</v>
+        <v>708</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -41209,7 +41218,7 @@
         <v>2857</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -41219,8 +41228,8 @@
       <c r="B260" s="3" t="s">
         <v>2858</v>
       </c>
-      <c r="D260" s="3" t="s">
-        <v>2859</v>
+      <c r="C260" s="3" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -41228,10 +41237,10 @@
         <v>2649</v>
       </c>
       <c r="B261" s="3" t="s">
+        <v>2859</v>
+      </c>
+      <c r="D261" s="3" t="s">
         <v>2860</v>
-      </c>
-      <c r="C261" s="3" t="s">
-        <v>2861</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -41239,10 +41248,10 @@
         <v>2649</v>
       </c>
       <c r="B262" s="3" t="s">
+        <v>2861</v>
+      </c>
+      <c r="C262" s="3" t="s">
         <v>2862</v>
-      </c>
-      <c r="C262" s="3" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -41253,7 +41262,7 @@
         <v>2863</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>772</v>
+        <v>742</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -41264,7 +41273,7 @@
         <v>2864</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -41275,7 +41284,7 @@
         <v>2865</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>781</v>
+        <v>760</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -41286,7 +41295,7 @@
         <v>2866</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -41297,7 +41306,7 @@
         <v>2867</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>751</v>
+        <v>769</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -41308,7 +41317,7 @@
         <v>2868</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>2869</v>
+        <v>751</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -41316,10 +41325,10 @@
         <v>2649</v>
       </c>
       <c r="B269" s="3" t="s">
+        <v>2869</v>
+      </c>
+      <c r="C269" s="3" t="s">
         <v>2870</v>
-      </c>
-      <c r="C269" s="3" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -41330,7 +41339,7 @@
         <v>2871</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>736</v>
+        <v>788</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -41341,7 +41350,7 @@
         <v>2872</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -41363,18 +41372,18 @@
         <v>2874</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>794</v>
+        <v>747</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="3" t="s">
-        <v>615</v>
+        <v>2649</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>2875</v>
       </c>
-      <c r="D274" s="3" t="s">
-        <v>2876</v>
+      <c r="C274" s="3" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -41382,10 +41391,10 @@
         <v>615</v>
       </c>
       <c r="B275" s="3" t="s">
+        <v>2876</v>
+      </c>
+      <c r="D275" s="3" t="s">
         <v>2877</v>
-      </c>
-      <c r="D275" s="3" t="s">
-        <v>2878</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -41393,10 +41402,10 @@
         <v>615</v>
       </c>
       <c r="B276" s="3" t="s">
+        <v>2878</v>
+      </c>
+      <c r="D276" s="3" t="s">
         <v>2879</v>
-      </c>
-      <c r="D276" s="3" t="s">
-        <v>2880</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -41404,10 +41413,10 @@
         <v>615</v>
       </c>
       <c r="B277" s="3" t="s">
+        <v>2880</v>
+      </c>
+      <c r="D277" s="3" t="s">
         <v>2881</v>
-      </c>
-      <c r="D277" s="3" t="s">
-        <v>2876</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -41418,7 +41427,7 @@
         <v>2882</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -41429,7 +41438,7 @@
         <v>2883</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -41439,8 +41448,8 @@
       <c r="B280" s="3" t="s">
         <v>2884</v>
       </c>
-      <c r="C280" s="3" t="s">
-        <v>490</v>
+      <c r="D280" s="3" t="s">
+        <v>2877</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -41450,8 +41459,8 @@
       <c r="B281" s="3" t="s">
         <v>2885</v>
       </c>
-      <c r="D281" s="3" t="s">
-        <v>2886</v>
+      <c r="C281" s="3" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -41459,10 +41468,10 @@
         <v>615</v>
       </c>
       <c r="B282" s="3" t="s">
+        <v>2886</v>
+      </c>
+      <c r="D282" s="3" t="s">
         <v>2887</v>
-      </c>
-      <c r="D282" s="3" t="s">
-        <v>2888</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -41470,10 +41479,10 @@
         <v>615</v>
       </c>
       <c r="B283" s="3" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D283" s="3" t="s">
         <v>2889</v>
-      </c>
-      <c r="D283" s="3" t="s">
-        <v>2890</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -41481,10 +41490,10 @@
         <v>615</v>
       </c>
       <c r="B284" s="3" t="s">
+        <v>2890</v>
+      </c>
+      <c r="D284" s="3" t="s">
         <v>2891</v>
-      </c>
-      <c r="D284" s="3" t="s">
-        <v>2892</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -41492,10 +41501,10 @@
         <v>615</v>
       </c>
       <c r="B285" s="3" t="s">
+        <v>2892</v>
+      </c>
+      <c r="D285" s="3" t="s">
         <v>2893</v>
-      </c>
-      <c r="D285" s="3" t="s">
-        <v>2894</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -41503,10 +41512,10 @@
         <v>615</v>
       </c>
       <c r="B286" s="3" t="s">
+        <v>2894</v>
+      </c>
+      <c r="D286" s="3" t="s">
         <v>2895</v>
-      </c>
-      <c r="D286" s="3" t="s">
-        <v>2896</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -41514,10 +41523,10 @@
         <v>615</v>
       </c>
       <c r="B287" s="3" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D287" s="3" t="s">
         <v>2897</v>
-      </c>
-      <c r="D287" s="3" t="s">
-        <v>2898</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -41525,10 +41534,10 @@
         <v>615</v>
       </c>
       <c r="B288" s="3" t="s">
+        <v>2898</v>
+      </c>
+      <c r="D288" s="3" t="s">
         <v>2899</v>
-      </c>
-      <c r="D288" s="3" t="s">
-        <v>2900</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -41536,10 +41545,10 @@
         <v>615</v>
       </c>
       <c r="B289" s="3" t="s">
+        <v>2900</v>
+      </c>
+      <c r="D289" s="3" t="s">
         <v>2901</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>2902</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -41547,10 +41556,10 @@
         <v>615</v>
       </c>
       <c r="B290" s="3" t="s">
+        <v>2902</v>
+      </c>
+      <c r="D290" s="3" t="s">
         <v>2903</v>
-      </c>
-      <c r="D290" s="3" t="s">
-        <v>2904</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -41558,14 +41567,25 @@
         <v>615</v>
       </c>
       <c r="B291" s="3" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D291" s="3" t="s">
         <v>2905</v>
       </c>
-      <c r="D291" s="3" t="s">
-        <v>2876</v>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>2906</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>2877</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D291"/>
+  <autoFilter ref="A1:D292"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not in the list" error="Pick one of: operation, job, schedule, handler." promptTitle="Kind" prompt="operation, job, schedule or handler" sqref="A2:A2001">
       <formula1>"operation,job,schedule,handler"</formula1>
@@ -41580,7 +41600,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -41590,314 +41610,328 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B7" s="3">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B8" s="3">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B14" s="3">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B15" s="3">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="B16" s="3">
         <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="B17" s="3">
         <v>17</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="B18" s="3">
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="B19" s="3">
         <v>19</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B20" s="3">
         <v>20</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="3" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B21" s="3">
         <v>21</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B22" s="3">
         <v>22</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2956</v>
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="3" t="s">
+        <v>2951</v>
+      </c>
+      <c r="B23" s="3">
+        <v>23</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>2958</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>2959</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D22"/>
+  <autoFilter ref="A1:D23"/>
   <dataValidations count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Date" prompt="YYYY-MM-DD" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Plan version" prompt="From 1, one per change." sqref="B2:B2001"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -18,9 +18,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Actors!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$292</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$475</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$294</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$477</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$174</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$367</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Records!$A$1:$I$272</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8982" uniqueCount="2960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8997" uniqueCount="2968">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Plan version</t>
   </si>
   <si>
-    <t>23 (2026-10-28)</t>
+    <t>26 (2026-10-28)</t>
   </si>
   <si>
     <t>What this is</t>
@@ -6644,6 +6644,18 @@
     <t>The member took it back (Undo).</t>
   </si>
   <si>
+    <t>destination_changed</t>
+  </si>
+  <si>
+    <t>The inbox no longer sends from where the author's request was bound.</t>
+  </si>
+  <si>
+    <t>release_lost</t>
+  </si>
+  <si>
+    <t>A scheduled send was long overdue with no release job; it was not sent, and may never have been.</t>
+  </si>
+  <si>
     <t>sender_may_not_send</t>
   </si>
   <si>
@@ -7895,6 +7907,9 @@
     <t>maintenance, no action of anyone: MACs re-tagged after a key rotation</t>
   </si>
   <si>
+    <t>conversations.sweep_overdue_sends</t>
+  </si>
+  <si>
     <t>conversations.wake_needs</t>
   </si>
   <si>
@@ -8684,6 +8699,9 @@
     <t>conversations.dispatch_needs_backfills</t>
   </si>
   <si>
+    <t>conversations.dispatch_overdue_sends</t>
+  </si>
+  <si>
     <t>conversations.dispatch_rule_resigns</t>
   </si>
   <si>
@@ -8910,6 +8928,12 @@
   </si>
   <si>
     <t>#699</t>
+  </si>
+  <si>
+    <t>Send later review fixes (campbooks-cloud#392): conversations.unschedule_reason gains destination_changed (the inbox no longer sends from where the request was bound) and release_lost (a scheduled send found overdue with no release job); Coverage for the sweep job and its schedule.</t>
+  </si>
+  <si>
+    <t>#705</t>
   </si>
 </sst>
 </file>
@@ -33005,7 +33029,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C475"/>
+  <dimension ref="A1:C477"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -36293,7 +36317,7 @@
     </row>
     <row r="299" spans="1:3">
       <c r="A299" s="3" t="s">
-        <v>1051</v>
+        <v>943</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>2206</v>
@@ -36304,7 +36328,7 @@
     </row>
     <row r="300" spans="1:3">
       <c r="A300" s="3" t="s">
-        <v>1051</v>
+        <v>943</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>2208</v>
@@ -36318,10 +36342,10 @@
         <v>1051</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>61</v>
+        <v>2210</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -36329,10 +36353,10 @@
         <v>1051</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -36340,51 +36364,51 @@
         <v>1051</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304" s="3" t="s">
-        <v>1034</v>
+        <v>1051</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>2030</v>
+        <v>2215</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="3" t="s">
-        <v>1034</v>
+        <v>1051</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>169</v>
+        <v>75</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" s="3" t="s">
-        <v>1564</v>
+        <v>1034</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>2216</v>
+        <v>2030</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" s="3" t="s">
-        <v>1564</v>
+        <v>1034</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>2218</v>
+        <v>169</v>
       </c>
       <c r="C307" s="3" t="s">
         <v>2219</v>
@@ -36403,46 +36427,46 @@
     </row>
     <row r="309" spans="1:3">
       <c r="A309" s="3" t="s">
-        <v>1539</v>
+        <v>1564</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>447</v>
+        <v>2222</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" s="3" t="s">
-        <v>1539</v>
+        <v>1564</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>2220</v>
+        <v>2224</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" s="3" t="s">
-        <v>1029</v>
+        <v>1539</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>2018</v>
+        <v>447</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" s="3" t="s">
-        <v>1029</v>
+        <v>1539</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>2022</v>
+        <v>2224</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -36450,32 +36474,32 @@
         <v>1029</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" s="3" t="s">
-        <v>1081</v>
+        <v>1029</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>1928</v>
+        <v>2022</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" s="3" t="s">
-        <v>1081</v>
+        <v>1029</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>2228</v>
+        <v>2026</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -36483,7 +36507,7 @@
         <v>1081</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>2230</v>
+        <v>1928</v>
       </c>
       <c r="C316" s="3" t="s">
         <v>2231</v>
@@ -36557,43 +36581,43 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323" s="3" t="s">
-        <v>1027</v>
+        <v>1081</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>447</v>
+        <v>2244</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" s="3" t="s">
-        <v>1027</v>
+        <v>1081</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>904</v>
+        <v>2246</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" s="3" t="s">
-        <v>1097</v>
+        <v>1027</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>2246</v>
+        <v>447</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" s="3" t="s">
-        <v>1097</v>
+        <v>1027</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>2248</v>
+        <v>904</v>
       </c>
       <c r="C326" s="3" t="s">
         <v>2249</v>
@@ -36604,32 +36628,32 @@
         <v>1097</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>743</v>
+        <v>2250</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" s="3" t="s">
-        <v>1574</v>
+        <v>1097</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>184</v>
+        <v>2252</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" s="3" t="s">
-        <v>1574</v>
+        <v>1097</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>1889</v>
+        <v>743</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -36637,29 +36661,29 @@
         <v>1574</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>2185</v>
+        <v>184</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" s="3" t="s">
-        <v>1121</v>
+        <v>1574</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>2254</v>
+        <v>1889</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" s="3" t="s">
-        <v>1121</v>
+        <v>1574</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>2256</v>
+        <v>2185</v>
       </c>
       <c r="C332" s="3" t="s">
         <v>2257</v>
@@ -36670,29 +36694,29 @@
         <v>1121</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>2024</v>
+        <v>2258</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" s="3" t="s">
-        <v>1111</v>
+        <v>1121</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" s="3" t="s">
-        <v>1111</v>
+        <v>1121</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>2261</v>
+        <v>2024</v>
       </c>
       <c r="C335" s="3" t="s">
         <v>2262</v>
@@ -36733,7 +36757,7 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339" s="3" t="s">
-        <v>1144</v>
+        <v>1111</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>2269</v>
@@ -36744,7 +36768,7 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340" s="3" t="s">
-        <v>1144</v>
+        <v>1111</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>2271</v>
@@ -36755,7 +36779,7 @@
     </row>
     <row r="341" spans="1:3">
       <c r="A341" s="3" t="s">
-        <v>1153</v>
+        <v>1144</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>2273</v>
@@ -36766,7 +36790,7 @@
     </row>
     <row r="342" spans="1:3">
       <c r="A342" s="3" t="s">
-        <v>1153</v>
+        <v>1144</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>2275</v>
@@ -36788,7 +36812,7 @@
     </row>
     <row r="344" spans="1:3">
       <c r="A344" s="3" t="s">
-        <v>1583</v>
+        <v>1153</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>2279</v>
@@ -36799,32 +36823,32 @@
     </row>
     <row r="345" spans="1:3">
       <c r="A345" s="3" t="s">
-        <v>1583</v>
+        <v>1153</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>75</v>
+        <v>2281</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="3" t="s">
-        <v>1160</v>
+        <v>1583</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" s="3" t="s">
-        <v>1160</v>
+        <v>1583</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>2284</v>
+        <v>75</v>
       </c>
       <c r="C347" s="3" t="s">
         <v>2285</v>
@@ -36835,10 +36859,10 @@
         <v>1160</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>255</v>
+        <v>2286</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -36846,10 +36870,10 @@
         <v>1160</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>1223</v>
+        <v>2288</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -36857,10 +36881,10 @@
         <v>1160</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>514</v>
+        <v>255</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -36868,10 +36892,10 @@
         <v>1160</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>2289</v>
+        <v>1223</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -36879,10 +36903,10 @@
         <v>1160</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -36890,10 +36914,10 @@
         <v>1160</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -36901,7 +36925,7 @@
         <v>1160</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>2294</v>
+        <v>519</v>
       </c>
       <c r="C354" s="3" t="s">
         <v>2295</v>
@@ -36956,10 +36980,10 @@
         <v>1160</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>1425</v>
+        <v>2304</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -36967,10 +36991,10 @@
         <v>1160</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -36978,7 +37002,7 @@
         <v>1160</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>2307</v>
+        <v>1425</v>
       </c>
       <c r="C361" s="3" t="s">
         <v>2308</v>
@@ -36997,7 +37021,7 @@
     </row>
     <row r="363" spans="1:3">
       <c r="A363" s="3" t="s">
-        <v>1129</v>
+        <v>1160</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>2311</v>
@@ -37008,7 +37032,7 @@
     </row>
     <row r="364" spans="1:3">
       <c r="A364" s="3" t="s">
-        <v>1129</v>
+        <v>1160</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>2313</v>
@@ -37019,24 +37043,24 @@
     </row>
     <row r="365" spans="1:3">
       <c r="A365" s="3" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>2028</v>
+        <v>2315</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" s="3" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>2030</v>
+        <v>2317</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -37044,10 +37068,10 @@
         <v>1132</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>2317</v>
+        <v>2028</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -37055,7 +37079,7 @@
         <v>1132</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>2319</v>
+        <v>2030</v>
       </c>
       <c r="C368" s="3" t="s">
         <v>2320</v>
@@ -37096,7 +37120,7 @@
     </row>
     <row r="372" spans="1:3">
       <c r="A372" s="3" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>2327</v>
@@ -37107,40 +37131,40 @@
     </row>
     <row r="373" spans="1:3">
       <c r="A373" s="3" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>2329</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>2258</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" s="3" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" s="3" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>2333</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" s="3" t="s">
-        <v>1165</v>
+        <v>1136</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>2334</v>
@@ -37151,35 +37175,35 @@
     </row>
     <row r="377" spans="1:3">
       <c r="A377" s="3" t="s">
-        <v>1165</v>
+        <v>1136</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>607</v>
+        <v>2336</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="3" t="s">
-        <v>1629</v>
+        <v>1165</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>1954</v>
+        <v>2338</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" s="3" t="s">
-        <v>1629</v>
+        <v>1165</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>1956</v>
+        <v>607</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -37187,10 +37211,10 @@
         <v>1629</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>1957</v>
+        <v>1954</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -37198,10 +37222,10 @@
         <v>1629</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -37209,76 +37233,76 @@
         <v>1629</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="3" t="s">
-        <v>1204</v>
+        <v>1629</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>2342</v>
+        <v>1958</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" s="3" t="s">
-        <v>1204</v>
+        <v>1629</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>2256</v>
+        <v>1959</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" s="3" t="s">
-        <v>1596</v>
+        <v>1204</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" s="3" t="s">
-        <v>1596</v>
+        <v>1204</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>904</v>
+        <v>2260</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="3" t="s">
-        <v>1184</v>
+        <v>1596</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>1606</v>
+        <v>2349</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" s="3" t="s">
-        <v>1184</v>
+        <v>1596</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>1006</v>
+        <v>904</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -37286,10 +37310,10 @@
         <v>1184</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>2350</v>
+        <v>1606</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -37297,10 +37321,10 @@
         <v>1184</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>1582</v>
+        <v>1006</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -37308,10 +37332,10 @@
         <v>1184</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>1595</v>
+        <v>2354</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -37319,10 +37343,10 @@
         <v>1184</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>1425</v>
+        <v>1582</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -37330,10 +37354,10 @@
         <v>1184</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>2355</v>
+        <v>1595</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -37341,32 +37365,32 @@
         <v>1184</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>2271</v>
+        <v>1425</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>2272</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="3" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" s="3" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>2359</v>
+        <v>2275</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>2360</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -37418,10 +37442,10 @@
         <v>1181</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>2263</v>
+        <v>2369</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -37429,10 +37453,10 @@
         <v>1181</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -37440,7 +37464,7 @@
         <v>1181</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>2372</v>
+        <v>2267</v>
       </c>
       <c r="C403" s="3" t="s">
         <v>2373</v>
@@ -37470,7 +37494,7 @@
     </row>
     <row r="406" spans="1:3">
       <c r="A406" s="3" t="s">
-        <v>1624</v>
+        <v>1181</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>2378</v>
@@ -37481,7 +37505,7 @@
     </row>
     <row r="407" spans="1:3">
       <c r="A407" s="3" t="s">
-        <v>1624</v>
+        <v>1181</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>2380</v>
@@ -37492,24 +37516,24 @@
     </row>
     <row r="408" spans="1:3">
       <c r="A408" s="3" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>743</v>
+        <v>2382</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" s="3" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>904</v>
+        <v>2384</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -37517,32 +37541,32 @@
         <v>1626</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>2384</v>
+        <v>743</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="3" t="s">
-        <v>1648</v>
+        <v>1626</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>630</v>
+        <v>904</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" s="3" t="s">
-        <v>1648</v>
+        <v>1626</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>99</v>
+        <v>2388</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -37550,76 +37574,76 @@
         <v>1648</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>2388</v>
+        <v>630</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" s="3" t="s">
-        <v>1619</v>
+        <v>1648</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>2091</v>
+        <v>99</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" s="3" t="s">
-        <v>1619</v>
+        <v>1648</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>2144</v>
+        <v>2392</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" s="3" t="s">
-        <v>1593</v>
+        <v>1619</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>2018</v>
+        <v>2091</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" s="3" t="s">
-        <v>1593</v>
+        <v>1619</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>2026</v>
+        <v>2144</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" s="3" t="s">
-        <v>1189</v>
+        <v>1593</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>2394</v>
+        <v>2018</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="3" t="s">
-        <v>1189</v>
+        <v>1593</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>103</v>
+        <v>2026</v>
       </c>
       <c r="C419" s="3" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -37627,10 +37651,10 @@
         <v>1189</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -37638,29 +37662,29 @@
         <v>1189</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>2388</v>
+        <v>103</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" s="3" t="s">
-        <v>1213</v>
+        <v>1189</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" s="3" t="s">
-        <v>1213</v>
+        <v>1189</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>2402</v>
+        <v>2392</v>
       </c>
       <c r="C423" s="3" t="s">
         <v>2403</v>
@@ -37671,10 +37695,10 @@
         <v>1213</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>1657</v>
+        <v>2404</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -37682,10 +37706,10 @@
         <v>1213</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>2355</v>
+        <v>2406</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -37693,18 +37717,18 @@
         <v>1213</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>2406</v>
+        <v>1657</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="3" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>2408</v>
+        <v>2359</v>
       </c>
       <c r="C427" s="3" t="s">
         <v>2409</v>
@@ -37712,13 +37736,13 @@
     </row>
     <row r="428" spans="1:3">
       <c r="A428" s="3" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>1896</v>
+        <v>2410</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -37726,10 +37750,10 @@
         <v>1218</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="C429" s="3" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -37737,7 +37761,7 @@
         <v>1218</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>2413</v>
+        <v>1896</v>
       </c>
       <c r="C430" s="3" t="s">
         <v>2414</v>
@@ -37745,68 +37769,68 @@
     </row>
     <row r="431" spans="1:3">
       <c r="A431" s="3" t="s">
-        <v>1241</v>
+        <v>1218</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>616</v>
+        <v>2415</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" s="3" t="s">
-        <v>1241</v>
+        <v>1218</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>743</v>
+        <v>2417</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" s="3" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>2345</v>
+        <v>616</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" s="3" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>904</v>
+        <v>743</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>2347</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" s="3" t="s">
-        <v>1684</v>
+        <v>1243</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>1223</v>
+        <v>2349</v>
       </c>
       <c r="C435" s="3" t="s">
-        <v>2418</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" s="3" t="s">
-        <v>1684</v>
+        <v>1243</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>1835</v>
+        <v>904</v>
       </c>
       <c r="C436" s="3" t="s">
-        <v>2419</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -37814,29 +37838,29 @@
         <v>1684</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>2263</v>
+        <v>1223</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438" s="3" t="s">
-        <v>1261</v>
+        <v>1684</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>2421</v>
+        <v>1835</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" s="3" t="s">
-        <v>1261</v>
+        <v>1684</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>2423</v>
+        <v>2267</v>
       </c>
       <c r="C439" s="3" t="s">
         <v>2424</v>
@@ -37844,43 +37868,43 @@
     </row>
     <row r="440" spans="1:3">
       <c r="A440" s="3" t="s">
-        <v>1238</v>
+        <v>1261</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>2271</v>
+        <v>2425</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>2272</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" s="3" t="s">
-        <v>1238</v>
+        <v>1261</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>1691</v>
+        <v>2427</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" s="3" t="s">
-        <v>1681</v>
+        <v>1238</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>2426</v>
+        <v>2275</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>2427</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" s="3" t="s">
-        <v>1681</v>
+        <v>1238</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>2428</v>
+        <v>1691</v>
       </c>
       <c r="C443" s="3" t="s">
         <v>2429</v>
@@ -37899,24 +37923,24 @@
     </row>
     <row r="445" spans="1:3">
       <c r="A445" s="3" t="s">
-        <v>1264</v>
+        <v>1681</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>693</v>
+        <v>2432</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" s="3" t="s">
-        <v>1264</v>
+        <v>1681</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>713</v>
+        <v>2434</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -37924,51 +37948,51 @@
         <v>1264</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>1894</v>
+        <v>693</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" s="3" t="s">
-        <v>1236</v>
+        <v>1264</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>1898</v>
+        <v>713</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>1899</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" s="3" t="s">
-        <v>1236</v>
+        <v>1264</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>1902</v>
+        <v>1894</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>2435</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" s="3" t="s">
-        <v>1730</v>
+        <v>1236</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>2436</v>
+        <v>1898</v>
       </c>
       <c r="C450" s="3" t="s">
-        <v>2437</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" s="3" t="s">
-        <v>1730</v>
+        <v>1236</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>2438</v>
+        <v>1902</v>
       </c>
       <c r="C451" s="3" t="s">
         <v>2439</v>
@@ -37987,46 +38011,46 @@
     </row>
     <row r="453" spans="1:3">
       <c r="A453" s="3" t="s">
-        <v>1278</v>
+        <v>1730</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>748</v>
+        <v>2442</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" s="3" t="s">
-        <v>1278</v>
+        <v>1730</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>169</v>
+        <v>2444</v>
       </c>
       <c r="C454" s="3" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" s="3" t="s">
-        <v>1707</v>
+        <v>1278</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>2394</v>
+        <v>748</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" s="3" t="s">
-        <v>1707</v>
+        <v>1278</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>2445</v>
+        <v>169</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -38034,98 +38058,98 @@
         <v>1707</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>1889</v>
+        <v>2398</v>
       </c>
       <c r="C457" s="3" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" s="3" t="s">
-        <v>1275</v>
+        <v>1707</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>255</v>
+        <v>2449</v>
       </c>
       <c r="C458" s="3" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" s="3" t="s">
-        <v>1275</v>
+        <v>1707</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>738</v>
+        <v>1889</v>
       </c>
       <c r="C459" s="3" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="3" t="s">
-        <v>1734</v>
+        <v>1275</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>2436</v>
+        <v>255</v>
       </c>
       <c r="C460" s="3" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" s="3" t="s">
-        <v>1734</v>
+        <v>1275</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>2440</v>
+        <v>738</v>
       </c>
       <c r="C461" s="3" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" s="3" t="s">
-        <v>1280</v>
+        <v>1734</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>1956</v>
+        <v>2440</v>
       </c>
       <c r="C462" s="3" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" s="3" t="s">
-        <v>1280</v>
+        <v>1734</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>2011</v>
+        <v>2444</v>
       </c>
       <c r="C463" s="3" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" s="3" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>58</v>
+        <v>1956</v>
       </c>
       <c r="C464" s="3" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" s="3" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>743</v>
+        <v>2011</v>
       </c>
       <c r="C465" s="3" t="s">
-        <v>2090</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -38133,32 +38157,32 @@
         <v>1283</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>2455</v>
+        <v>58</v>
       </c>
       <c r="C466" s="3" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" s="3" t="s">
-        <v>1718</v>
+        <v>1283</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>2174</v>
+        <v>743</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>2457</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="3" t="s">
-        <v>1718</v>
+        <v>1283</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>2445</v>
+        <v>2459</v>
       </c>
       <c r="C468" s="3" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -38166,10 +38190,10 @@
         <v>1718</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>68</v>
+        <v>2174</v>
       </c>
       <c r="C469" s="3" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -38177,32 +38201,32 @@
         <v>1718</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>2460</v>
+        <v>2449</v>
       </c>
       <c r="C470" s="3" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" s="3" t="s">
-        <v>1292</v>
+        <v>1718</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>774</v>
+        <v>68</v>
       </c>
       <c r="C471" s="3" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" s="3" t="s">
-        <v>1292</v>
+        <v>1718</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>1889</v>
+        <v>2464</v>
       </c>
       <c r="C472" s="3" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -38210,36 +38234,58 @@
         <v>1292</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" s="3" t="s">
-        <v>1303</v>
+        <v>1292</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>1729</v>
+        <v>1889</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>1731</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B475" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="C475" s="3" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3">
+      <c r="A476" s="3" t="s">
         <v>1303</v>
       </c>
-      <c r="B475" s="3" t="s">
-        <v>2465</v>
-      </c>
-      <c r="C475" s="3" t="s">
-        <v>2466</v>
+      <c r="B476" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C476" s="3" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3">
+      <c r="A477" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B477" s="3" t="s">
+        <v>2469</v>
+      </c>
+      <c r="C477" s="3" t="s">
+        <v>2470</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C475"/>
+  <autoFilter ref="A1:C477"/>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Enum" prompt="&lt;module&gt;.&lt;enum&gt;" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Value" prompt="snake_case" sqref="B2:B2001"/>
@@ -38261,10 +38307,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>2467</v>
+        <v>2471</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>2468</v>
+        <v>2472</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>53</v>
@@ -38275,10 +38321,10 @@
         <v>326</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2469</v>
+        <v>2473</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2470</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -38286,10 +38332,10 @@
         <v>386</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2471</v>
+        <v>2475</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2472</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -38297,21 +38343,21 @@
         <v>72</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2473</v>
+        <v>2477</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2474</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>2475</v>
+        <v>2479</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2473</v>
+        <v>2477</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2476</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -38319,10 +38365,10 @@
         <v>63</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2477</v>
+        <v>2481</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2478</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -38330,10 +38376,10 @@
         <v>58</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2479</v>
+        <v>2483</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2480</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -38341,10 +38387,10 @@
         <v>125</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2263</v>
+        <v>2267</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2481</v>
+        <v>2485</v>
       </c>
     </row>
   </sheetData>
@@ -38360,7 +38406,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D292"/>
+  <dimension ref="A1:D294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -38371,112 +38417,112 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>2482</v>
+        <v>2486</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>2483</v>
+        <v>2487</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2484</v>
+        <v>2488</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2485</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2487</v>
+        <v>2491</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2488</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2489</v>
+        <v>2493</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2493</v>
+        <v>2497</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2494</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2495</v>
+        <v>2499</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2496</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2497</v>
+        <v>2501</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2498</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2499</v>
+        <v>2503</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2500</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>132</v>
@@ -38484,10 +38530,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>2503</v>
+        <v>2507</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>132</v>
@@ -38495,43 +38541,43 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>2504</v>
+        <v>2508</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2505</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>2506</v>
+        <v>2510</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2507</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>149</v>
@@ -38539,43 +38585,43 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2513</v>
+        <v>2517</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2514</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2516</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2517</v>
+        <v>2521</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>168</v>
@@ -38583,32 +38629,32 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2522</v>
+        <v>2526</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>292</v>
@@ -38616,10 +38662,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2523</v>
+        <v>2527</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>300</v>
@@ -38627,10 +38673,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2524</v>
+        <v>2528</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>287</v>
@@ -38638,76 +38684,76 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2526</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2527</v>
+        <v>2531</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2528</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>2529</v>
+        <v>2533</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>2531</v>
+        <v>2535</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>2532</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>2533</v>
+        <v>2537</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>2534</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>2535</v>
+        <v>2539</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>2536</v>
+        <v>2540</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>398</v>
@@ -38715,76 +38761,76 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>2537</v>
+        <v>2541</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2538</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>2539</v>
+        <v>2543</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>2540</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>2541</v>
+        <v>2545</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2542</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>2543</v>
+        <v>2547</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>2544</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>2545</v>
+        <v>2549</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>2546</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>2547</v>
+        <v>2551</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>2548</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>2549</v>
+        <v>2553</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>543</v>
@@ -38792,10 +38838,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>2550</v>
+        <v>2554</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>558</v>
@@ -38803,32 +38849,32 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>2551</v>
+        <v>2555</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>2552</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>2553</v>
+        <v>2557</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>2554</v>
+        <v>2558</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>547</v>
@@ -38836,10 +38882,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>2555</v>
+        <v>2559</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>547</v>
@@ -38847,21 +38893,21 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>2556</v>
+        <v>2560</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>2557</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>2558</v>
+        <v>2562</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>673</v>
@@ -38869,10 +38915,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>2559</v>
+        <v>2563</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>149</v>
@@ -38880,10 +38926,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>2560</v>
+        <v>2564</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>665</v>
@@ -38891,21 +38937,21 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>2561</v>
+        <v>2565</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2562</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>2563</v>
+        <v>2567</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>614</v>
@@ -38913,98 +38959,98 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>2564</v>
+        <v>2568</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>2565</v>
+        <v>2569</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>2566</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>2567</v>
+        <v>2571</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2568</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>2569</v>
+        <v>2573</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>2570</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>2571</v>
+        <v>2575</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>2572</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>2573</v>
+        <v>2577</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>2574</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>2575</v>
+        <v>2579</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>2576</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>2577</v>
+        <v>2581</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>2578</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>2579</v>
+        <v>2583</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>708</v>
@@ -39012,21 +39058,21 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>2580</v>
+        <v>2584</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>2581</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>2582</v>
+        <v>2586</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>703</v>
@@ -39034,10 +39080,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>2583</v>
+        <v>2587</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>732</v>
@@ -39045,21 +39091,21 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>2584</v>
+        <v>2588</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>754</v>
@@ -39067,10 +39113,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="3" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>2586</v>
+        <v>2590</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>757</v>
@@ -39081,10 +39127,10 @@
         <v>496</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>2587</v>
+        <v>2591</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>2588</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -39092,10 +39138,10 @@
         <v>496</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>2590</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -39103,10 +39149,10 @@
         <v>496</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>2591</v>
+        <v>2595</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>2592</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -39114,10 +39160,10 @@
         <v>496</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>2593</v>
+        <v>2597</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>2594</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -39125,7 +39171,7 @@
         <v>496</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>144</v>
@@ -39136,10 +39182,10 @@
         <v>496</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>2596</v>
+        <v>2600</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>2597</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -39147,10 +39193,10 @@
         <v>496</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>2598</v>
+        <v>2602</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -39158,7 +39204,7 @@
         <v>496</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>2600</v>
+        <v>2604</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>295</v>
@@ -39169,7 +39215,7 @@
         <v>496</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>2601</v>
+        <v>2605</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>359</v>
@@ -39180,10 +39226,10 @@
         <v>496</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>2602</v>
+        <v>2606</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2603</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -39191,7 +39237,7 @@
         <v>496</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>2604</v>
+        <v>2608</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>271</v>
@@ -39202,7 +39248,7 @@
         <v>496</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>2605</v>
+        <v>2609</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>300</v>
@@ -39213,10 +39259,10 @@
         <v>496</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>2606</v>
+        <v>2610</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>2607</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -39224,10 +39270,10 @@
         <v>496</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>2608</v>
+        <v>2612</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>2609</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -39235,10 +39281,10 @@
         <v>496</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>2610</v>
+        <v>2614</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>2611</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -39246,7 +39292,7 @@
         <v>496</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>2612</v>
+        <v>2616</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>305</v>
@@ -39257,7 +39303,7 @@
         <v>496</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>2613</v>
+        <v>2617</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>305</v>
@@ -39268,10 +39314,10 @@
         <v>496</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>2614</v>
+        <v>2618</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>2603</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -39279,10 +39325,10 @@
         <v>496</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>2615</v>
+        <v>2619</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>2616</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -39290,10 +39336,10 @@
         <v>496</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>2617</v>
+        <v>2621</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>2618</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -39301,10 +39347,10 @@
         <v>496</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>2619</v>
+        <v>2623</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>2620</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -39312,10 +39358,10 @@
         <v>496</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>2621</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>2603</v>
+        <v>2625</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -39323,10 +39369,10 @@
         <v>496</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>2622</v>
+        <v>2626</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>2623</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -39334,10 +39380,10 @@
         <v>496</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>2624</v>
+        <v>2627</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>2625</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -39345,10 +39391,10 @@
         <v>496</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>2626</v>
+        <v>2629</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>2627</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -39356,10 +39402,10 @@
         <v>496</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>2628</v>
+        <v>2631</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>2629</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -39367,10 +39413,10 @@
         <v>496</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>2630</v>
+        <v>2633</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>2631</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -39378,10 +39424,10 @@
         <v>496</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>2632</v>
+        <v>2635</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>2633</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -39389,10 +39435,10 @@
         <v>496</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>2634</v>
+        <v>2637</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>2635</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -39400,10 +39446,10 @@
         <v>496</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>2636</v>
+        <v>2639</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>2637</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -39411,10 +39457,10 @@
         <v>496</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>2638</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>149</v>
+        <v>2641</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>2642</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -39422,7 +39468,7 @@
         <v>496</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>2639</v>
+        <v>2643</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>149</v>
@@ -39433,10 +39479,10 @@
         <v>496</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>2640</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>2641</v>
+        <v>2644</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -39444,10 +39490,10 @@
         <v>496</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>2642</v>
+        <v>2645</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>2643</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -39455,10 +39501,10 @@
         <v>496</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>2644</v>
+        <v>2647</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>2645</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -39466,10 +39512,10 @@
         <v>496</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>2646</v>
+        <v>2649</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>2647</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -39477,128 +39523,128 @@
         <v>496</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>2648</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>791</v>
+        <v>2651</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>2652</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="3" t="s">
-        <v>2649</v>
+        <v>496</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>2650</v>
+        <v>2653</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>2651</v>
+        <v>791</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>2652</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>2653</v>
+        <v>2655</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>2656</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>2654</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>85</v>
+        <v>2657</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>2658</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>2655</v>
+        <v>2659</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>2656</v>
+        <v>85</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>2657</v>
+        <v>2660</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>89</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>2658</v>
+        <v>2662</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>2651</v>
+        <v>89</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>2659</v>
+        <v>2663</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>93</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>2660</v>
+        <v>2664</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>2661</v>
+        <v>2665</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>2662</v>
+        <v>2666</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>2663</v>
+        <v>2667</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>121</v>
@@ -39606,10 +39652,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>2664</v>
+        <v>2668</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>121</v>
@@ -39617,10 +39663,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>2665</v>
+        <v>2669</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>121</v>
@@ -39628,10 +39674,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>2666</v>
+        <v>2670</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>121</v>
@@ -39639,10 +39685,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>121</v>
@@ -39650,10 +39696,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>2668</v>
+        <v>2672</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>121</v>
@@ -39661,10 +39707,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>2669</v>
+        <v>2673</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>121</v>
@@ -39672,10 +39718,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>2670</v>
+        <v>2674</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>121</v>
@@ -39683,10 +39729,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>2671</v>
+        <v>2675</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>121</v>
@@ -39694,54 +39740,54 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>2672</v>
+        <v>2676</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>2673</v>
+        <v>2677</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>2674</v>
+        <v>132</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>2675</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>2676</v>
+        <v>2678</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>2679</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>2677</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>121</v>
+        <v>2680</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>2681</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>2678</v>
+        <v>2682</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>121</v>
@@ -39749,593 +39795,593 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>2679</v>
+        <v>2683</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>2680</v>
+        <v>2684</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>2681</v>
+        <v>137</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>2682</v>
+        <v>2685</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>168</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>2683</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>2684</v>
+        <v>2687</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>2685</v>
+        <v>2688</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>2686</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>2687</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>173</v>
+        <v>2690</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>2691</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>2688</v>
+        <v>2692</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>2689</v>
+        <v>2693</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>348</v>
+        <v>204</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>2690</v>
+        <v>2694</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>196</v>
+        <v>348</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>2691</v>
+        <v>2695</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>279</v>
+        <v>196</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>2692</v>
+        <v>2696</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>343</v>
+        <v>279</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>2693</v>
+        <v>2697</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>2694</v>
+        <v>2698</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>2695</v>
+        <v>312</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>2696</v>
+        <v>2699</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>253</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>2697</v>
+        <v>2701</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>2698</v>
+        <v>253</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>2699</v>
+        <v>2702</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>340</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>2700</v>
+        <v>2704</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>259</v>
+        <v>340</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>2701</v>
+        <v>2705</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>324</v>
+        <v>259</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>2702</v>
+        <v>2706</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>2703</v>
+        <v>2707</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>213</v>
+        <v>363</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>2704</v>
+        <v>2708</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>2705</v>
+        <v>2709</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>2706</v>
+        <v>2710</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>2707</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>2708</v>
+        <v>2711</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>2709</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>233</v>
+        <v>2712</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>2713</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>2710</v>
+        <v>2714</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>352</v>
+        <v>233</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>2711</v>
+        <v>2715</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>2712</v>
+        <v>2716</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>217</v>
+        <v>316</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>2713</v>
+        <v>2717</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>309</v>
+        <v>217</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>2714</v>
+        <v>2718</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>2715</v>
+        <v>2719</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>2716</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>2717</v>
+        <v>2720</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>267</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>2718</v>
+        <v>2722</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>329</v>
+        <v>267</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>2719</v>
+        <v>2723</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>221</v>
+        <v>329</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>2720</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>2721</v>
+        <v>2724</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>2722</v>
+        <v>2725</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>2721</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>2723</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>225</v>
+        <v>2727</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>2726</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>2724</v>
+        <v>2728</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>2725</v>
+        <v>2729</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>2726</v>
+        <v>2730</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>2727</v>
+        <v>2731</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>284</v>
+        <v>249</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>2728</v>
+        <v>2732</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>2729</v>
+        <v>284</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>2730</v>
+        <v>2733</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>284</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>2731</v>
-      </c>
-      <c r="D169" s="3" t="s">
-        <v>2721</v>
+        <v>2735</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>2732</v>
+        <v>2736</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>2721</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>2733</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>377</v>
+        <v>2737</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>2726</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>2734</v>
+        <v>2738</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>2735</v>
+        <v>2739</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>2736</v>
+        <v>381</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>2737</v>
+        <v>2740</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>2739</v>
-      </c>
-      <c r="D175" s="3" t="s">
-        <v>2740</v>
+        <v>2742</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>2743</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>2741</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>2742</v>
+        <v>2744</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>2745</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>2743</v>
+        <v>2746</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>426</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>2744</v>
+        <v>2748</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>466</v>
+        <v>426</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>2745</v>
+        <v>2749</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>466</v>
@@ -40343,505 +40389,505 @@
     </row>
     <row r="180" spans="1:3">
       <c r="A180" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>2746</v>
+        <v>2750</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>2747</v>
+        <v>466</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>2748</v>
+        <v>2751</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>2749</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>2750</v>
+        <v>2753</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>2751</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>2752</v>
+        <v>2755</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>417</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>2753</v>
+        <v>2757</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>2754</v>
+        <v>2758</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>446</v>
+        <v>385</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>2755</v>
+        <v>2759</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>390</v>
+        <v>446</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>2756</v>
+        <v>2760</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>450</v>
+        <v>390</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>2757</v>
+        <v>2761</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>2758</v>
+        <v>2762</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>2759</v>
+        <v>2763</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>2760</v>
+        <v>2764</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>410</v>
+        <v>462</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>2761</v>
+        <v>2765</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>2762</v>
+        <v>2766</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>470</v>
+        <v>393</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>2763</v>
-      </c>
-      <c r="D194" s="3" t="s">
-        <v>2764</v>
+        <v>2767</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>2765</v>
+        <v>2768</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>2766</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>2767</v>
+        <v>2770</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>2768</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>2769</v>
+        <v>2772</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>2770</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>2771</v>
+        <v>2774</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>2772</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>2773</v>
-      </c>
-      <c r="C199" s="3" t="s">
-        <v>2774</v>
+        <v>2776</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>2777</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>2775</v>
+        <v>2778</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>592</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>2776</v>
+        <v>2780</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>2777</v>
+        <v>592</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>2778</v>
+        <v>2781</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>601</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>2779</v>
+        <v>2783</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>518</v>
+        <v>601</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>2780</v>
+        <v>2784</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>562</v>
+        <v>518</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>2781</v>
+        <v>2785</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>2782</v>
+        <v>562</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>2783</v>
+        <v>2786</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>610</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>2784</v>
-      </c>
-      <c r="D207" s="3" t="s">
-        <v>2785</v>
+        <v>2788</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>2786</v>
+        <v>2789</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>2787</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>2788</v>
+        <v>2791</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>2789</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>2790</v>
-      </c>
-      <c r="C210" s="3" t="s">
-        <v>2791</v>
+        <v>2793</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>2794</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>2792</v>
+        <v>2795</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>571</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>2793</v>
+        <v>2797</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>2794</v>
+        <v>2798</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>596</v>
+        <v>574</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>2795</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>2796</v>
+        <v>2799</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>2799</v>
+        <v>2802</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>2800</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>2801</v>
-      </c>
-      <c r="C217" s="3" t="s">
-        <v>530</v>
+        <v>2804</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>2805</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>2802</v>
+        <v>2806</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>555</v>
+        <v>530</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>2803</v>
+        <v>2807</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>578</v>
+        <v>555</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>2804</v>
-      </c>
-      <c r="D220" s="3" t="s">
-        <v>2805</v>
+        <v>2808</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>2806</v>
-      </c>
-      <c r="C221" s="3" t="s">
-        <v>511</v>
+        <v>2809</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>2810</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>2807</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>2808</v>
+        <v>2811</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>2809</v>
-      </c>
-      <c r="C223" s="3" t="s">
-        <v>581</v>
+        <v>2812</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>2813</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>2810</v>
+        <v>2814</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>2811</v>
+        <v>2815</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>547</v>
@@ -40849,527 +40895,527 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>2812</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>2813</v>
+        <v>2816</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>2814</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>585</v>
+        <v>2817</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>2818</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>2815</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>2816</v>
+        <v>2819</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>2817</v>
-      </c>
-      <c r="C229" s="3" t="s">
-        <v>524</v>
+        <v>2820</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>2821</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>2818</v>
+        <v>2822</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>551</v>
+        <v>524</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>2819</v>
+        <v>2823</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>588</v>
+        <v>551</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>2820</v>
+        <v>2824</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>2821</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>2822</v>
+        <v>2825</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>2823</v>
+        <v>2826</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>2824</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>2825</v>
+        <v>2828</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>2826</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>2827</v>
-      </c>
-      <c r="C236" s="3" t="s">
-        <v>633</v>
+        <v>2830</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>2831</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>2828</v>
+        <v>2832</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>2829</v>
+        <v>2833</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>2830</v>
+        <v>2834</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>2831</v>
+        <v>2835</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>2832</v>
+        <v>2836</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>2833</v>
+        <v>2837</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>2834</v>
+        <v>657</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>2835</v>
+        <v>2838</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>2836</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>2837</v>
+        <v>2840</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>677</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>2838</v>
+        <v>2842</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>494</v>
+        <v>677</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>2839</v>
+        <v>2843</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>2840</v>
+        <v>2844</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>2841</v>
+        <v>2845</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>2842</v>
-      </c>
-      <c r="D249" s="3" t="s">
-        <v>2843</v>
+        <v>2846</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>2844</v>
+        <v>2847</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>2845</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>2846</v>
-      </c>
-      <c r="C251" s="3" t="s">
-        <v>727</v>
+        <v>2849</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>2850</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>2847</v>
+        <v>2851</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>686</v>
+        <v>727</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>2848</v>
+        <v>2852</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>2849</v>
+        <v>686</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>2850</v>
+        <v>2853</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>2851</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>2852</v>
+        <v>2855</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>703</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>2853</v>
+        <v>2857</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>2854</v>
+        <v>703</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>2855</v>
+        <v>2858</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>716</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>2856</v>
+        <v>2860</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>2857</v>
+        <v>2861</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>724</v>
+        <v>708</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>2858</v>
+        <v>2862</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>2859</v>
-      </c>
-      <c r="D261" s="3" t="s">
-        <v>2860</v>
+        <v>2863</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>2861</v>
-      </c>
-      <c r="C262" s="3" t="s">
-        <v>2862</v>
+        <v>2864</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>2865</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>2863</v>
+        <v>2866</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>742</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>2864</v>
+        <v>2868</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>772</v>
+        <v>742</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>2865</v>
+        <v>2869</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>2866</v>
+        <v>2870</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>781</v>
+        <v>760</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>2867</v>
+        <v>2871</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>2868</v>
+        <v>2872</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>751</v>
+        <v>769</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>2869</v>
+        <v>2873</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>2870</v>
+        <v>751</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>2871</v>
+        <v>2874</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>788</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>2872</v>
+        <v>2876</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>736</v>
+        <v>788</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>2873</v>
+        <v>2877</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>2874</v>
+        <v>2878</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>747</v>
@@ -41377,24 +41423,24 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="3" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>2875</v>
+        <v>2879</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>794</v>
+        <v>747</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="3" t="s">
-        <v>615</v>
+        <v>2654</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>2876</v>
-      </c>
-      <c r="D275" s="3" t="s">
-        <v>2877</v>
+        <v>2880</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -41402,10 +41448,10 @@
         <v>615</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>2878</v>
+        <v>2881</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>2879</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -41413,10 +41459,10 @@
         <v>615</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>2880</v>
+        <v>2883</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>2881</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -41424,10 +41470,10 @@
         <v>615</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>2882</v>
+        <v>2885</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>2877</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -41435,10 +41481,10 @@
         <v>615</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>2883</v>
+        <v>2887</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>2877</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -41446,10 +41492,10 @@
         <v>615</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>2884</v>
+        <v>2888</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>2877</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -41457,10 +41503,10 @@
         <v>615</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>2885</v>
-      </c>
-      <c r="C281" s="3" t="s">
-        <v>490</v>
+        <v>2889</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>2882</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -41468,10 +41514,10 @@
         <v>615</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>2886</v>
+        <v>2890</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>2887</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -41479,10 +41525,10 @@
         <v>615</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>2888</v>
-      </c>
-      <c r="D283" s="3" t="s">
-        <v>2889</v>
+        <v>2891</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -41490,10 +41536,10 @@
         <v>615</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>2891</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -41501,10 +41547,10 @@
         <v>615</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>2892</v>
+        <v>2894</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>2893</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -41512,10 +41558,10 @@
         <v>615</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>2895</v>
+        <v>2897</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -41523,10 +41569,10 @@
         <v>615</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>2896</v>
+        <v>2898</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>2897</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -41534,10 +41580,10 @@
         <v>615</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>2898</v>
+        <v>2900</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>2899</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -41545,10 +41591,10 @@
         <v>615</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>2900</v>
+        <v>2902</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>2901</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -41556,10 +41602,10 @@
         <v>615</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>2902</v>
+        <v>2904</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>2903</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -41567,10 +41613,10 @@
         <v>615</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>2904</v>
+        <v>2906</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>2905</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -41578,14 +41624,36 @@
         <v>615</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>2906</v>
+        <v>2908</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>2877</v>
+        <v>2909</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>2910</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>2911</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>2912</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>2882</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D292"/>
+  <autoFilter ref="A1:D294"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not in the list" error="Pick one of: operation, job, schedule, handler." promptTitle="Kind" prompt="operation, job, schedule or handler" sqref="A2:A2001">
       <formula1>"operation,job,schedule,handler"</formula1>
@@ -41600,7 +41668,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -41610,328 +41678,342 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>2907</v>
+        <v>2913</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2908</v>
+        <v>2914</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2909</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>2910</v>
+        <v>2916</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2911</v>
+        <v>2917</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2912</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>2913</v>
+        <v>2919</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2914</v>
+        <v>2920</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2915</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>2913</v>
+        <v>2919</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2916</v>
+        <v>2922</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2917</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>2913</v>
+        <v>2919</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2918</v>
+        <v>2924</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2919</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2921</v>
+        <v>2927</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2922</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="B7" s="3">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2923</v>
+        <v>2929</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2924</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="B8" s="3">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2925</v>
+        <v>2931</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2926</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>2927</v>
+        <v>2933</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2928</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2929</v>
+        <v>2935</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2930</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>2931</v>
+        <v>2937</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2932</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2933</v>
+        <v>2939</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2934</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>2935</v>
+        <v>2941</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2936</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="B14" s="3">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>2937</v>
+        <v>2943</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2938</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="B15" s="3">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>2939</v>
+        <v>2945</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2940</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>2941</v>
+        <v>2947</v>
       </c>
       <c r="B16" s="3">
         <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>2942</v>
+        <v>2948</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2943</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>2941</v>
+        <v>2947</v>
       </c>
       <c r="B17" s="3">
         <v>17</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>2944</v>
+        <v>2950</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2945</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>2941</v>
+        <v>2947</v>
       </c>
       <c r="B18" s="3">
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>2946</v>
+        <v>2952</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2947</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>2948</v>
+        <v>2954</v>
       </c>
       <c r="B19" s="3">
         <v>19</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>2949</v>
+        <v>2955</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2950</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>2951</v>
+        <v>2957</v>
       </c>
       <c r="B20" s="3">
         <v>20</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>2952</v>
+        <v>2958</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2953</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="3" t="s">
-        <v>2951</v>
+        <v>2957</v>
       </c>
       <c r="B21" s="3">
         <v>21</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>2954</v>
+        <v>2960</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2955</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>2951</v>
+        <v>2957</v>
       </c>
       <c r="B22" s="3">
         <v>22</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>2956</v>
+        <v>2962</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2957</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="3" t="s">
-        <v>2951</v>
+        <v>2957</v>
       </c>
       <c r="B23" s="3">
         <v>23</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>2958</v>
+        <v>2964</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2959</v>
+        <v>2965</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="3" t="s">
+        <v>2957</v>
+      </c>
+      <c r="B24" s="3">
+        <v>26</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>2966</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>2967</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D23"/>
+  <autoFilter ref="A1:D24"/>
   <dataValidations count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Date" prompt="YYYY-MM-DD" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Plan version" prompt="From 1, one per change." sqref="B2:B2001"/>

--- a/tracking/tracking-plan.xlsx
+++ b/tracking/tracking-plan.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Actors!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$294</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Changelog!$A$1:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Coverage!$A$1:$D$295</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enums!$A$1:$C$477</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Events!$A$1:$L$174</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Properties!$A$1:$K$367</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8997" uniqueCount="2968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9003" uniqueCount="2972">
   <si>
     <t>Campbooks tracking plan</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Plan version</t>
   </si>
   <si>
-    <t>26 (2026-10-28)</t>
+    <t>27 (2026-10-31)</t>
   </si>
   <si>
     <t>What this is</t>
@@ -7721,6 +7721,9 @@
     <t>schedule.apply_calendar_changes</t>
   </si>
   <si>
+    <t>schedule.apply_calendar_list</t>
+  </si>
+  <si>
     <t>schedule.apply_outcome</t>
   </si>
   <si>
@@ -8934,6 +8937,15 @@
   </si>
   <si>
     <t>#705</t>
+  </si>
+  <si>
+    <t>2026-10-31</t>
+  </si>
+  <si>
+    <t>Calendars shared after connecting (campbooks-cloud#405): Coverage for schedule.apply_calendar_list, which tracks the calendars it adds as schedule.calendar_added.</t>
+  </si>
+  <si>
+    <t>#713</t>
   </si>
 </sst>
 </file>
@@ -38406,7 +38418,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D294"/>
+  <dimension ref="A1:D295"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -38921,7 +38933,7 @@
         <v>2563</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>149</v>
+        <v>614</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -38932,7 +38944,7 @@
         <v>2564</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>665</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -38942,8 +38954,8 @@
       <c r="B48" s="3" t="s">
         <v>2565</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>2566</v>
+      <c r="C48" s="3" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -38951,10 +38963,10 @@
         <v>2490</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>2566</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>2567</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -38964,8 +38976,8 @@
       <c r="B50" s="3" t="s">
         <v>2568</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>2494</v>
+      <c r="C50" s="3" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -38976,7 +38988,7 @@
         <v>2569</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>2570</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -38984,10 +38996,10 @@
         <v>2490</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>2571</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>2572</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -38995,10 +39007,10 @@
         <v>2490</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>2572</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>2573</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>2574</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -39006,10 +39018,10 @@
         <v>2490</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>2575</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>2576</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -39017,10 +39029,10 @@
         <v>2490</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>2576</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>2577</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>2578</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -39028,10 +39040,10 @@
         <v>2490</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>2578</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>2579</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>2580</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -39039,10 +39051,10 @@
         <v>2490</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>2580</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>2581</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>2582</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -39050,10 +39062,10 @@
         <v>2490</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>2582</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>2583</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -39064,7 +39076,7 @@
         <v>2584</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>2585</v>
+        <v>708</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -39072,10 +39084,10 @@
         <v>2490</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>2586</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -39086,7 +39098,7 @@
         <v>2587</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>732</v>
+        <v>703</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -39096,8 +39108,8 @@
       <c r="B62" s="3" t="s">
         <v>2588</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>2494</v>
+      <c r="C62" s="3" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -39107,8 +39119,8 @@
       <c r="B63" s="3" t="s">
         <v>2589</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>754</v>
+      <c r="D63" s="3" t="s">
+        <v>2494</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -39119,18 +39131,18 @@
         <v>2590</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="3" t="s">
-        <v>496</v>
+        <v>2490</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>2591</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>2592</v>
+      <c r="C65" s="3" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -39138,10 +39150,10 @@
         <v>496</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>2592</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>2593</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>2594</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -39149,10 +39161,10 @@
         <v>496</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>2594</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>2595</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>2596</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -39160,10 +39172,10 @@
         <v>496</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>2596</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>2597</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>2598</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -39171,10 +39183,10 @@
         <v>496</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>2598</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>2599</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -39185,7 +39197,7 @@
         <v>2600</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>2601</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -39193,10 +39205,10 @@
         <v>496</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>2602</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>2603</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -39204,10 +39216,10 @@
         <v>496</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>2603</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>2604</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -39218,7 +39230,7 @@
         <v>2605</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>359</v>
+        <v>295</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -39228,8 +39240,8 @@
       <c r="B74" s="3" t="s">
         <v>2606</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>2607</v>
+      <c r="C74" s="3" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -39237,10 +39249,10 @@
         <v>496</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>2607</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>2608</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -39251,7 +39263,7 @@
         <v>2609</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>300</v>
+        <v>271</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -39261,8 +39273,8 @@
       <c r="B77" s="3" t="s">
         <v>2610</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>2611</v>
+      <c r="C77" s="3" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -39270,10 +39282,10 @@
         <v>496</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>2611</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>2612</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>2613</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -39281,10 +39293,10 @@
         <v>496</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>2614</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>2615</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -39292,10 +39304,10 @@
         <v>496</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>2615</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>2616</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -39316,8 +39328,8 @@
       <c r="B82" s="3" t="s">
         <v>2618</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>2607</v>
+      <c r="C82" s="3" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -39327,8 +39339,8 @@
       <c r="B83" s="3" t="s">
         <v>2619</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>2620</v>
+      <c r="D83" s="3" t="s">
+        <v>2608</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -39336,10 +39348,10 @@
         <v>496</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>2620</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>2621</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>2622</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -39347,10 +39359,10 @@
         <v>496</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>2623</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>2624</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -39358,10 +39370,10 @@
         <v>496</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>2624</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>2625</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -39371,8 +39383,8 @@
       <c r="B87" s="3" t="s">
         <v>2626</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>2607</v>
+      <c r="C87" s="3" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -39383,7 +39395,7 @@
         <v>2627</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>2628</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -39391,10 +39403,10 @@
         <v>496</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>2628</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>2629</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>2630</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -39402,10 +39414,10 @@
         <v>496</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>2630</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>2631</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>2632</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -39413,10 +39425,10 @@
         <v>496</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>2633</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>2634</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -39424,10 +39436,10 @@
         <v>496</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>2634</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>2635</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>2636</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -39435,10 +39447,10 @@
         <v>496</v>
       </c>
       <c r="B93" s="3" t="s">
+        <v>2636</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>2637</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>2638</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -39446,10 +39458,10 @@
         <v>496</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>2638</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>2639</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>2640</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -39457,10 +39469,10 @@
         <v>496</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>2641</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>2642</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -39468,10 +39480,10 @@
         <v>496</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>2642</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>2643</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -39492,8 +39504,8 @@
       <c r="B98" s="3" t="s">
         <v>2645</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>2646</v>
+      <c r="C98" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -39501,10 +39513,10 @@
         <v>496</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>2646</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>2647</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>2648</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -39512,10 +39524,10 @@
         <v>496</v>
       </c>
       <c r="B100" s="3" t="s">
+        <v>2648</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>2649</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>2650</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -39523,10 +39535,10 @@
         <v>496</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>2650</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>2651</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>2652</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -39534,125 +39546,125 @@
         <v>496</v>
       </c>
       <c r="B102" s="3" t="s">
+        <v>2652</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>2653</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>2654</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>2655</v>
-      </c>
       <c r="C103" s="3" t="s">
-        <v>2656</v>
+        <v>791</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B104" s="3" t="s">
+        <v>2656</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>2657</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>2658</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>2658</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>2659</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>2660</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>2661</v>
+        <v>85</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B107" s="3" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>2662</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>2663</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>2656</v>
+        <v>89</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>2664</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>93</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>2665</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>2666</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>2667</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>2668</v>
@@ -39663,7 +39675,7 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>2669</v>
@@ -39674,7 +39686,7 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>2670</v>
@@ -39685,7 +39697,7 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>2671</v>
@@ -39696,7 +39708,7 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>2672</v>
@@ -39707,7 +39719,7 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>2673</v>
@@ -39718,7 +39730,7 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>2674</v>
@@ -39729,7 +39741,7 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>2675</v>
@@ -39740,7 +39752,7 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>2676</v>
@@ -39751,51 +39763,51 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>2677</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>2678</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>2679</v>
+        <v>132</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B124" s="3" t="s">
+        <v>2679</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>2680</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>2681</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B125" s="3" t="s">
+        <v>2681</v>
+      </c>
+      <c r="D125" s="3" t="s">
         <v>2682</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>2683</v>
@@ -39806,590 +39818,590 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>2684</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>2685</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>2686</v>
+        <v>137</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B129" s="3" t="s">
+        <v>2686</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>2687</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>2688</v>
       </c>
-      <c r="D130" s="3" t="s">
-        <v>2689</v>
+      <c r="C130" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B131" s="3" t="s">
+        <v>2689</v>
+      </c>
+      <c r="D131" s="3" t="s">
         <v>2690</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>2691</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B132" s="3" t="s">
+        <v>2691</v>
+      </c>
+      <c r="D132" s="3" t="s">
         <v>2692</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>2693</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>2694</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>348</v>
+        <v>204</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>2695</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>196</v>
+        <v>348</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>2696</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>279</v>
+        <v>196</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>2697</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>343</v>
+        <v>279</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>2698</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>2699</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>2700</v>
+        <v>312</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B140" s="3" t="s">
+        <v>2700</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>2701</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>2702</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>2703</v>
+        <v>253</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B142" s="3" t="s">
+        <v>2703</v>
+      </c>
+      <c r="C142" s="3" t="s">
         <v>2704</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>2705</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>259</v>
+        <v>340</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>2706</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>324</v>
+        <v>259</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>2707</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>2708</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>213</v>
+        <v>363</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>2709</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>2710</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>2711</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>2712</v>
       </c>
-      <c r="D150" s="3" t="s">
-        <v>2713</v>
+      <c r="C150" s="3" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B151" s="3" t="s">
+        <v>2713</v>
+      </c>
+      <c r="D151" s="3" t="s">
         <v>2714</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>2715</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>352</v>
+        <v>233</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>2716</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>2717</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>217</v>
+        <v>316</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>2718</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>309</v>
+        <v>217</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>2719</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>2720</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>2721</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B158" s="3" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C158" s="3" t="s">
         <v>2722</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>2723</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>329</v>
+        <v>267</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>2724</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>221</v>
+        <v>329</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>2725</v>
       </c>
-      <c r="D161" s="3" t="s">
-        <v>2726</v>
+      <c r="C161" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B162" s="3" t="s">
+        <v>2726</v>
+      </c>
+      <c r="D162" s="3" t="s">
         <v>2727</v>
-      </c>
-      <c r="D162" s="3" t="s">
-        <v>2726</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>2728</v>
       </c>
-      <c r="C163" s="3" t="s">
-        <v>225</v>
+      <c r="D163" s="3" t="s">
+        <v>2727</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>2729</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>2730</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>2731</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>2732</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>284</v>
+        <v>249</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>2733</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>2734</v>
+        <v>284</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B169" s="3" t="s">
+        <v>2734</v>
+      </c>
+      <c r="C169" s="3" t="s">
         <v>2735</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>2736</v>
       </c>
-      <c r="D170" s="3" t="s">
-        <v>2726</v>
+      <c r="C170" s="3" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>2737</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>2726</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>2738</v>
       </c>
-      <c r="C172" s="3" t="s">
-        <v>377</v>
+      <c r="D172" s="3" t="s">
+        <v>2727</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>2739</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>2740</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>2741</v>
+        <v>381</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B175" s="3" t="s">
+        <v>2741</v>
+      </c>
+      <c r="C175" s="3" t="s">
         <v>2742</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>2743</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B176" s="3" t="s">
+        <v>2743</v>
+      </c>
+      <c r="C176" s="3" t="s">
         <v>2744</v>
       </c>
-      <c r="D176" s="3" t="s">
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" s="3" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B177" s="3" t="s">
         <v>2745</v>
       </c>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="A177" s="3" t="s">
-        <v>2654</v>
-      </c>
-      <c r="B177" s="3" t="s">
+      <c r="D177" s="3" t="s">
         <v>2746</v>
       </c>
-      <c r="C177" s="3" t="s">
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" s="3" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B178" s="3" t="s">
         <v>2747</v>
       </c>
-    </row>
-    <row r="178" spans="1:3">
-      <c r="A178" s="3" t="s">
-        <v>2654</v>
-      </c>
-      <c r="B178" s="3" t="s">
+      <c r="C178" s="3" t="s">
         <v>2748</v>
       </c>
-      <c r="C178" s="3" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3">
+    </row>
+    <row r="179" spans="1:4">
       <c r="A179" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>2749</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
       <c r="A180" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>2750</v>
@@ -40398,504 +40410,504 @@
         <v>466</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:4">
       <c r="A181" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>2751</v>
       </c>
       <c r="C181" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" s="3" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B182" s="3" t="s">
         <v>2752</v>
       </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182" s="3" t="s">
-        <v>2654</v>
-      </c>
-      <c r="B182" s="3" t="s">
+      <c r="C182" s="3" t="s">
         <v>2753</v>
       </c>
-      <c r="C182" s="3" t="s">
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" s="3" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B183" s="3" t="s">
         <v>2754</v>
       </c>
-    </row>
-    <row r="183" spans="1:3">
-      <c r="A183" s="3" t="s">
-        <v>2654</v>
-      </c>
-      <c r="B183" s="3" t="s">
+      <c r="C183" s="3" t="s">
         <v>2755</v>
       </c>
-      <c r="C183" s="3" t="s">
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" s="3" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B184" s="3" t="s">
         <v>2756</v>
       </c>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="A184" s="3" t="s">
-        <v>2654</v>
-      </c>
-      <c r="B184" s="3" t="s">
+      <c r="C184" s="3" t="s">
         <v>2757</v>
       </c>
-      <c r="C184" s="3" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3">
+    </row>
+    <row r="185" spans="1:4">
       <c r="A185" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>2758</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
       <c r="A186" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>2759</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
       <c r="A187" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>2760</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
       <c r="A188" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>2761</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
       <c r="A189" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>2762</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
       <c r="A190" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>2763</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
       <c r="A191" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>2764</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
       <c r="A192" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>2765</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>410</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>2766</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>2767</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>470</v>
+        <v>393</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>2768</v>
       </c>
-      <c r="D195" s="3" t="s">
-        <v>2769</v>
+      <c r="C195" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>2769</v>
+      </c>
+      <c r="D196" s="3" t="s">
         <v>2770</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>2771</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B197" s="3" t="s">
+        <v>2771</v>
+      </c>
+      <c r="D197" s="3" t="s">
         <v>2772</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>2773</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B198" s="3" t="s">
+        <v>2773</v>
+      </c>
+      <c r="D198" s="3" t="s">
         <v>2774</v>
-      </c>
-      <c r="D198" s="3" t="s">
-        <v>2775</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B199" s="3" t="s">
+        <v>2775</v>
+      </c>
+      <c r="D199" s="3" t="s">
         <v>2776</v>
-      </c>
-      <c r="D199" s="3" t="s">
-        <v>2777</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B200" s="3" t="s">
+        <v>2777</v>
+      </c>
+      <c r="D200" s="3" t="s">
         <v>2778</v>
-      </c>
-      <c r="C200" s="3" t="s">
-        <v>2779</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B201" s="3" t="s">
+        <v>2779</v>
+      </c>
+      <c r="C201" s="3" t="s">
         <v>2780</v>
-      </c>
-      <c r="C201" s="3" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>2781</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>2782</v>
+        <v>592</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B203" s="3" t="s">
+        <v>2782</v>
+      </c>
+      <c r="C203" s="3" t="s">
         <v>2783</v>
-      </c>
-      <c r="C203" s="3" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>2784</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>518</v>
+        <v>601</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>2785</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>562</v>
+        <v>518</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>2786</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>2787</v>
+        <v>562</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B207" s="3" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C207" s="3" t="s">
         <v>2788</v>
-      </c>
-      <c r="C207" s="3" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>2789</v>
       </c>
-      <c r="D208" s="3" t="s">
-        <v>2790</v>
+      <c r="C208" s="3" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B209" s="3" t="s">
+        <v>2790</v>
+      </c>
+      <c r="D209" s="3" t="s">
         <v>2791</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>2792</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B210" s="3" t="s">
+        <v>2792</v>
+      </c>
+      <c r="D210" s="3" t="s">
         <v>2793</v>
-      </c>
-      <c r="D210" s="3" t="s">
-        <v>2794</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B211" s="3" t="s">
+        <v>2794</v>
+      </c>
+      <c r="D211" s="3" t="s">
         <v>2795</v>
-      </c>
-      <c r="C211" s="3" t="s">
-        <v>2796</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B212" s="3" t="s">
+        <v>2796</v>
+      </c>
+      <c r="C212" s="3" t="s">
         <v>2797</v>
-      </c>
-      <c r="C212" s="3" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>2798</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>2799</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>596</v>
+        <v>574</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>2800</v>
       </c>
-      <c r="D215" s="3" t="s">
-        <v>2801</v>
+      <c r="C215" s="3" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B216" s="3" t="s">
+        <v>2801</v>
+      </c>
+      <c r="D216" s="3" t="s">
         <v>2802</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B217" s="3" t="s">
+        <v>2803</v>
+      </c>
+      <c r="D217" s="3" t="s">
         <v>2804</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>2805</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B218" s="3" t="s">
+        <v>2805</v>
+      </c>
+      <c r="D218" s="3" t="s">
         <v>2806</v>
-      </c>
-      <c r="C218" s="3" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>2807</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>555</v>
+        <v>530</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>2808</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>578</v>
+        <v>555</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>2809</v>
       </c>
-      <c r="D221" s="3" t="s">
-        <v>2810</v>
+      <c r="C221" s="3" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B222" s="3" t="s">
+        <v>2810</v>
+      </c>
+      <c r="D222" s="3" t="s">
         <v>2811</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>2812</v>
       </c>
-      <c r="D223" s="3" t="s">
-        <v>2813</v>
+      <c r="C223" s="3" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B224" s="3" t="s">
+        <v>2813</v>
+      </c>
+      <c r="D224" s="3" t="s">
         <v>2814</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>2815</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>2816</v>
@@ -40906,524 +40918,524 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>2817</v>
       </c>
-      <c r="D227" s="3" t="s">
-        <v>2818</v>
+      <c r="C227" s="3" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B228" s="3" t="s">
+        <v>2818</v>
+      </c>
+      <c r="D228" s="3" t="s">
         <v>2819</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>2820</v>
       </c>
-      <c r="D229" s="3" t="s">
-        <v>2821</v>
+      <c r="C229" s="3" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B230" s="3" t="s">
+        <v>2821</v>
+      </c>
+      <c r="D230" s="3" t="s">
         <v>2822</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>2823</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>551</v>
+        <v>524</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>2824</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>588</v>
+        <v>551</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>2825</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>2826</v>
       </c>
-      <c r="D234" s="3" t="s">
-        <v>2827</v>
+      <c r="C234" s="3" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B235" s="3" t="s">
+        <v>2827</v>
+      </c>
+      <c r="D235" s="3" t="s">
         <v>2828</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>2829</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B236" s="3" t="s">
+        <v>2829</v>
+      </c>
+      <c r="D236" s="3" t="s">
         <v>2830</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>2831</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B237" s="3" t="s">
+        <v>2831</v>
+      </c>
+      <c r="D237" s="3" t="s">
         <v>2832</v>
-      </c>
-      <c r="C237" s="3" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>2833</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>2834</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>2835</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>2836</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>2837</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>2838</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>2839</v>
+        <v>657</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B244" s="3" t="s">
+        <v>2839</v>
+      </c>
+      <c r="C244" s="3" t="s">
         <v>2840</v>
-      </c>
-      <c r="C244" s="3" t="s">
-        <v>2841</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B245" s="3" t="s">
+        <v>2841</v>
+      </c>
+      <c r="C245" s="3" t="s">
         <v>2842</v>
-      </c>
-      <c r="C245" s="3" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>2843</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>494</v>
+        <v>677</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>2844</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>2845</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>2846</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>2847</v>
       </c>
-      <c r="D250" s="3" t="s">
-        <v>2848</v>
+      <c r="C250" s="3" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B251" s="3" t="s">
+        <v>2848</v>
+      </c>
+      <c r="D251" s="3" t="s">
         <v>2849</v>
-      </c>
-      <c r="D251" s="3" t="s">
-        <v>2850</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B252" s="3" t="s">
+        <v>2850</v>
+      </c>
+      <c r="D252" s="3" t="s">
         <v>2851</v>
-      </c>
-      <c r="C252" s="3" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>2852</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>686</v>
+        <v>727</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>2853</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>2854</v>
+        <v>686</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B255" s="3" t="s">
+        <v>2854</v>
+      </c>
+      <c r="C255" s="3" t="s">
         <v>2855</v>
-      </c>
-      <c r="C255" s="3" t="s">
-        <v>2856</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B256" s="3" t="s">
+        <v>2856</v>
+      </c>
+      <c r="C256" s="3" t="s">
         <v>2857</v>
-      </c>
-      <c r="C256" s="3" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>2858</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>2859</v>
+        <v>703</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B258" s="3" t="s">
+        <v>2859</v>
+      </c>
+      <c r="C258" s="3" t="s">
         <v>2860</v>
-      </c>
-      <c r="C258" s="3" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>2861</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>2862</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>724</v>
+        <v>708</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>2863</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>2864</v>
       </c>
-      <c r="D262" s="3" t="s">
-        <v>2865</v>
+      <c r="C262" s="3" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B263" s="3" t="s">
+        <v>2865</v>
+      </c>
+      <c r="D263" s="3" t="s">
         <v>2866</v>
-      </c>
-      <c r="C263" s="3" t="s">
-        <v>2867</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B264" s="3" t="s">
+        <v>2867</v>
+      </c>
+      <c r="C264" s="3" t="s">
         <v>2868</v>
-      </c>
-      <c r="C264" s="3" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>2869</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>772</v>
+        <v>742</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>2870</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>2871</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>781</v>
+        <v>760</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>2872</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>2873</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>751</v>
+        <v>769</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>2874</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>2875</v>
+        <v>751</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B271" s="3" t="s">
+        <v>2875</v>
+      </c>
+      <c r="C271" s="3" t="s">
         <v>2876</v>
-      </c>
-      <c r="C271" s="3" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>2877</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>736</v>
+        <v>788</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>2878</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>2879</v>
@@ -41434,24 +41446,24 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="3" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>2880</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>794</v>
+        <v>747</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="3" t="s">
-        <v>615</v>
+        <v>2655</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>2881</v>
       </c>
-      <c r="D276" s="3" t="s">
-        <v>2882</v>
+      <c r="C276" s="3" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -41459,10 +41471,10 @@
         <v>615</v>
       </c>
       <c r="B277" s="3" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D277" s="3" t="s">
         <v>2883</v>
-      </c>
-      <c r="D277" s="3" t="s">
-        <v>2884</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -41470,10 +41482,10 @@
         <v>615</v>
       </c>
       <c r="B278" s="3" t="s">
+        <v>2884</v>
+      </c>
+      <c r="D278" s="3" t="s">
         <v>2885</v>
-      </c>
-      <c r="D278" s="3" t="s">
-        <v>2886</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -41481,10 +41493,10 @@
         <v>615</v>
       </c>
       <c r="B279" s="3" t="s">
+        <v>2886</v>
+      </c>
+      <c r="D279" s="3" t="s">
         <v>2887</v>
-      </c>
-      <c r="D279" s="3" t="s">
-        <v>2882</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -41495,7 +41507,7 @@
         <v>2888</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -41506,7 +41518,7 @@
         <v>2889</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -41517,7 +41529,7 @@
         <v>2890</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -41527,8 +41539,8 @@
       <c r="B283" s="3" t="s">
         <v>2891</v>
       </c>
-      <c r="C283" s="3" t="s">
-        <v>490</v>
+      <c r="D283" s="3" t="s">
+        <v>2883</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -41538,8 +41550,8 @@
       <c r="B284" s="3" t="s">
         <v>2892</v>
       </c>
-      <c r="D284" s="3" t="s">
-        <v>2893</v>
+      <c r="C284" s="3" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -41547,10 +41559,10 @@
         <v>615</v>
       </c>
       <c r="B285" s="3" t="s">
+        <v>2893</v>
+      </c>
+      <c r="D285" s="3" t="s">
         <v>2894</v>
-      </c>
-      <c r="D285" s="3" t="s">
-        <v>2895</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -41558,10 +41570,10 @@
         <v>615</v>
       </c>
       <c r="B286" s="3" t="s">
+        <v>2895</v>
+      </c>
+      <c r="D286" s="3" t="s">
         <v>2896</v>
-      </c>
-      <c r="D286" s="3" t="s">
-        <v>2897</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -41569,10 +41581,10 @@
         <v>615</v>
       </c>
       <c r="B287" s="3" t="s">
+        <v>2897</v>
+      </c>
+      <c r="D287" s="3" t="s">
         <v>2898</v>
-      </c>
-      <c r="D287" s="3" t="s">
-        <v>2899</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -41580,10 +41592,10 @@
         <v>615</v>
       </c>
       <c r="B288" s="3" t="s">
+        <v>2899</v>
+      </c>
+      <c r="D288" s="3" t="s">
         <v>2900</v>
-      </c>
-      <c r="D288" s="3" t="s">
-        <v>2901</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -41591,10 +41603,10 @@
         <v>615</v>
       </c>
       <c r="B289" s="3" t="s">
+        <v>2901</v>
+      </c>
+      <c r="D289" s="3" t="s">
         <v>2902</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>2903</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -41602,10 +41614,10 @@
         <v>615</v>
       </c>
       <c r="B290" s="3" t="s">
+        <v>2903</v>
+      </c>
+      <c r="D290" s="3" t="s">
         <v>2904</v>
-      </c>
-      <c r="D290" s="3" t="s">
-        <v>2905</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -41613,10 +41625,10 @@
         <v>615</v>
       </c>
       <c r="B291" s="3" t="s">
+        <v>2905</v>
+      </c>
+      <c r="D291" s="3" t="s">
         <v>2906</v>
-      </c>
-      <c r="D291" s="3" t="s">
-        <v>2907</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -41624,10 +41636,10 @@
         <v>615</v>
       </c>
       <c r="B292" s="3" t="s">
+        <v>2907</v>
+      </c>
+      <c r="D292" s="3" t="s">
         <v>2908</v>
-      </c>
-      <c r="D292" s="3" t="s">
-        <v>2909</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -41635,10 +41647,10 @@
         <v>615</v>
       </c>
       <c r="B293" s="3" t="s">
+        <v>2909</v>
+      </c>
+      <c r="D293" s="3" t="s">
         <v>2910</v>
-      </c>
-      <c r="D293" s="3" t="s">
-        <v>2911</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -41646,14 +41658,25 @@
         <v>615</v>
       </c>
       <c r="B294" s="3" t="s">
+        <v>2911</v>
+      </c>
+      <c r="D294" s="3" t="s">
         <v>2912</v>
       </c>
-      <c r="D294" s="3" t="s">
-        <v>2882</v>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>2913</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>2883</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D294"/>
+  <autoFilter ref="A1:D295"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not in the list" error="Pick one of: operation, job, schedule, handler." promptTitle="Kind" prompt="operation, job, schedule or handler" sqref="A2:A2001">
       <formula1>"operation,job,schedule,handler"</formula1>
@@ -41668,7 +41691,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -41678,342 +41701,356 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B7" s="3">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B8" s="3">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B14" s="3">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B15" s="3">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="B16" s="3">
         <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="B17" s="3">
         <v>17</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="B18" s="3">
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B19" s="3">
         <v>19</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="B20" s="3">
         <v>20</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="3" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="B21" s="3">
         <v>21</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="B22" s="3">
         <v>22</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="3" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="B23" s="3">
         <v>23</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="3" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="B24" s="3">
         <v>26</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>2967</v>
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="3" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B25" s="3">
+        <v>27</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>2970</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>2971</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D24"/>
+  <autoFilter ref="A1:D25"/>
   <dataValidations count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Date" prompt="YYYY-MM-DD" sqref="A2:A2001"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Plan version" prompt="From 1, one per change." sqref="B2:B2001"/>
